--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,6 +560,369 @@
       <c r="AC1" t="inlineStr">
         <is>
           <t>PDF Path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gregory</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Ehmann</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>An</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>35215 N 7th St</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85086</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>$190,328.00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>is regulated by  &amp;</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2018089979</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>July 28, 2026</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>20260221869</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Gregory L Ehmann, an unmarried man</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>ocr_fallback</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221869</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221869.pdf</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260221869.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Himmelstein &amp; Adkins, LLC, 6720 North Scottsdale Road, Suite 261, Scottsdale, Arizona 85253, on</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>$972,000.00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>{Qualified under A.R.S. section 33-803.A.2]</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>021-0188851</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>February 19, 2021</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>20260221886</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>See Exhibit A
+Tax Parcel Number{s]: 304-53-189
+Original Principal Balance: $972,000.00
+Current Beneficiary’s
+Name and Address: FINEMARK NATIONAL BANK &amp; TRUST
+7600 East Doubletree Ranch Road, Suite 100
+Scottsdale, AZ 85258
+Original Trustor’s
+Name and Address: Seth Dixon
+Jessica Dixon
+2111 E. Melrose Street
+Gilbert, AZ 85297
+1031.001 / Dixon / Trustee’s Sale (2026) / Notice of Trustee’s Sale
+20260221886
+Current Trustee’s
+Name and Address: Todd M. Adkins, Esq.
+Himmelstein &amp; Adkins, LLC
+6720 North Scottsdale Road, Suite 261
+Scottsdale, Arizona 85253
+Phone: (480) 922-3933
+This sale will not exhaust the power of sale contained in the Deed of Trust as to any remaining
+property encumbered by the Deed of Trust or the financing statements described above, which may, at the
+Beneficiary’s option, be sold in one or more subsequent sale proceedings. The recordation of this Notice
+does not constitute an election to proceed against any given collateral, or to pursue any given remedy, to
+the exclusio</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>ocr_fallback;missing_owner</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221886</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221886.pdf</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260221886.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>is 150 5. Dobson</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>150 Dobson Road</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85202:</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>thereof</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>$1,932,500.00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>appointed herein qualifies as trustee of the Trust Deed in the trustee’s capacity as a</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2022083246</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>20260222380</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>ACCORDING TO THE DEED OF TRUST OR UPON INFORMATION SUPPLIED BY THE BENEFICIARY, THE
+FOLLOWING INFORMATION IS PROVIDED PURSUANT TO A.R.S. SECTION 33-808(C):
+Street address or identifiable location: 150 S. Dobson Road
+Mesa, AZ 85202
+A.P.N.: 134-33-0023
+Original Principal Balance: $1,932,500.00
+NAME AND ADDRESS OF ORIGINAL TRUSTOR (as shown on the Deed of Trust):
+JNRL Enterprises, LLC, an Arizona limited liability company
+150 S. Dobson Road
+Mesa, AZ 85202
+NAME AND ADDRESS OF BENEFICIARY (as of recording of Notice of Sale):
+Live Oak Banking Company
+1741 Tiburon Drive
+Wilmington, NC 28403
+20260222380
+TS#: Live Oak v JNRL Ent. Loan #: XX3485
+NOTICE OF TRUSTEE'S SALE
+The successor trustee appointed herein qualifies as trustee of the Trust Deed in the trustee’s capacity as a
+member of the Arizona State Bar as required by ARS Section 33-803, Subsection A(2). Name of Trustee's
+Regulator: Arizona State Bar Association
+NAME, ADDRESS &amp; TELEPHONE NUMBER OF TRUSTEE (as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>ocr_fallback;missing_owner</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222380</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222380.pdf</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222380.pdf</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,369 +560,6 @@
       <c r="AC1" t="inlineStr">
         <is>
           <t>PDF Path</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Gregory</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ehmann</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>An</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>35215 N 7th St</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>85086</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>$190,328.00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>is regulated by  &amp;</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2018089979</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>July 28, 2026</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>20260221869</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Gregory L Ehmann, an unmarried man</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="n">
-        <v>85</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>ocr_fallback</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221869</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221869.pdf</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260221869.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Himmelstein &amp; Adkins, LLC, 6720 North Scottsdale Road, Suite 261, Scottsdale, Arizona 85253, on</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>$972,000.00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>{Qualified under A.R.S. section 33-803.A.2]</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>021-0188851</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>February 19, 2021</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>20260221886</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>See Exhibit A
-Tax Parcel Number{s]: 304-53-189
-Original Principal Balance: $972,000.00
-Current Beneficiary’s
-Name and Address: FINEMARK NATIONAL BANK &amp; TRUST
-7600 East Doubletree Ranch Road, Suite 100
-Scottsdale, AZ 85258
-Original Trustor’s
-Name and Address: Seth Dixon
-Jessica Dixon
-2111 E. Melrose Street
-Gilbert, AZ 85297
-1031.001 / Dixon / Trustee’s Sale (2026) / Notice of Trustee’s Sale
-20260221886
-Current Trustee’s
-Name and Address: Todd M. Adkins, Esq.
-Himmelstein &amp; Adkins, LLC
-6720 North Scottsdale Road, Suite 261
-Scottsdale, Arizona 85253
-Phone: (480) 922-3933
-This sale will not exhaust the power of sale contained in the Deed of Trust as to any remaining
-property encumbered by the Deed of Trust or the financing statements described above, which may, at the
-Beneficiary’s option, be sold in one or more subsequent sale proceedings. The recordation of this Notice
-does not constitute an election to proceed against any given collateral, or to pursue any given remedy, to
-the exclusio</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>ocr_fallback;missing_owner</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221886</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221886.pdf</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260221886.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>is 150 5. Dobson</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>150 Dobson Road</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>85202:</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Maricopa</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>thereof</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>$1,932,500.00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>appointed herein qualifies as trustee of the Trust Deed in the trustee’s capacity as a</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2022083246</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>July 16, 2026</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>20260222380</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>N/TR SALE</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>ACCORDING TO THE DEED OF TRUST OR UPON INFORMATION SUPPLIED BY THE BENEFICIARY, THE
-FOLLOWING INFORMATION IS PROVIDED PURSUANT TO A.R.S. SECTION 33-808(C):
-Street address or identifiable location: 150 S. Dobson Road
-Mesa, AZ 85202
-A.P.N.: 134-33-0023
-Original Principal Balance: $1,932,500.00
-NAME AND ADDRESS OF ORIGINAL TRUSTOR (as shown on the Deed of Trust):
-JNRL Enterprises, LLC, an Arizona limited liability company
-150 S. Dobson Road
-Mesa, AZ 85202
-NAME AND ADDRESS OF BENEFICIARY (as of recording of Notice of Sale):
-Live Oak Banking Company
-1741 Tiburon Drive
-Wilmington, NC 28403
-20260222380
-TS#: Live Oak v JNRL Ent. Loan #: XX3485
-NOTICE OF TRUSTEE'S SALE
-The successor trustee appointed herein qualifies as trustee of the Trust Deed in the trustee’s capacity as a
-member of the Arizona State Bar as required by ARS Section 33-803, Subsection A(2). Name of Trustee's
-Regulator: Arizona State Bar Association
-NAME, ADDRESS &amp; TELEPHONE NUMBER OF TRUSTEE (as of recording of Notice of Sale)</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>ocr_fallback;missing_owner</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222380</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222380.pdf</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222380.pdf</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,6 +563,1287 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>20260219643</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260219643</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260219643.pdf</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>20260220010</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260220010</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260220010.pdf</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>20260220108</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260220108</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260220108.pdf</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>20260220458</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260220458</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260220458.pdf</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>20260220483</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260220483</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260220483.pdf</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>20260221099</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221099</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221099.pdf</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>20260221116</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221116</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221116.pdf</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>20260221131</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221131</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221131.pdf</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>20260221159</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221159</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221159.pdf</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>20260221277</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221277</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221277.pdf</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>20260221728</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221728</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221728.pdf</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>20260221835</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221835</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221835.pdf</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>20260221862</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221862</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221862.pdf</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>20260221869</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221869</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221869.pdf</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>20260221880</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221880</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221880.pdf</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>20260221886</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221886</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221886.pdf</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>20260222095</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222095</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222095.pdf</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>20260222178</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222178</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222178.pdf</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>20260222252</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222252</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222252.pdf</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>20260222297</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222297</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222297.pdf</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>20260222380</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222380</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222380.pdf</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,7 +589,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>20260219643</t>
+          <t>20260222588</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
@@ -614,12 +614,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260219643</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222588</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260219643.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222588.pdf</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -650,7 +650,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>20260220010</t>
+          <t>20260222606</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
@@ -675,12 +675,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260220010</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222606</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260220010.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222606.pdf</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -711,7 +711,7 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20260220108</t>
+          <t>20260222631</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
@@ -736,12 +736,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260220108</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222631</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260220108.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222631.pdf</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -772,7 +772,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>20260220458</t>
+          <t>20260222700</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
@@ -797,12 +797,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260220458</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222700</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260220458.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222700.pdf</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -833,17 +833,17 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>20260220483</t>
+          <t>20260222835</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>N/TR SALE</t>
+          <t>N/TR SALE+</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
@@ -858,12 +858,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260220483</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222835</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260220483.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222835.pdf</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -894,7 +894,7 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>20260221099</t>
+          <t>20260222909</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
@@ -919,12 +919,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221099</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222909</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221099.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222909.pdf</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -955,7 +955,7 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>20260221116</t>
+          <t>20260223068</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221116</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223068</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221116.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223068.pdf</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>20260221131</t>
+          <t>20260223111</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221131</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223111</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221131.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223111.pdf</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>20260221159</t>
+          <t>20260223127</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221159</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223127</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221159.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223127.pdf</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1138,7 +1138,7 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>20260221277</t>
+          <t>20260223286</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221277</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223286</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221277.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223286.pdf</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -1199,7 +1199,7 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>20260221728</t>
+          <t>20260223322</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221728</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223322</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221728.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223322.pdf</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>20260221835</t>
+          <t>20260223541</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221835</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223541</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221835.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223541.pdf</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -1321,7 +1321,7 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>20260221862</t>
+          <t>20260224183</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221862</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224183</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221862.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224183.pdf</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -1382,7 +1382,7 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>20260221869</t>
+          <t>20260224205</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221869</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224205</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221869.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224205.pdf</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -1443,7 +1443,7 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>20260221880</t>
+          <t>20260224218</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -1468,12 +1468,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221880</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224218</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221880.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224218.pdf</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -1504,7 +1504,7 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>20260221886</t>
+          <t>20260224386</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260221886</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224386</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260221886.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224386.pdf</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>20260222095</t>
+          <t>20260224598</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222095</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224598</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222095.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224598.pdf</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -1626,7 +1626,7 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>20260222178</t>
+          <t>20260224897</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222178</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224897</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222178.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224897.pdf</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -1687,7 +1687,7 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>20260222252</t>
+          <t>20260224899</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222252</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224899</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222252.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224899.pdf</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -1748,7 +1748,7 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
-          <t>20260222297</t>
+          <t>20260224933</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222297</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224933</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222297.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224933.pdf</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -1809,7 +1809,7 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>20260222380</t>
+          <t>20260224934</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -1834,15 +1834,564 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222380</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224934</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222380.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224934.pdf</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>20260224938</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224938</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224938.pdf</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>20260225129</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225129</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225129.pdf</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>20260225192</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225192</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225192.pdf</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>20260225194</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225194</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225194.pdf</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>20260225195</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225195</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225195.pdf</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>20260225265</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225265</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225265.pdf</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>20260225382</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225382</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225382.pdf</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>20260225528</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225528</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225528.pdf</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>20260225555</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225555</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225555.pdf</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -564,29 +564,77 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20220603286</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(S):</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>An</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4130 W NANCY LN</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>105-89-133</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>$250,000.00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>'s Sale</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2022060328</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>7/21/2026</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>20260222588</t>
@@ -602,14 +650,26 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>(s): SPS PLATINUM PROPERTIES, LLC, AN</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>LOT 114, LAS CASAS GRANDES, ACCORDING TO THE PLAT OF
+RECORD IN THE OFFICE OF THE COUNTY RECORDER OF MARICOPA
+COUNTY, ARIZONA, RECORDED IN BOOK 136 OF MAPS, PAGE 25
+AND PLAT OF CORRECTION RECORDED IN BOOK 138 OF MAPS,
+PAGE 2,</t>
+        </is>
+      </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -622,32 +682,96 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222588.pdf</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222588.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20240056798</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Peggy</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dated</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7730 Market Center Ave Suite 100</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>El Paso</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>79912</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15252 N 100TH STREET # 1146</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SCOTTSDALE</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85260</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>217-54-700</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>$ 630,000.00</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2024005679</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>April 13, 2026</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>20260222606</t>
@@ -663,14 +787,36 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>PEGGY LEE KNIGHT, TRUSTEE OF THE PEGGY LEE KNIGHT 1999 REVOCABLE TRUST DATED</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNIT 1146, VILLAGES NORTH PHASE III CONDOMINIUMS, A CONDOMINIUM AS CREATED BY
+THE CERTAIN DECLARATION RECORDED FEBRUARY 3, 1995, INRECORDER'S NO. 95-0065 120, RE-
+RECORDED FEBRUARY 16, 1995 IN RECORDER'S NO. 95-0087467, FIRST AMENDMENT RECORDED
+OCTOBER 27, 1995 IN RECORDER'S NO. 95-0659342, SECOND AMENDMENT RECORDED
+SEPTEMBER 17, 1996 IN RECORDER'S NO. 96-0657540, AND AS SHOWN ON PLAT OF SAID
+CONDOMINIUM RECORDED IN BOOK 420 OF MAPS, PAGE 7, RECORDS OF MARICOPA COUNTY,
+ARIZONA.
+TOGETHER WITH A PROPORTIONATE INTEREST IN THE COMMON AREAS AND FACILITIES IN
+SAID DECLARATION AND PLAT;
+EXCEPT ALL OIL, GAS, OTHER HYDROCARBON SUBSTANCES, HELIUM OR OTHER SUBSTANCES
+OF A GASEOUS NATURE, COAL, METALS, MINERALS, FOSSILS, FERTILIZER OF EVERY NAME
+AND DESCRIPTION, TOGETHER WITH ALL URANIUM, THORIUM OR ANY OTHER MINERAL
+WHICH IS OR MAY BE DETERMINED BY THE LAWS OF THE UNITED STATES, OR OF THIS STATE,
+OR DECISIONS OF COURT TO BE PECULIARLY ESSENTIAL TO THE PRODUCTION OF
+FISSIONABLE MATERIALS, WHETHER </t>
+        </is>
+      </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -683,32 +829,88 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222606.pdf</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222606.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20130557230</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>17100 Gillette Ave</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Irvine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>92614</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1036 E HIGHLAND AVENUE</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85014</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>155-11-018</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>101-1084974</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>. The purchaser at the sale, other than the Beneficiary to the extent of his</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>20260222631</t>
@@ -727,11 +929,11 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -744,10 +946,18 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222631.pdf</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222631.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20230480957</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -756,7 +966,11 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street, Phoenix, AZ 85003 on July 23, 2026 at 10:00 AM on said day.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -765,11 +979,31 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>503-51-109T3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>$444,795.00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2023048095</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>. The purchaser at the sale, other than the Beneficiary to the extent of his</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>20260222700</t>
@@ -786,13 +1020,17 @@
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>ATTACHED AS EXHIBIT "A"</t>
+        </is>
+      </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -805,14 +1043,34 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222700.pdf</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222700.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>’S</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Address:</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Avenue</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -826,11 +1084,31 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>135-33-586</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>$55,250,000</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>’s Name, Address, and Telephone Number: Jason D. Curry, Renaissance One</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>019-0625397</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>August 13, 2019</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>20260222835</t>
@@ -846,14 +1124,22 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>’s Stated Name and Address: Salt River Point TT, LLC, 777 Third Avenue</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>See attached Exhibit A</t>
+        </is>
+      </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_property_address</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -866,7 +1152,11 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222835.pdf</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222835.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -878,20 +1168,48 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2855 S Extension Rd Unit 247</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85210</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>$304,385</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2022069546</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>July 15, 2026</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>20260222909</t>
@@ -910,11 +1228,11 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -927,32 +1245,92 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222909.pdf</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222909.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20211316991</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>17100 Gillette Ave</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Irvine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>92614</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3037 N 69TH AVENUE</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85033</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>102-21-180</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>$294,566.00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2021131699</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>. The purchaser at the sale, other than the Beneficiary to the extent of his</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>20260223068</t>
@@ -969,13 +1347,18 @@
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>LOT 54, MARYVALE TERRACE NO. 49, ACCORDING TO BOOK 199 OF MAPS, PAGE 45, RECORDS
+OF MARICOPA COUNTY, ARIZONA.</t>
+        </is>
+      </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -988,32 +1371,84 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223068.pdf</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223068.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20220901360</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Margie</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Az</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>17 LOGS Legal Group LLP Ga. 2390 E. Camelback Road, Suite 130, PMB 1253 Phoenix, AZ 85016 (602) 222-5711 File # 26-030251 RFT</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1501 East Nielson Avenue</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85204</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>138-13-118</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>$100,000.00</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>(602) 222-5711</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>December 20, 2022</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>20260223111</t>
@@ -1029,14 +1464,23 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Margie C. Yates, an unmarried woman, 1501 East Nielson Avenue, Mesa, AZ</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>LOT 113, MESA HOMES, PER MAP RECORDED IN BOOK 57 OF MAPS, PAGE 38, IN THE OFFICE OF THE
+COUNTY RECORDER, MARICOPA COUNTY, ARIZONA.</t>
+        </is>
+      </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1049,19 +1493,47 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223111.pdf</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223111.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20230507420</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>17100 Gillette Ave</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Irvine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>92614</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street, Phoenix, AZ 85003 on July 23, 2026 at 10:00 AM on said day.</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1070,11 +1542,27 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>502-88-840</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>$322,200.00</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>2023050742</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>. The purchaser at the sale, other than the Beneficiary to the extent of his</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>20260223127</t>
@@ -1091,13 +1579,19 @@
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>LOT 263, OF SIERRA MONTANA PARCEL 14, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE
+OF THE COUNTY RECORDER OF MARICOPA COUNTY, ARIZONA, RECORDED IN BOOK 686 OF
+MAPS, PAGE 10.</t>
+        </is>
+      </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1110,32 +1604,92 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223127.pdf</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223127.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20240318293</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>17100 Gillette Ave</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Irvine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2614</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>22495 E STIRRUP ST</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>314-16-119</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>$766,550.00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2024031829</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>. The purchaser at the sale, other than the Beneficiary to the extent of his</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>20260223286</t>
@@ -1152,13 +1706,19 @@
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>LOT 119, OF MADERA PHASE 1A, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE OF THE
+COUNTY RECORDED OF MARICOPA COUNTY, ARIZONA RECORDED IN IN BOOK 1520 OF MAPS,
+PAGE 37</t>
+        </is>
+      </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1171,32 +1731,92 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223286.pdf</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223286.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20180303382</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>17100 Gillette Ave</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>irvine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>92614</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3832 N 86TH AVE</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85037</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>102-23-132</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>$82,500.00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2018030338</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>. The purchaser at the sale. other than the Beneficiary to the extent of his</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>20260223322</t>
@@ -1213,13 +1833,19 @@
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>LOT 121, OF ARIZONA HOMES, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE OF THE
+COUNTY RECORDER OF MARICOPA COUNTY, ARIZONA, RECORDED IN BOOK 137 OF MAPS, PAGE
+7.</t>
+        </is>
+      </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1232,32 +1858,80 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223322.pdf</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223322.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mary</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4525 N 66" St Unit 14</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5420 W Onyx Ave.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85302.</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>$250,000.00</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>022-0774491</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>July 15, 2026</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>20260223541</t>
@@ -1273,14 +1947,22 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mary Watola, a single woman, 4525 N 66" St Unit 14</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Exhibit “A”</t>
+        </is>
+      </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1293,15 +1975,35 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223541.pdf</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223541.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20220867985</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>(As</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Trust)</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ZBS Law, LLP 3550 N. Central Ave., Ste. 1190 Phoenix, Arizona 85012 SPACE ABOVE THIS LINE FOR RECORDERS USE TS#: 26-77660 Order #: 260050652-AZ-VOI</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -1314,11 +2016,31 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>220-21-417</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>$381,954.00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'S SALE</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2022086798</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>March 1, 2026</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr">
         <is>
           <t>20260224183</t>
@@ -1334,14 +2056,34 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>, in the office of the
+County Recorder of Maricopa County, Arizona, NOTICE! IF YOU BELIEVE THERE IS A DEFENSE TO
+THE TRUSTEE SALE OR IF YOU HAVE AN OBJECTION TO THE TRUSTEE SALE, YOU MUST FILE
+AN ACTION AND OBTAIN A COURT ORDER PURSUANT TO RULE 65, ARIZONA RULES OF CIVIL
+PROCEDURE, STOPPING THE SALE NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME OF
+THE LAST BUSINESS DAY BEFORE THE SCHEDULED DATE OF THE SALE, OR YOU MAY HAVE
+WAIVED ANY DEFENSES OR OBJECTIONS TO THE SALE. UNLESS YOU OBTAIN AN ORDER, THE
+SALE WILL BE FINAL AND WILL OCCUR at public auction to the highest bidder in the Courtyard, by the
+main entrance of the Superior Court Building, 201 West Jefferson, Phoenix, Arizona 85003, on 7/21/2026 at
+12:00 PM of said day:
+LOT 26, OF PARADISE VILLAGE II, ACCORDING TO BOOK 484 OF MAPS, PAGE 49 AND RE-
+RECORDED IN BOOK 495 OF MAPS, PAGE 3, RECORDS OF MARICOPA COUNTY, ARIZONA.
+Per A.R.S. Section 33-803 (A)(2) the successor trustee appointed here qualifies as a Trustee of the trust deed i</t>
+        </is>
+      </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_property_address</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1354,32 +2096,76 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224183.pdf</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224183.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Jerry</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Title No: 260189030-AZ-VOI</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>$302,421.00</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2021062196</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>July 23, 2026</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>20260224205</t>
@@ -1395,14 +2181,35 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jerry Beck, a single man</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Lot 79, of LAVEEN MEADOWS - PARCEL 3, according to the Plat of Record in the Office of the County Recorder
+of Maricopa County, Arizona, recorded in Book 729 of Maps, Page 40.
+The street address/location of the real property described above is purported to be:
+7350 W. Desert Lane
+Laveen, AZ 85339
+Tax Parcel No.: 300-01-899 4
+The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
+the street address and other common designation, if any, shown herein.
+Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
+possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
+interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
+thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts created by said Deed
+of Trust.
+(Notice of</t>
+        </is>
+      </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -1415,7 +2222,11 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224205.pdf</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224205.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1423,24 +2234,56 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Title No: 260201429-AZ-VOI</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>$104,000.00</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2021093457</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>July 30, 2026</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr">
         <is>
           <t>20260224218</t>
@@ -1457,13 +2300,29 @@
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Lot 518, of the Highlands at Arrowhead Ranch IV, according to the Plat of Record in the Office of the County
+Recorder of Maricopa County, Arizona, recorded in Book 419 of Maps, Page 40.
+The street address/location of the real property described above is purported to be:
+6619 W Kristal Way
+Glendale, AZ 85308
+Tax Parcel No.: 200-28-471 0
+The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
+the street address and other common designation, if any, shown herein.
+Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
+possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
+interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
+thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts created by said Deed
+of Trust</t>
+        </is>
+      </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -1476,7 +2335,11 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224218.pdf</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224218.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1488,20 +2351,52 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1737 E. Manhattan Dr. The street address is purported to be:</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tempe</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85282</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>133-37-259</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>$465,000.00</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2003000098</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>April 15, 2026</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>20260224386</t>
@@ -1518,13 +2413,19 @@
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Lot 577, TEMPE GARDENS UNIT FIVE, according to the plat of record in the office of the County
+Recorder of Maricopa County, Arizona in Book 120 of Maps, Page 22.
+The street address is purported to be: 1737 E. Manhattan Dr., Tempe, AZ 85282</t>
+        </is>
+      </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -1537,7 +2438,11 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224386.pdf</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224386.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1545,24 +2450,56 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>TIFFANY &amp; BOSCO, P.A. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona 85004 ee OO u-O Oo 0 ems Title No: 92723396</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1434 W Kerry Lane</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85027</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>$1,295,280.00</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>007-0195094</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>July 15, 2026</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>20260224598</t>
@@ -1579,13 +2516,30 @@
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lot 24, of MARLBOROUGH COUNTRY UNIT SIX, according to the Plat of Record in the Office of the County
+Recorder of Maricopa County, Arizona, recorded in Book 187 of Maps, Page 40.
+The street address/location of the real property described above is purported to be:
+1434 W Kerry Lane
+Phoenix, AZ 85027
+Tax Parcel No.: 209-23-024 0
+The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
+the street address and other common designation, if any, shown herein.
+Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
+possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
+interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
+thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts created by said Deed
+of Trust.
+(Notice </t>
+        </is>
+      </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -1598,7 +2552,11 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224598.pdf</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224598.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1606,24 +2564,56 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>85004 Title No: 22600371 RAY 22 TIFFANY &amp; BOSCO, P.A. Yo. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4931 E Sharon Dr</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85254</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>$117,930.00</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2023009805</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>July 15, 2026</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>20260224897</t>
@@ -1640,13 +2630,30 @@
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Lot 920, Sunburst Estates Two, according to the plat of record in the office of the County Recorder of Maricopa
+County, Arizona, recorded in Book 189 of Maps, Page 7.
+The street address/location of the real property described above is purported to be:
+4931 E Sharon Dr
+Scottsdale, AZ 85254-3527
+Tax Parcel No.: 167-05-388 0
+The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
+the street address and other common designation, if any, shown herein.
+Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
+possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
+interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
+thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts created by said Deed
+of Trust.
+(Notice of S</t>
+        </is>
+      </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -1659,32 +2666,76 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224897.pdf</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224897.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Antonio</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>85004 Title No: 22600368 Car 22 TIFFANY &amp; BOSCO, P.A. Yo. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6302 West Windsor Blvd.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>$167,200.00</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>2006167899</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>July 22, 2026</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>20260224899</t>
@@ -1700,14 +2751,36 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Antonio A. Rodriguez, Jr., an unmarried man</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Lot 68, of WEDGEWOOD PARK UNIT EIGHT, according to Book 134 of Maps, Page 39, records of Maricopa
+County, Arizona.
+More Correctly Described As:
+Lot 68, of WEDGEWOOD PARK UNIT 8, according to Book 134 of Maps, Page 39, records of Maricopa County,
+Arizona.
+The street address/location of the real property described above is purported to be:
+4817 West Almeria Road
+Phoenix, AZ 85035
+Tax Parcel No.: 103-20-587 6
+The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
+the street address and other common designation, if any, shown herein.
+Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
+possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
+interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
+thereon as proved in said Note, plus fees, charges and</t>
+        </is>
+      </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -1720,32 +2793,96 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224899.pdf</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224899.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sole</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Separate</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1850 North Central Avenue 22 TIFFANY &amp; BOSCO, P.A. Ga. Central Arts Plaza Twenty Fourth Floor</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>85004</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>2021088582</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>July 30, 2026</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>20260224933</t>
@@ -1761,14 +2898,33 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jaime G Lopez, a married man as his sole and separate property</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Lot 454, of WEST PHOENIX ESTATES UNIT FOUR AMENDED, according to the Plat of Record in the Office of
+the County Recorder of Maricopa County, Arizona, recorded in Book 129 of Maps, Page 46, of Official Records.
+The street address/location of the real property described above is purported to be:
+41121 W Montebcllo Ave
+Tonopah, AZ 85354
+Tax Parcel No.: 506-35-036 8
+The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
+the street address and other common designation, if any, shown herein.
+Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
+possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
+interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
+thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts cr</t>
+        </is>
+      </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -1781,7 +2937,11 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224933.pdf</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224933.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1789,24 +2949,68 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1850 North Central Avenue 22 TIFFANY &amp; BOSCO, P.A. Ga. Central Arts Plaza Twenty Fourth Floor</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>85004</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>302 E Mohave St</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85004</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>$262,350.00</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>2022052003</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>July 22, 2026</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>20260224934</t>
@@ -1825,11 +3029,11 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -1842,32 +3046,76 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224934.pdf</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224934.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>85004 Title No: 22600237 CARY 22 TIFFANY &amp; BOSCO, P.A. Ho: Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>$206,196.00</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>2018046746</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>August 6, 2026</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>20260224938</t>
@@ -1883,14 +3131,35 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jorge A Cornejo, an unmarried man</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lot 202, of RIATA WEST UNIT 1, according to the Plat of Record in the Office of the County Recorder of Maricopa
+County, Arizona, recorded in Book 842 of Maps, Page 16.
+The street address/location of the real property described above is purported to be:
+23976 W Pecan Road
+Buckeye, AZ, 85326
+Tax Parcel No.: 504-75-530 1
+The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
+the street address and other common designation, if any, shown herein.
+Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
+possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
+interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
+thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts created by said Deed
+of Trust.
+(Notice of Sale </t>
+        </is>
+      </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -1903,15 +3172,31 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224938.pdf</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224938.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>(As</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Trust)</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, LLC 1920 Old Tustin Ave. Santa Ana, California 92705 Phone: 949-427-2010 SPACE ABOVE THIS LINE FOR RECORDERS USE TS#: 26-19021 Loan #: ******1147 Order #: 260147405-AZ-VOI</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1924,11 +3209,31 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>137-32-272</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>$147,000.00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>'S SALE</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>949-427-2010</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>7/15/2008</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr">
         <is>
           <t>20260225129</t>
@@ -1944,14 +3249,30 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>LOT 166, ENCHANTED VILLAGE, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE OF
+THE COUNTY RECORDER OF MARICOPA COUNTY, ARIZONA, RECORDED IN BOOK 107 OF
+MAPS, PAGE 14.
+The successor trustee appointed herein qualifies as trustee of the Trust Deed in the trustee’s capacity as a
+member of the Arizona State Bar as required pursuant to ARS 33-803(A)(2).
+ACCORDING TO THE DEED OF TRUST OR UPON INFORMATION SUPPLIED BY THE BENEFICIARY,
+THE FOLLOWING INFORMATION IS PROVIDED PURSUANT TO A.R.S. SECTION 33-808(C):
+Street address or identifiable location: 1122 NORTH WELD CIRCLE
+MESA, Arizona 85203</t>
+        </is>
+      </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_property_address</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -1964,32 +3285,88 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225129.pdf</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225129.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20150019725</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>(S):</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ii</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Andria</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2778 NORTH 150TH LANE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85395</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>508-14-199</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>$353,100.00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>'s Sale</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>2015001972</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>7/22/2026</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr">
         <is>
           <t>20260225192</t>
@@ -2005,14 +3382,24 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>(s): TYRONE DANIEL WEST II AND ANDRIA</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>LOT 191, GOODYEAR PLANNED REGIONAL CENTER PARCEL 10,
+ACCORDING TO BOOK 648 OF MAPS, PAGE 15, RECORDS OF
+MARICOPA COUNTY, ARIZONA.</t>
+        </is>
+      </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -2025,32 +3412,88 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225192.pdf</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225192.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20211366018</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>(S):</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sole</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Separate</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2799 E BALSAM DR</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>CHANDLER</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85286</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>303-43-776</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>$455,000.00</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>SALE OR IF YOU HAVE AN OBJECTION TO THE TRUSTEE SALE, YOU MUST FILE AN</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>2021136601</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr">
         <is>
           <t>20260225194</t>
@@ -2066,14 +3509,26 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>(s): Ariel Carlos, a married man, as his sole and separate</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>LOT 96, OF ABRALEE MEADOW, ACCORDING TO THE PLAT OF
+RECORD IN THE OFFICE OF THE COUNTY RECORDER OF MARICOPA
+COUNTY, ARIZONA, RECORDED IN BOOK 652 OF MAPS, PAGE 23
+AND CERTIFICATE OF CORRECTION RECORDED IN RECORDING NO.
+2004-1261016</t>
+        </is>
+      </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -2086,32 +3541,96 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225194.pdf</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225194.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20250315111</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>(S):</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Teresa</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Hernandez-Brent</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Quality Loan Service Corporation 2763 Camino Del Rio South San Diego, CA 92108 “TS No.. AZ-26-1048525-AB~—~—~C~&lt;“is—sts~s~*st::OC(CS”:*:*:*:CCSCS*CSS pace above this fine for recorders use</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3636 W LAREDO ST</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>CHANDLER</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85226</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>301-64-666</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>$185,739.00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>'s Sale</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>012-0812180</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr">
         <is>
           <t>20260225195</t>
@@ -2127,14 +3646,25 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>(s): Paul A. Brent and Teresa D. Hernandez-Brent</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Lot 210, of Copperfield Estates, according to the plat of record in the Office of
+the County Recorder of Maricopa County, Arizona, recorded in Book 272 of
+Maps, Page 11 and Affidavit of Correction recorded in Instrument No. 84-
+412077. :</t>
+        </is>
+      </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -2147,15 +3677,31 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225195.pdf</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225195.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>(As</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Trust)</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, LLC 1920 Old Tustin Ave. Santa Ana, California 92705 Phone: 949-427-2010 SPACE ABOVE THIS LINE FOR RECORDERS USE TS#: 26-18971 Loan #: ******9988 Order #: 260141702-AZ-VOI</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2168,11 +3714,31 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>101-57-175</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>$373,117.00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>'S SALE</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>949-427-2010</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>10/28/2021</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr">
         <is>
           <t>20260225265</t>
@@ -2188,14 +3754,30 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>LOT 175, OF 91ST AVENUE AND LOWER BUCKEYE ROAD, ACCORDING TO THE PLAT OF
+RECORD IN THE OFFICE OF THE COUNTY RECORDER OF MARICOPA COUNTY, ARIZONA,
+RECORDED IN BOOK 648 OF MAPS, PAGE 34.
+The successor trustee appointed herein qualifies as trustee of the Trust Deed in the trustee’s capacity as a
+member of the Arizona State Bar as required pursuant to ARS 33-803(A)(2).
+ACCORDING TO THE DEED OF TRUST OR UPON INFORMATION SUPPLIED BY THE BENEFICIARY,
+THE FOLLOWING INFORMATION IS PROVIDED PURSUANT TO A.R.S. SECTION 33-808(C):
+Street address or identifiable location: 9018 W HILTON AVE
+TOLLESON, Arizona 85353</t>
+        </is>
+      </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_property_address</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -2208,32 +3790,88 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225265.pdf</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225265.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20220478953</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>17100 Gillette Ave</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Irvine</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>92614</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>25836 N 43RD PL</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85050-8930</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>212-09-405</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>$596,000.00</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2022047895</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>. The purchaser at the</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr">
         <is>
           <t>20260225382</t>
@@ -2250,13 +3888,24 @@
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>LOT 32, OF TATUM HIGHLANDS PARCEL 19, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE
+OF THE COUNTY RECORDER OF MARICOPA COUNTY, ARIZONA, RECORDED IN BOOK 392 OF
+MAPS, PAGE 15;EXCEPT ALL OIL, GAS, OTHER HYDROCARBON SUBSTANCES, HELIUM OR OTHER
+SUBSTANCES OF A GASEOUS NATURE, COAL, METALS, MINERALS, FOSSILS, FERTILIZER OF
+EVERY NAME AND DESCRIPTION, AND EXCEPT ALL MATERIAL WHICH MAY BE ESSENTIAL TO THE
+PRODUCTION OF FISSIONABLE MATERIALS AS RESERVED PURSUANT TO RECORDED
+INSTRUMENT IN FAVOR OF THE UNITED STATES OF AMERICA OR THE STATE OF ARIZONA,
+PURSUANT TO THE PROVISIONS OF ARIZONA REVISED STATUTES 37-231.</t>
+        </is>
+      </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -2269,32 +3918,108 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225382.pdf</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225382.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20070149857</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>(S):</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tany!</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Colette</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ebail</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Unofficial 2~Document 17 Ho:</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>South San Diego</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>92108</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>201 West Jefferson</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>313-04-589</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>$550,800.00</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>'s Sale</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>2007014985</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Sale</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr">
         <is>
           <t>20260225528</t>
@@ -2310,14 +4035,28 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>(s): CORNELIUS E TANY! AND COLETTE T EBAIL</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Purported Street Address:
+7/22/2026 at 12:00PM
+In the courtyard by the main entrance of the Superior Court Building,
+located at 201 West Jefferson, Phoenix, AZ 85003
+LOT 2, SEVILLE 21, ACCORDING TO BOOK 644 OF MAPS, PAGE 34,
+RECORDS OF MARICOPA COUNTY, ARIZONA,
+7110 SOUTH CHAMPAGNE WAY, GILBERT, AZ, 85297</t>
+        </is>
+      </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -2330,32 +4069,84 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225528.pdf</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225528.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20211006457</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>(S):</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>7264 N 128TH AVE</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85307</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>501-53-449</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>$392,950.00</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>'s Sale</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>2021100645</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>8/6/2026</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr">
         <is>
           <t>20260225555</t>
@@ -2371,14 +4162,24 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>(s): ROBERT L HENDERSON JR, SINGLE MAN</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>LOT 54, LUKE LANDING, ACCORDING TO THE FINAL PLAT
+RECORDED IN BOOK 1462 MAPS, PAGE 23, RECORDS OF MARICOPA
+COUNTY, ARIZONA.</t>
+        </is>
+      </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -2391,7 +4192,11 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225555.pdf</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225555.pdf</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(S):</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>An</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -622,7 +622,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>'s Sale</t>
+          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>(s): SPS PLATINUM PROPERTIES, LLC, AN</t>
+          <t>ARIZONA LIMITED LIABILIFY COMPANY</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -761,7 +761,11 @@
           <t>$ 630,000.00</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Unofficial Document</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>2024005679</t>
@@ -812,11 +816,11 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -841,10 +845,26 @@
           <t>20130557230</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Donald</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Echols</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Colleen</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Wife</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>17100 Gillette Ave</t>
@@ -900,7 +920,11 @@
           <t>$285,000.00</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>17100 Gillette Ave</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>101-1084974</t>
@@ -926,14 +950,18 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>DONALD J. ECHOLS AND COLLEEN A. ECHOLS, HUSBAND AND WIFE</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -958,8 +986,16 @@
           <t>20230480957</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -968,12 +1004,24 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street, Phoenix, AZ 85003 on July 23, 2026 at 10:00 AM on said day.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -991,7 +1039,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1019,18 +1067,22 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>MASON BODROG, AN UNMARRIED MAN</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>ATTACHED AS EXHIBIT "A"</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1053,22 +1105,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>’S</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Address:</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Avenue</t>
+          <t>Seiden</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1096,7 +1148,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>’s Name, Address, and Telephone Number: Jason D. Curry, Renaissance One</t>
+          <t>Two North Central Avenue, Suite 600, Phoenix, Arizona 85004, Jason.Curry@quarles.com,</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1126,7 +1178,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>’s Stated Name and Address: Salt River Point TT, LLC, 777 Third Avenue</t>
+          <t>Floor 25, New York, NY 10017 c/o Bradley Seiden</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1160,8 +1212,16 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2855</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>85210</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -1199,7 +1259,11 @@
           <t>$304,385</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>PennyMac Loan Services, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>2022069546</t>
@@ -1225,14 +1289,18 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2855 S Extension Rd Unit 247, Mesa, AZ 85210</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1257,10 +1325,26 @@
           <t>20211316991</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Alexis</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Iyoana</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>An</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>17100 Gillette Ave</t>
@@ -1318,7 +1402,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1346,7 +1430,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>ALEXIS M JAUREGU! RODRIGUEZ, AN UNMARRIED MAN, AND IYOANA G CHAVEZ, AN</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>LOT 54, MARYVALE TERRACE NO. 49, ACCORDING TO BOOK 199 OF MAPS, PAGE 45, RECORDS
@@ -1354,11 +1442,11 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1383,21 +1471,18 @@
           <t>20220901360</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Margie</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Az</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17 LOGS Legal Group LLP Ga. 2390 E. Camelback Road, Suite 130, PMB 1253 Phoenix, AZ 85016 (602) 222-5711 File # 26-030251 RFT</t>
+          <t>17
+LOGS Legal Group LLP Ga.
+2390 E. Camelback Road, Suite 130, PMB 1253
+Phoenix, AZ 85016
+(602) 222-5711
+File # 26-030251 RFT</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1438,7 +1523,11 @@
           <t>$100,000.00</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1253, Phoenix, AZ 85016, (602) 222-5711</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>(602) 222-5711</t>
@@ -1464,11 +1553,7 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Margie C. Yates, an unmarried woman, 1501 East Nielson Avenue, Mesa, AZ</t>
-        </is>
-      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>LOT 113, MESA HOMES, PER MAP RECORDED IN BOOK 57 OF MAPS, PAGE 38, IN THE OFFICE OF THE
@@ -1476,11 +1561,11 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback;missing_owner</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1505,10 +1590,26 @@
           <t>20230507420</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Aprilyn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Woman</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>17100 Gillette Ave</t>
@@ -1531,12 +1632,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street, Phoenix, AZ 85003 on July 23, 2026 at 10:00 AM on said day.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>201 W. Jefferson Street</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1552,7 +1665,11 @@
           <t>$322,200.00</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>17100 Gillette Ave</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>2023050742</t>
@@ -1578,7 +1695,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>LOGAN HAINLEN, AN UNMARRIED MAN, AND APRILYN STREETY, AN UNMARRIED WOMAN</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>LOT 263, OF SIERRA MONTANA PARCEL 14, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE
@@ -1587,11 +1708,11 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1616,10 +1737,26 @@
           <t>20240318293</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Parkinson</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Alexis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Wife</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>17100 Gillette Ave</t>
@@ -1677,7 +1814,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1705,7 +1842,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>JOSEPH PARKINSON AND ALEXIS PARKINSON, HUSBAND AND WIFE</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>LOT 119, OF MADERA PHASE 1A, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE OF THE
@@ -1714,11 +1855,11 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,8 +1884,16 @@
           <t>20180303382</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Man</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
@@ -1804,7 +1953,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1832,7 +1981,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>ROBERTO GAMINO, A SINGLE MAN</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>LOT 121, OF ARIZONA HOMES, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE OF THE
@@ -1841,11 +1994,11 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1868,12 +2021,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Scottsdale,</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>85251.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1921,7 +2074,11 @@
           <t>$250,000.00</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>TS 26-076</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>022-0774491</t>
@@ -1949,7 +2106,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Mary Watola, a single woman, 4525 N 66" St Unit 14</t>
+          <t>Scottsdale, AZ 85251.</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -1958,11 +2115,11 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2001,7 +2158,12 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBS Law, LLP 3550 N. Central Ave., Ste. 1190 Phoenix, Arizona 85012 SPACE ABOVE THIS LINE FOR RECORDERS USE TS#: 26-77660 Order #: 260050652-AZ-VOI</t>
+          <t>ZBS Law, LLP
+3550 N. Central Ave., Ste. 1190
+Phoenix, Arizona 85012
+SPACE ABOVE THIS LINE FOR RECORDERS USE
+TS#: 26-77660
+Order #: 260050652-AZ-VOI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2026,11 +2188,7 @@
           <t>$381,954.00</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>'S SALE</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>2022086798</t>
@@ -2079,11 +2237,11 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address</t>
+          <t>ocr_fallback;missing_property_address;missing_trustee</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2106,12 +2264,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jerry</t>
+          <t>7350</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Man</t>
+          <t>85339</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2155,7 +2313,11 @@
           <t>$302,421.00</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>2021062196</t>
@@ -2183,7 +2345,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Jerry Beck, a single man</t>
+          <t>7350 W. Desert Lane, Laveen, AZ 85339</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2205,11 +2367,11 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,8 +2392,16 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6619</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
@@ -2273,7 +2443,11 @@
           <t>$104,000.00</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>V.LP. Mortgage, Inc. Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>2021093457</t>
@@ -2299,7 +2473,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>6619 W Kristal Way, Glendale, AZ 85308</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
           <t>Lot 518, of the Highlands at Arrowhead Ranch IV, according to the Plat of Record in the Office of the County
@@ -2318,11 +2496,11 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,8 +2521,16 @@
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rowland</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>91748</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -2386,7 +2572,11 @@
           <t>$465,000.00</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Acct No. 20030000983297 SFS No. 604178</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>2003000098</t>
@@ -2412,7 +2602,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rowland Heights, CA 91748</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
           <t>Lot 577, TEMPE GARDENS UNIT FIVE, according to the plat of record in the office of the County
@@ -2421,11 +2615,11 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2446,13 +2640,27 @@
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1434</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>85027</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TIFFANY &amp; BOSCO, P.A. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona 85004 ee OO u-O Oo 0 ems Title No: 92723396</t>
+          <t>TIFFANY &amp; BOSCO, P.A.
+Central Arts Plaza
+Twenty Fourth Floor
+1850 North Central Avenue
+Phoenix, Arizona 85004
+ee OO u-O Oo 0 ems
+Title No: 92723396</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2489,7 +2697,11 @@
           <t>$1,295,280.00</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Bank of America, N.A Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>007-0195094</t>
@@ -2515,7 +2727,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1434 W Kerry Lane, Phoenix, Arizona 85027</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t xml:space="preserve">Lot 24, of MARLBOROUGH COUNTRY UNIT SIX, according to the Plat of Record in the Office of the County
@@ -2535,11 +2751,11 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2560,13 +2776,27 @@
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4931</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>85254</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>85004 Title No: 22600371 RAY 22 TIFFANY &amp; BOSCO, P.A. Yo. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
+          <t>22
+TIFFANY &amp; BOSCO, P.A. Yo.
+Central Arts Plaza
+Twenty Fourth Floor
+1850 North Central Avenue
+Phoenix, Arizona 85004
+Title No: 22600371 RAY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2603,7 +2833,11 @@
           <t>$117,930.00</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Solera National Bank Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>2023009805</t>
@@ -2629,7 +2863,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>4931 E Sharon Dr, Scottsdale, AZ 85254</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>Lot 920, Sunburst Estates Two, according to the plat of record in the office of the County Recorder of Maricopa
@@ -2649,11 +2887,11 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2676,19 +2914,25 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Man</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>85004 Title No: 22600368 Car 22 TIFFANY &amp; BOSCO, P.A. Yo. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
+          <t>22
+TIFFANY &amp; BOSCO, P.A. Yo.
+Central Arts Plaza
+Twenty Fourth Floor
+1850 North Central Avenue
+Phoenix, Arizona 85004
+Title No: 22600368 Car</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2725,7 +2969,11 @@
           <t>$167,200.00</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>2006167899</t>
@@ -2753,7 +3001,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Antonio A. Rodriguez, Jr., an unmarried man</t>
+          <t>6302 West Windsor Blvd., Glendale, AZ 85301</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2776,11 +3024,11 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2803,27 +3051,19 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jaime</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sole</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Separate</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
+          <t>85354</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue 22 TIFFANY &amp; BOSCO, P.A. Ga. Central Arts Plaza Twenty Fourth Floor</t>
+          <t>1850 North Central Avenue</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2872,7 +3112,11 @@
           <t>$285,000.00</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>2021088582</t>
@@ -2900,7 +3144,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Jaime G Lopez, a married man as his sole and separate property</t>
+          <t>41121 W Montebello Ave, Tonopah, Arizona 85354</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2920,11 +3164,11 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2945,13 +3189,21 @@
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>85004</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue 22 TIFFANY &amp; BOSCO, P.A. Ga. Central Arts Plaza Twenty Fourth Floor</t>
+          <t>1850 North Central Avenue</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3000,7 +3252,11 @@
           <t>$262,350.00</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Bell Bank Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>2022052003</t>
@@ -3026,14 +3282,18 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>302 E Mohave St, Phoenix, AZ 85004</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3056,19 +3316,25 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Man</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>85004 Title No: 22600237 CARY 22 TIFFANY &amp; BOSCO, P.A. Ho: Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
+          <t>22
+TIFFANY &amp; BOSCO, P.A. Ho:
+Central Arts Plaza ‘
+Twenty Fourth Floor
+1850 North Central Avenue
+Phoenix, Arizona 85004
+Title No: 22600237 CARY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -3105,7 +3371,11 @@
           <t>$206,196.00</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>2018046746</t>
@@ -3133,7 +3403,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Jorge A Cornejo, an unmarried man</t>
+          <t>23976 W Pecan Road, Buckeye, AZ 85326</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3155,11 +3425,11 @@
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3194,7 +3464,12 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Prestige Default Services, LLC 1920 Old Tustin Ave. Santa Ana, California 92705 Phone: 949-427-2010 SPACE ABOVE THIS LINE FOR RECORDERS USE TS#: 26-19021 Loan #: ******1147 Order #: 260147405-AZ-VOI</t>
+          <t>Prestige Default Services, LLC
+1920 Old Tustin Ave.
+Santa Ana, California 92705
+Phone: 949-427-2010
+SPACE ABOVE THIS LINE FOR RECORDERS USE
+TS#: 26-19021 Loan #: ******1147 Order #: 260147405-AZ-VOI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -3219,11 +3494,7 @@
           <t>$147,000.00</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>'S SALE</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>949-427-2010</t>
@@ -3268,11 +3539,11 @@
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address</t>
+          <t>ocr_fallback;missing_property_address;missing_trustee</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3299,20 +3570,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>(S):</t>
+          <t>Elania</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ii</t>
+          <t>Husband</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Andria</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>Wife,</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>As</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -3354,7 +3629,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>'s Sale</t>
+          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3384,7 +3659,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>(s): TYRONE DANIEL WEST II AND ANDRIA</t>
+          <t>ELANIA WEST, HUSBAND AND WIFE, AS</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3426,19 +3701,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>(S):</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sole</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Separate</t>
-        </is>
-      </c>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -3481,7 +3748,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>SALE OR IF YOU HAVE AN OBJECTION TO THE TRUSTEE SALE, YOU MUST FILE AN</t>
+          <t>ACTION AND OBTAIN A COURT ORDER PURSUANT TO RULE 65, ARIZONA RULES OF CIVIL</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3511,7 +3778,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>(s): Ariel Carlos, a married man, as his sole and separate</t>
+          <t>property</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3555,27 +3822,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>(S):</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Brent</t>
-        </is>
-      </c>
+          <t>Husband</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Teresa</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Hernandez-Brent</t>
-        </is>
-      </c>
+          <t>Wife</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Quality Loan Service Corporation 2763 Camino Del Rio South San Diego, CA 92108 “TS No.. AZ-26-1048525-AB~—~—~C~&lt;“is—sts~s~*st::OC(CS”:*:*:*:CCSCS*CSS pace above this fine for recorders use</t>
+          <t>Quality Loan Service Corporation
+2763 Camino Del Rio South
+San Diego, CA 92108
+“TS No.. AZ-26-1048525-AB~—~—~C~&lt;“is—sts~s~*st::OC(CS”:*:*:*:CCSCS*CSS pace above this fine for recorders use</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3618,7 +3880,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>'s Sale</t>
+          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3648,7 +3910,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>(s): Paul A. Brent and Teresa D. Hernandez-Brent</t>
+          <t>husband and wife</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3699,7 +3961,12 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Prestige Default Services, LLC 1920 Old Tustin Ave. Santa Ana, California 92705 Phone: 949-427-2010 SPACE ABOVE THIS LINE FOR RECORDERS USE TS#: 26-18971 Loan #: ******9988 Order #: 260141702-AZ-VOI</t>
+          <t>Prestige Default Services, LLC
+1920 Old Tustin Ave.
+Santa Ana, California 92705
+Phone: 949-427-2010
+SPACE ABOVE THIS LINE FOR RECORDERS USE
+TS#: 26-18971 Loan #: ******9988 Order #: 260141702-AZ-VOI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3724,11 +3991,7 @@
           <t>$373,117.00</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>'S SALE</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>949-427-2010</t>
@@ -3773,11 +4036,11 @@
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address</t>
+          <t>ocr_fallback;missing_property_address;missing_trustee</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3802,10 +4065,26 @@
           <t>20220478953</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Serena</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Shao</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>With</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>17100 Gillette Ave</t>
@@ -3861,7 +4140,11 @@
           <t>$596,000.00</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>17100 Gillette Ave</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>2022047895</t>
@@ -3887,7 +4170,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>SERENA SHAO AND SAMUEL TANG, WIFE AND HUSBAND AS COMMUNITY PROPERTY WITH</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr">
         <is>
           <t>LOT 32, OF TATUM HIGHLANDS PARCEL 19, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE
@@ -3901,11 +4188,11 @@
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3932,32 +4219,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>(S):</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Tany!</t>
-        </is>
-      </c>
+          <t>Husband</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Colette</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Ebail</t>
-        </is>
-      </c>
+          <t>Wife</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Unofficial 2~Document 17 Ho:</t>
+          <t>Unofficial
+ 2~Document
+ 17
+ Ho:</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>South San Diego</t>
+          <t>South
+ San Diego</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4007,7 +4290,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>'s Sale</t>
+          <t>Recorder of MARICOPA County, Arizona. NOTICE! IF YOU BELEEVE THERE IS A DEFENSE TO THE</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -4037,7 +4320,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>(s): CORNELIUS E TANY! AND COLETTE T EBAIL</t>
+          <t>HUSBAND AND WIFE</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -4083,12 +4366,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>(S):</t>
+          <t>14145</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Man</t>
+          <t>Az</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -4134,7 +4417,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>'s Sale</t>
+          <t>, 2763 Camino Dei Rio South, San Diego, CA 92108</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -4164,7 +4447,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>(s): ROBERT L HENDERSON JR, SINGLE MAN</t>
+          <t>14145 N 92ND ST UNIT 1188, SCOTTSDALE, AZ</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -571,12 +571,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>(S):</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Company</t>
+          <t>An</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -622,7 +622,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
+          <t>'s Sale</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>ARIZONA LIMITED LIABILIFY COMPANY</t>
+          <t>(s): SPS PLATINUM PROPERTIES, LLC, AN</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -761,11 +761,7 @@
           <t>$ 630,000.00</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Unofficial Document</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>2024005679</t>
@@ -816,11 +812,11 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -845,26 +841,10 @@
           <t>20130557230</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Donald</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Echols</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Colleen</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>17100 Gillette Ave</t>
@@ -920,11 +900,7 @@
           <t>$285,000.00</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>101-1084974</t>
@@ -950,18 +926,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>DONALD J. ECHOLS AND COLLEEN A. ECHOLS, HUSBAND AND WIFE</t>
-        </is>
-      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,16 +958,8 @@
           <t>20230480957</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Mason</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -1004,24 +968,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+          <t>201 W. Jefferson Street, Phoenix, AZ 85003 on July 23, 2026 at 10:00 AM on said day.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1037,11 +989,7 @@
           <t>$444,795.00</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>2023048095</t>
@@ -1067,22 +1015,18 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>MASON BODROG, AN UNMARRIED MAN</t>
-        </is>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>ATTACHED AS EXHIBIT "A"</t>
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,22 +1049,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Floor</t>
+          <t>’S</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Address:</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Seiden</t>
+          <t>Avenue</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -1148,7 +1092,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Two North Central Avenue, Suite 600, Phoenix, Arizona 85004, Jason.Curry@quarles.com,</t>
+          <t>’s Name, Address, and Telephone Number: Jason D. Curry, Renaissance One</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1178,7 +1122,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Floor 25, New York, NY 10017 c/o Bradley Seiden</t>
+          <t>’s Stated Name and Address: Salt River Point TT, LLC, 777 Third Avenue</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1212,42 +1156,18 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>85210</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2855 S Extension Rd Unit 247</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>85210</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1259,11 +1179,7 @@
           <t>$304,385</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>PennyMac Loan Services, LLC Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>2022069546</t>
@@ -1289,18 +1205,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>2855 S Extension Rd Unit 247, Mesa, AZ 85210</t>
-        </is>
-      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_property_address;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,26 +1237,10 @@
           <t>20211316991</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Alexis</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Iyoana</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>An</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>17100 Gillette Ave</t>
@@ -1400,11 +1296,7 @@
           <t>$294,566.00</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>2021131699</t>
@@ -1430,11 +1322,7 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>ALEXIS M JAUREGU! RODRIGUEZ, AN UNMARRIED MAN, AND IYOANA G CHAVEZ, AN</t>
-        </is>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>LOT 54, MARYVALE TERRACE NO. 49, ACCORDING TO BOOK 199 OF MAPS, PAGE 45, RECORDS
@@ -1442,11 +1330,11 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,20 +1359,19 @@
           <t>20220901360</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Margie</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Az</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>17
-LOGS Legal Group LLP Ga.
-2390 E. Camelback Road, Suite 130, PMB 1253
-Phoenix, AZ 85016
-(602) 222-5711
-File # 26-030251 RFT</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -1523,11 +1410,7 @@
           <t>$100,000.00</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1253, Phoenix, AZ 85016, (602) 222-5711</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>(602) 222-5711</t>
@@ -1553,7 +1436,11 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Margie C. Yates, an unmarried woman, 1501 East Nielson Avenue, Mesa, AZ</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>LOT 113, MESA HOMES, PER MAP RECORDED IN BOOK 57 OF MAPS, PAGE 38, IN THE OFFICE OF THE
@@ -1561,11 +1448,11 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,26 +1477,10 @@
           <t>20230507420</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Logan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Aprilyn</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Woman</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>17100 Gillette Ave</t>
@@ -1632,24 +1503,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+          <t>201 W. Jefferson Street, Phoenix, AZ 85003 on July 23, 2026 at 10:00 AM on said day.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1665,11 +1524,7 @@
           <t>$322,200.00</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>2023050742</t>
@@ -1695,11 +1550,7 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>LOGAN HAINLEN, AN UNMARRIED MAN, AND APRILYN STREETY, AN UNMARRIED WOMAN</t>
-        </is>
-      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>LOT 263, OF SIERRA MONTANA PARCEL 14, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE
@@ -1708,11 +1559,11 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1737,26 +1588,10 @@
           <t>20240318293</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Parkinson</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Alexis</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Wife</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>17100 Gillette Ave</t>
@@ -1812,11 +1647,7 @@
           <t>$766,550.00</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>2024031829</t>
@@ -1842,11 +1673,7 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>JOSEPH PARKINSON AND ALEXIS PARKINSON, HUSBAND AND WIFE</t>
-        </is>
-      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>LOT 119, OF MADERA PHASE 1A, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE OF THE
@@ -1855,11 +1682,11 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1884,16 +1711,8 @@
           <t>20180303382</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Roberto</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
@@ -1951,11 +1770,7 @@
           <t>$82,500.00</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>2018030338</t>
@@ -1981,11 +1796,7 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>ROBERTO GAMINO, A SINGLE MAN</t>
-        </is>
-      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>LOT 121, OF ARIZONA HOMES, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE OF THE
@@ -1994,11 +1805,11 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2021,12 +1832,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Scottsdale,</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>85251.</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2074,11 +1885,7 @@
           <t>$250,000.00</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>TS 26-076</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>022-0774491</t>
@@ -2106,7 +1913,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ 85251.</t>
+          <t>Mary Watola, a single woman, 4525 N 66" St Unit 14</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2115,11 +1922,11 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2156,16 +1963,7 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>ZBS Law, LLP
-3550 N. Central Ave., Ste. 1190
-Phoenix, Arizona 85012
-SPACE ABOVE THIS LINE FOR RECORDERS USE
-TS#: 26-77660
-Order #: 260050652-AZ-VOI</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -2188,7 +1986,11 @@
           <t>$381,954.00</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>'S SALE</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>2022086798</t>
@@ -2237,11 +2039,11 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address;missing_trustee</t>
+          <t>ocr_fallback;missing_property_address</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2264,12 +2066,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>Jerry</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>85339</t>
+          <t>Man</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2313,11 +2115,7 @@
           <t>$302,421.00</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>2021062196</t>
@@ -2345,7 +2143,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>7350 W. Desert Lane, Laveen, AZ 85339</t>
+          <t>Jerry Beck, a single man</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2367,11 +2165,11 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2392,16 +2190,8 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>6619</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>85308</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
@@ -2443,11 +2233,7 @@
           <t>$104,000.00</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>V.LP. Mortgage, Inc. Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>2021093457</t>
@@ -2473,11 +2259,7 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>6619 W Kristal Way, Glendale, AZ 85308</t>
-        </is>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>Lot 518, of the Highlands at Arrowhead Ranch IV, according to the Plat of Record in the Office of the County
@@ -2496,11 +2278,11 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2521,16 +2303,8 @@
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Rowland</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>91748</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -2572,11 +2346,7 @@
           <t>$465,000.00</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Acct No. 20030000983297 SFS No. 604178</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>2003000098</t>
@@ -2602,11 +2372,7 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Rowland Heights, CA 91748</t>
-        </is>
-      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>Lot 577, TEMPE GARDENS UNIT FIVE, according to the plat of record in the office of the County
@@ -2615,11 +2381,11 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2640,27 +2406,13 @@
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1434</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>85027</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>TIFFANY &amp; BOSCO, P.A.
-Central Arts Plaza
-Twenty Fourth Floor
-1850 North Central Avenue
-Phoenix, Arizona 85004
-ee OO u-O Oo 0 ems
-Title No: 92723396</t>
+          <t>TIFFANY &amp; BOSCO, P.A. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona 85004 ee OO u-O Oo 0 ems Title No: 92723396</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2697,11 +2449,7 @@
           <t>$1,295,280.00</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Bank of America, N.A Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>007-0195094</t>
@@ -2727,11 +2475,7 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>1434 W Kerry Lane, Phoenix, Arizona 85027</t>
-        </is>
-      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
           <t xml:space="preserve">Lot 24, of MARLBOROUGH COUNTRY UNIT SIX, according to the Plat of Record in the Office of the County
@@ -2751,11 +2495,11 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2776,27 +2520,13 @@
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>4931</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>85254</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>22
-TIFFANY &amp; BOSCO, P.A. Yo.
-Central Arts Plaza
-Twenty Fourth Floor
-1850 North Central Avenue
-Phoenix, Arizona 85004
-Title No: 22600371 RAY</t>
+          <t>85004 Title No: 22600371 RAY 22 TIFFANY &amp; BOSCO, P.A. Yo. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2833,11 +2563,7 @@
           <t>$117,930.00</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Solera National Bank Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>2023009805</t>
@@ -2863,11 +2589,7 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>4931 E Sharon Dr, Scottsdale, AZ 85254</t>
-        </is>
-      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
           <t>Lot 920, Sunburst Estates Two, according to the plat of record in the office of the County Recorder of Maricopa
@@ -2887,11 +2609,11 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2914,25 +2636,19 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>85301</t>
+          <t>Man</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>22
-TIFFANY &amp; BOSCO, P.A. Yo.
-Central Arts Plaza
-Twenty Fourth Floor
-1850 North Central Avenue
-Phoenix, Arizona 85004
-Title No: 22600368 Car</t>
+          <t>85004 Title No: 22600368 Car 22 TIFFANY &amp; BOSCO, P.A. Yo. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2969,11 +2685,7 @@
           <t>$167,200.00</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>2006167899</t>
@@ -3001,7 +2713,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>6302 West Windsor Blvd., Glendale, AZ 85301</t>
+          <t>Antonio A. Rodriguez, Jr., an unmarried man</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3024,11 +2736,11 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3051,19 +2763,27 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>41121</t>
+          <t>Jaime</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>85354</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+          <t>Sole</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Separate</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue</t>
+          <t>1850 North Central Avenue 22 TIFFANY &amp; BOSCO, P.A. Ga. Central Arts Plaza Twenty Fourth Floor</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3112,11 +2832,7 @@
           <t>$285,000.00</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>U.S. Bank National Association Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>2021088582</t>
@@ -3144,7 +2860,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>41121 W Montebello Ave, Tonopah, Arizona 85354</t>
+          <t>Jaime G Lopez, a married man as his sole and separate property</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -3164,11 +2880,11 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3189,21 +2905,13 @@
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>85004</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue</t>
+          <t>1850 North Central Avenue 22 TIFFANY &amp; BOSCO, P.A. Ga. Central Arts Plaza Twenty Fourth Floor</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3252,11 +2960,7 @@
           <t>$262,350.00</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Bell Bank Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>2022052003</t>
@@ -3282,18 +2986,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>302 E Mohave St, Phoenix, AZ 85004</t>
-        </is>
-      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3316,25 +3016,19 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>23976</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>85326</t>
+          <t>Man</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>22
-TIFFANY &amp; BOSCO, P.A. Ho:
-Central Arts Plaza ‘
-Twenty Fourth Floor
-1850 North Central Avenue
-Phoenix, Arizona 85004
-Title No: 22600237 CARY</t>
+          <t>85004 Title No: 22600237 CARY 22 TIFFANY &amp; BOSCO, P.A. Ho: Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -3371,11 +3065,7 @@
           <t>$206,196.00</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Guild Mortgage Company LLC Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>2018046746</t>
@@ -3403,7 +3093,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>23976 W Pecan Road, Buckeye, AZ 85326</t>
+          <t>Jorge A Cornejo, an unmarried man</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3425,11 +3115,11 @@
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3462,16 +3152,7 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Prestige Default Services, LLC
-1920 Old Tustin Ave.
-Santa Ana, California 92705
-Phone: 949-427-2010
-SPACE ABOVE THIS LINE FOR RECORDERS USE
-TS#: 26-19021 Loan #: ******1147 Order #: 260147405-AZ-VOI</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -3494,7 +3175,11 @@
           <t>$147,000.00</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>'S SALE</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>949-427-2010</t>
@@ -3539,11 +3224,11 @@
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address;missing_trustee</t>
+          <t>ocr_fallback;missing_property_address</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3570,24 +3255,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Elania</t>
+          <t>(S):</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Husband</t>
+          <t>Ii</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wife,</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>As</t>
-        </is>
-      </c>
+          <t>Andria</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -3629,7 +3310,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
+          <t>'s Sale</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3659,7 +3340,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>ELANIA WEST, HUSBAND AND WIFE, AS</t>
+          <t>(s): TYRONE DANIEL WEST II AND ANDRIA</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3701,11 +3382,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+          <t>(S):</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Sole</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Separate</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -3748,7 +3437,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>ACTION AND OBTAIN A COURT ORDER PURSUANT TO RULE 65, ARIZONA RULES OF CIVIL</t>
+          <t>SALE OR IF YOU HAVE AN OBJECTION TO THE TRUSTEE SALE, YOU MUST FILE AN</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3778,7 +3467,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>property</t>
+          <t>(s): Ariel Carlos, a married man, as his sole and separate</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3822,24 +3511,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Husband</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>(S):</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brent</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wife</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Quality Loan Service Corporation
-2763 Camino Del Rio South
-San Diego, CA 92108
-“TS No.. AZ-26-1048525-AB~—~—~C~&lt;“is—sts~s~*st::OC(CS”:*:*:*:CCSCS*CSS pace above this fine for recorders use</t>
-        </is>
-      </c>
+          <t>Teresa</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Hernandez-Brent</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -3880,7 +3570,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
+          <t>'s Sale</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3910,7 +3600,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>husband and wife</t>
+          <t>(s): Paul A. Brent and Teresa D. Hernandez-Brent</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3922,7 +3612,7 @@
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3959,16 +3649,7 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Prestige Default Services, LLC
-1920 Old Tustin Ave.
-Santa Ana, California 92705
-Phone: 949-427-2010
-SPACE ABOVE THIS LINE FOR RECORDERS USE
-TS#: 26-18971 Loan #: ******9988 Order #: 260141702-AZ-VOI</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -3991,7 +3672,11 @@
           <t>$373,117.00</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>'S SALE</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>949-427-2010</t>
@@ -4036,11 +3721,11 @@
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address;missing_trustee</t>
+          <t>ocr_fallback;missing_property_address</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4065,26 +3750,10 @@
           <t>20220478953</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Serena</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Shao</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Samuel</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>With</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>17100 Gillette Ave</t>
@@ -4140,11 +3809,7 @@
           <t>$596,000.00</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>2022047895</t>
@@ -4170,11 +3835,7 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>SERENA SHAO AND SAMUEL TANG, WIFE AND HUSBAND AS COMMUNITY PROPERTY WITH</t>
-        </is>
-      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
           <t>LOT 32, OF TATUM HIGHLANDS PARCEL 19, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE
@@ -4188,11 +3849,11 @@
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_owner;missing_trustee</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4219,40 +3880,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Husband</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>(S):</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tany!</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Wife</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Unofficial
- 2~Document
- 17
- Ho:</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>South
- San Diego</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>92108</t>
-        </is>
-      </c>
+          <t>Colette</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ebail</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>201 West Jefferson</t>
@@ -4290,7 +3939,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Recorder of MARICOPA County, Arizona. NOTICE! IF YOU BELEEVE THERE IS A DEFENSE TO THE</t>
+          <t>'s Sale</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -4320,7 +3969,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>HUSBAND AND WIFE</t>
+          <t>(s): CORNELIUS E TANY! AND COLETTE T EBAIL</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -4335,7 +3984,7 @@
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4366,12 +4015,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>(S):</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Az</t>
+          <t>Man</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -4417,7 +4066,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>, 2763 Camino Dei Rio South, San Diego, CA 92108</t>
+          <t>'s Sale</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -4447,7 +4096,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>14145 N 92ND ST UNIT 1188, SCOTTSDALE, AZ</t>
+          <t>(s): ROBERT L HENDERSON JR, SINGLE MAN</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -968,12 +968,24 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street, Phoenix, AZ 85003 on July 23, 2026 at 10:00 AM on said day.</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+          <t>29409 N 182ND AVE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SURPRISE</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85387-7084</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1022,7 +1034,7 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -1503,12 +1515,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street, Phoenix, AZ 85003 on July 23, 2026 at 10:00 AM on said day.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+          <t>14870 N 174TH LN</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SURPRISE</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>85388</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1559,7 +1583,7 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -2086,12 +2110,12 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>7350 W. Desert Lane</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Laveen</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2101,7 +2125,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85339</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2204,12 +2228,12 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>6619 W Kristal Way</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2219,7 +2243,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85308</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2803,22 +2827,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>41121 W Montebello Ave</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Tonopah</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85354</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3036,12 +3060,12 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>23976 W Pecan Road</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Buckeye</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3051,7 +3075,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85326</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3904,12 +3928,12 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>201 West Jefferson</t>
+          <t>7110 SOUTH CHAMPAGNE WAY</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>GILBERT</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3919,7 +3943,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85297</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -587,24 +587,12 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4130 W NANCY LN</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
+          <t>4130 W NANCY LN, PHOENIX, AZ 85041 Tax Parcel Number: 105-89-133</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -620,11 +608,7 @@
           <t>$250,000.00</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>'s Sale</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>2022060328</t>
@@ -665,11 +649,11 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -728,24 +712,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15252 N 100TH STREET # 1146</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>SCOTTSDALE</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>85260</t>
-        </is>
-      </c>
+          <t>15252 N 100TH STREET #1146, SCOTTSDALE, AZ 85260 Tax Parcel Number: 217-54-700</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -812,7 +784,7 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -983,7 +955,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85387-7084</t>
+          <t>85387</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1191,7 +1163,11 @@
           <t>$304,385</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>2022069546</t>
@@ -1220,11 +1196,11 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address;missing_owner;missing_trustee</t>
+          <t>ocr_fallback;missing_property_address;missing_owner</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,24 +1365,12 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1501 East Nielson Avenue</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>85204</t>
-        </is>
-      </c>
+          <t>1501 East Nielson Avenue, Mesa, AZ 85204 Tax Parcel # 138-13-118</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1460,7 +1424,7 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1891,7 +1855,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85302.</t>
+          <t>85302</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2010,11 +1974,7 @@
           <t>$381,954.00</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>'S SALE</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>2022086798</t>
@@ -2063,11 +2023,11 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address</t>
+          <t>ocr_fallback;missing_property_address;missing_trustee</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2100,11 +2060,7 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Title No: 260189030-AZ-VOI</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -2139,7 +2095,11 @@
           <t>$302,421.00</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>2021062196</t>
@@ -2189,11 +2149,11 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2218,11 +2178,7 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Title No: 260201429-AZ-VOI</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -2257,7 +2213,11 @@
           <t>$104,000.00</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>2021093457</t>
@@ -2302,11 +2262,11 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback;missing_owner</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2434,11 +2394,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>TIFFANY &amp; BOSCO, P.A. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona 85004 ee OO u-O Oo 0 ems Title No: 92723396</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -2454,7 +2410,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2473,7 +2429,11 @@
           <t>$1,295,280.00</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>007-0195094</t>
@@ -2519,11 +2479,11 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback;missing_owner</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2548,11 +2508,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>85004 Title No: 22600371 RAY 22 TIFFANY &amp; BOSCO, P.A. Yo. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -2587,7 +2543,11 @@
           <t>$117,930.00</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>2023009805</t>
@@ -2633,11 +2593,11 @@
         </is>
       </c>
       <c r="Y19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback;missing_owner</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2670,11 +2630,7 @@
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>85004 Title No: 22600368 Car 22 TIFFANY &amp; BOSCO, P.A. Yo. Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -2709,7 +2665,11 @@
           <t>$167,200.00</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>2006167899</t>
@@ -2760,11 +2720,11 @@
         </is>
       </c>
       <c r="Y20" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,26 +2765,10 @@
           <t>Property</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>1850 North Central Avenue 22 TIFFANY &amp; BOSCO, P.A. Ga. Central Arts Plaza Twenty Fourth Floor</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>85004</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>41121 W Montebello Ave</t>
@@ -2837,7 +2781,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2856,7 +2800,11 @@
           <t>$285,000.00</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>2021088582</t>
@@ -2904,11 +2852,11 @@
         </is>
       </c>
       <c r="Y21" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2933,26 +2881,10 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1850 North Central Avenue 22 TIFFANY &amp; BOSCO, P.A. Ga. Central Arts Plaza Twenty Fourth Floor</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>85004</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>302 E Mohave St</t>
@@ -2984,7 +2916,11 @@
           <t>$262,350.00</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>2022052003</t>
@@ -3013,11 +2949,11 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback;missing_owner</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3050,11 +2986,7 @@
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>85004 Title No: 22600237 CARY 22 TIFFANY &amp; BOSCO, P.A. Ho: Central Arts Plaza Twenty Fourth Floor 1850 North Central Avenue Phoenix, Arizona</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -3089,7 +3021,11 @@
           <t>$206,196.00</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>2018046746</t>
@@ -3139,11 +3075,11 @@
         </is>
       </c>
       <c r="Y23" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3199,11 +3135,7 @@
           <t>$147,000.00</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>'S SALE</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>949-427-2010</t>
@@ -3248,11 +3180,11 @@
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address</t>
+          <t>ocr_fallback;missing_property_address;missing_trustee</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3299,24 +3231,12 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2778 NORTH 150TH LANE</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>GOODYEAR</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>85395</t>
-        </is>
-      </c>
+          <t>2778 NORTH 150TH LANE, GOODYEAR, AZ 85395 Tax Parcel Number: 508-14-199</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -3332,11 +3252,7 @@
           <t>$353,100.00</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>'s Sale</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>2015001972</t>
@@ -3375,11 +3291,11 @@
         </is>
       </c>
       <c r="Y25" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3426,24 +3342,12 @@
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2799 E BALSAM DR</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>CHANDLER</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>85286</t>
-        </is>
-      </c>
+          <t>2799 E BALSAM DR, CHANDLER, AZ 85286 Tax Parcel Number: 303-43-776, 303-43-776 6</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -3459,11 +3363,7 @@
           <t>$455,000.00</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>SALE OR IF YOU HAVE AN OBJECTION TO THE TRUSTEE SALE, YOU MUST FILE AN</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>2021136601</t>
@@ -3504,11 +3404,11 @@
         </is>
       </c>
       <c r="Y26" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3559,24 +3459,12 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3636 W LAREDO ST</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>CHANDLER</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>85226</t>
-        </is>
-      </c>
+          <t>3636 W LAREDO ST, CHANDLER, AZ 85226 Tax Parcel Number: 301-64-666</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -3592,11 +3480,7 @@
           <t>$185,739.00</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>'s Sale</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>012-0812180</t>
@@ -3636,11 +3520,11 @@
         </is>
       </c>
       <c r="Y27" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3677,10 +3561,26 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>9018 W HILTON AVE</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>TOLLESON</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -3696,11 +3596,7 @@
           <t>$373,117.00</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>'S SALE</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>949-427-2010</t>
@@ -3745,11 +3641,11 @@
         </is>
       </c>
       <c r="Y28" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3815,7 +3711,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>85050-8930</t>
+          <t>85050</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3961,11 +3857,7 @@
           <t>$550,800.00</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>'s Sale</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>2007014985</t>
@@ -4008,11 +3900,11 @@
         </is>
       </c>
       <c r="Y30" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4055,24 +3947,12 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>7264 N 128TH AVE</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>GLENDALE</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>85307</t>
-        </is>
-      </c>
+          <t>7264 N 128TH AVE, GLENDALE, AZ, 85307 Tax Parcel Number: 501-53-449</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -4088,11 +3968,7 @@
           <t>$392,950.00</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>'s Sale</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>2021100645</t>
@@ -4131,11 +4007,11 @@
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback;missing_trustee</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -690,26 +690,10 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>7730 Market Center Ave Suite 100</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>El Paso</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>79912</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>15252 N 100TH STREET #1146, SCOTTSDALE, AZ 85260 Tax Parcel Number: 217-54-700</t>
@@ -784,7 +768,7 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -817,26 +801,10 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Irvine</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>92614</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>1036 E HIGHLAND AVENUE</t>
@@ -901,7 +869,7 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -1148,10 +1116,26 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2855 S Extension Rd Unit 247</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85210</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1196,11 +1180,11 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address;missing_owner</t>
+          <t>ocr_fallback;missing_owner</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1229,26 +1213,10 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Irvine</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>92614</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>3037 N 69TH AVENUE</t>
@@ -1318,7 +1286,7 @@
         </is>
       </c>
       <c r="Y8" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -1457,26 +1425,10 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Irvine</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>92614</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>14870 N 174TH LN</t>
@@ -1547,7 +1499,7 @@
         </is>
       </c>
       <c r="Y10" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -1580,26 +1532,10 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Irvine</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2614</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>22495 E STIRRUP ST</t>
@@ -1670,7 +1606,7 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -1703,26 +1639,10 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>irvine</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>92614</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>3832 N 86TH AVE</t>
@@ -1793,7 +1713,7 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -2297,24 +2217,12 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1737 E. Manhattan Dr. The street address is purported to be:</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Tempe</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>85282</t>
-        </is>
-      </c>
+          <t>1737 E. Manhattan Dr., Tempe, AZ 85282 Tax Parcel Number: 133-37-259</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -2365,7 +2273,7 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -3674,26 +3582,10 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Irvine</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>92614</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>25836 N 43RD PL</t>
@@ -3769,7 +3661,7 @@
         </is>
       </c>
       <c r="Y29" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -569,27 +569,15 @@
           <t>20220603286</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>(S):</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>An</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4130 W NANCY LN, PHOENIX, AZ 85041 Tax Parcel Number: 105-89-133</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -616,7 +604,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>7/21/2026</t>
+          <t>7/25/2022</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -634,26 +622,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>(s): SPS PLATINUM PROPERTIES, LLC, AN</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>LOT 114, LAS CASAS GRANDES, ACCORDING TO THE PLAT OF
-RECORD IN THE OFFICE OF THE COUNTY RECORDER OF MARICOPA
-COUNTY, ARIZONA, RECORDED IN BOOK 136 OF MAPS, PAGE 25
-AND PLAT OF CORRECTION RECORDED IN BOOK 138 OF MAPS,
-PAGE 2,</t>
-        </is>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -678,27 +654,15 @@
           <t>20240056798</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Peggy</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Dated</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>15252 N 100TH STREET #1146, SCOTTSDALE, AZ 85260 Tax Parcel Number: 217-54-700</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -725,7 +689,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>April 13, 2026</t>
+          <t>01/31/2024</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -743,36 +707,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>PEGGY LEE KNIGHT, TRUSTEE OF THE PEGGY LEE KNIGHT 1999 REVOCABLE TRUST DATED</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UNIT 1146, VILLAGES NORTH PHASE III CONDOMINIUMS, A CONDOMINIUM AS CREATED BY
-THE CERTAIN DECLARATION RECORDED FEBRUARY 3, 1995, INRECORDER'S NO. 95-0065 120, RE-
-RECORDED FEBRUARY 16, 1995 IN RECORDER'S NO. 95-0087467, FIRST AMENDMENT RECORDED
-OCTOBER 27, 1995 IN RECORDER'S NO. 95-0659342, SECOND AMENDMENT RECORDED
-SEPTEMBER 17, 1996 IN RECORDER'S NO. 96-0657540, AND AS SHOWN ON PLAT OF SAID
-CONDOMINIUM RECORDED IN BOOK 420 OF MAPS, PAGE 7, RECORDS OF MARICOPA COUNTY,
-ARIZONA.
-TOGETHER WITH A PROPORTIONATE INTEREST IN THE COMMON AREAS AND FACILITIES IN
-SAID DECLARATION AND PLAT;
-EXCEPT ALL OIL, GAS, OTHER HYDROCARBON SUBSTANCES, HELIUM OR OTHER SUBSTANCES
-OF A GASEOUS NATURE, COAL, METALS, MINERALS, FOSSILS, FERTILIZER OF EVERY NAME
-AND DESCRIPTION, TOGETHER WITH ALL URANIUM, THORIUM OR ANY OTHER MINERAL
-WHICH IS OR MAY BE DETERMINED BY THE LAWS OF THE UNITED STATES, OR OF THIS STATE,
-OR DECISIONS OF COURT TO BE PECULIARLY ESSENTIAL TO THE PRODUCTION OF
-FISSIONABLE MATERIALS, WHETHER </t>
-        </is>
-      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -848,7 +790,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>. The purchaser at the sale, other than the Beneficiary to the extent of his</t>
+          <t>08/29/2024</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -869,11 +811,11 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -949,7 +891,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>. The purchaser at the sale, other than the Beneficiary to the extent of his</t>
+          <t>08/29/2024</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -968,17 +910,13 @@
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>ATTACHED AS EXHIBIT "A"</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -998,27 +936,15 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>’S</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Address:</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Avenue</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260222835</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -1042,11 +968,7 @@
           <t>$55,250,000</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>’s Name, Address, and Telephone Number: Jason D. Curry, Renaissance One</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>019-0625397</t>
@@ -1054,7 +976,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>August 13, 2019</t>
+          <t>5/3/2029</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1072,22 +994,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>’s Stated Name and Address: Salt River Point TT, LLC, 777 Third Avenue</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>See attached Exhibit A</t>
-        </is>
-      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1107,7 +1021,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20220695468</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -1118,7 +1036,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2855 S Extension Rd Unit 247</t>
+          <t>2855 S Extension Rd Unit 247 Mesa</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1147,11 +1065,7 @@
           <t>$304,385</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>2022069546</t>
@@ -1159,7 +1073,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>July 15, 2026</t>
+          <t>09/07/2022</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1180,11 +1094,11 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1217,26 +1131,10 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>3037 N 69TH AVENUE</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>85033</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1260,7 +1158,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>. The purchaser at the sale, other than the Beneficiary to the extent of his</t>
+          <t>08/29/2024</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1279,18 +1177,13 @@
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>LOT 54, MARYVALE TERRACE NO. 49, ACCORDING TO BOOK 199 OF MAPS, PAGE 45, RECORDS
-OF MARICOPA COUNTY, ARIZONA.</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1315,27 +1208,15 @@
           <t>20220901360</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Margie</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Az</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>1501 East Nielson Avenue, Mesa, AZ 85204 Tax Parcel # 138-13-118</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1360,11 +1241,7 @@
           <t>(602) 222-5711</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>December 20, 2022</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
           <t>20260223111</t>
@@ -1380,23 +1257,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Margie C. Yates, an unmarried woman, 1501 East Nielson Avenue, Mesa, AZ</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>LOT 113, MESA HOMES, PER MAP RECORDED IN BOOK 57 OF MAPS, PAGE 38, IN THE OFFICE OF THE
-COUNTY RECORDER, MARICOPA COUNTY, ARIZONA.</t>
-        </is>
-      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1429,26 +1297,10 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>14870 N 174TH LN</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>SURPRISE</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>85388</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1472,7 +1324,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>. The purchaser at the sale, other than the Beneficiary to the extent of his</t>
+          <t>08/29/2024</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1491,19 +1343,13 @@
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>LOT 263, OF SIERRA MONTANA PARCEL 14, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE
-OF THE COUNTY RECORDER OF MARICOPA COUNTY, ARIZONA, RECORDED IN BOOK 686 OF
-MAPS, PAGE 10.</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1536,26 +1382,10 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>22495 E STIRRUP ST</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>QUEEN CREEK</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>85142</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1579,7 +1409,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>. The purchaser at the sale, other than the Beneficiary to the extent of his</t>
+          <t>08/29/2024</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1598,19 +1428,13 @@
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>LOT 119, OF MADERA PHASE 1A, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE OF THE
-COUNTY RECORDED OF MARICOPA COUNTY, ARIZONA RECORDED IN IN BOOK 1520 OF MAPS,
-PAGE 37</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1643,26 +1467,10 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3832 N 86TH AVE</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>85037</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1686,7 +1494,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>. The purchaser at the sale. other than the Beneficiary to the extent of his</t>
+          <t>08/29/2024</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1705,19 +1513,13 @@
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>LOT 121, OF ARIZONA HOMES, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE OF THE
-COUNTY RECORDER OF MARICOPA COUNTY, ARIZONA, RECORDED IN BOOK 137 OF MAPS, PAGE
-7.</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1737,47 +1539,23 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Mary</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260223541</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>4525 N 66" St Unit 14</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>5420 W Onyx Ave.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>85302</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -1799,11 +1577,7 @@
           <t>022-0774491</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>July 15, 2026</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t>20260223541</t>
@@ -1819,22 +1593,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Mary Watola, a single woman, 4525 N 66" St Unit 14</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Exhibit “A”</t>
-        </is>
-      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1859,16 +1625,8 @@
           <t>20220867985</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>(As</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Trust)</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -1902,7 +1660,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>March 1, 2026</t>
+          <t>11/30/2022</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1920,34 +1678,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>, in the office of the
-County Recorder of Maricopa County, Arizona, NOTICE! IF YOU BELIEVE THERE IS A DEFENSE TO
-THE TRUSTEE SALE OR IF YOU HAVE AN OBJECTION TO THE TRUSTEE SALE, YOU MUST FILE
-AN ACTION AND OBTAIN A COURT ORDER PURSUANT TO RULE 65, ARIZONA RULES OF CIVIL
-PROCEDURE, STOPPING THE SALE NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME OF
-THE LAST BUSINESS DAY BEFORE THE SCHEDULED DATE OF THE SALE, OR YOU MAY HAVE
-WAIVED ANY DEFENSES OR OBJECTIONS TO THE SALE. UNLESS YOU OBTAIN AN ORDER, THE
-SALE WILL BE FINAL AND WILL OCCUR at public auction to the highest bidder in the Courtyard, by the
-main entrance of the Superior Court Building, 201 West Jefferson, Phoenix, Arizona 85003, on 7/21/2026 at
-12:00 PM of said day:
-LOT 26, OF PARADISE VILLAGE II, ACCORDING TO BOOK 484 OF MAPS, PAGE 49 AND RE-
-RECORDED IN BOOK 495 OF MAPS, PAGE 3, RECORDS OF MARICOPA COUNTY, ARIZONA.
-Per A.R.S. Section 33-803 (A)(2) the successor trustee appointed here qualifies as a Trustee of the trust deed i</t>
-        </is>
-      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1967,17 +1705,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Jerry</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20210621960</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -1986,24 +1720,12 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7350 W. Desert Lane</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Laveen</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>85339</t>
-        </is>
-      </c>
+          <t>7350 W</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -2015,11 +1737,7 @@
           <t>$302,421.00</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>2021062196</t>
@@ -2027,7 +1745,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>July 23, 2026</t>
+          <t>06/04/2021</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2045,31 +1763,10 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Jerry Beck, a single man</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>Lot 79, of LAVEEN MEADOWS - PARCEL 3, according to the Plat of Record in the Office of the County Recorder
-of Maricopa County, Arizona, recorded in Book 729 of Maps, Page 40.
-The street address/location of the real property described above is purported to be:
-7350 W. Desert Lane
-Laveen, AZ 85339
-Tax Parcel No.: 300-01-899 4
-The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
-the street address and other common designation, if any, shown herein.
-Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
-possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
-interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
-thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts created by said Deed
-of Trust.
-(Notice of</t>
-        </is>
-      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
@@ -2093,7 +1790,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20210934575</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -2104,7 +1805,7 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6619 W Kristal Way</t>
+          <t>6619 W Kristal Way Glendale</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2133,11 +1834,7 @@
           <t>$104,000.00</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>2021093457</t>
@@ -2145,7 +1842,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>July 30, 2026</t>
+          <t>08/30/2021</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2164,29 +1861,13 @@
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>Lot 518, of the Highlands at Arrowhead Ranch IV, according to the Plat of Record in the Office of the County
-Recorder of Maricopa County, Arizona, recorded in Book 419 of Maps, Page 40.
-The street address/location of the real property described above is purported to be:
-6619 W Kristal Way
-Glendale, AZ 85308
-Tax Parcel No.: 200-28-471 0
-The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
-the street address and other common designation, if any, shown herein.
-Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
-possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
-interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
-thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts created by said Deed
-of Trust</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2206,7 +1887,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20030000983297</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -2217,7 +1902,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1737 E. Manhattan Dr., Tempe, AZ 85282 Tax Parcel Number: 133-37-259</t>
+          <t>1737 E</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2246,7 +1931,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>April 15, 2026</t>
+          <t>04/15/2026</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2265,19 +1950,13 @@
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Lot 577, TEMPE GARDENS UNIT FIVE, according to the plat of record in the office of the County
-Recorder of Maricopa County, Arizona in Book 120 of Maps, Page 22.
-The street address is purported to be: 1737 E. Manhattan Dr., Tempe, AZ 85282</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2297,7 +1976,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260224598</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -2308,7 +1991,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1434 W Kerry Lane</t>
+          <t>1434 W Kerry Lane Phoenix</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2337,11 +2020,7 @@
           <t>$1,295,280.00</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>007-0195094</t>
@@ -2349,7 +2028,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>July 15, 2026</t>
+          <t>02/16/2007</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2368,30 +2047,13 @@
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lot 24, of MARLBOROUGH COUNTRY UNIT SIX, according to the Plat of Record in the Office of the County
-Recorder of Maricopa County, Arizona, recorded in Book 187 of Maps, Page 40.
-The street address/location of the real property described above is purported to be:
-1434 W Kerry Lane
-Phoenix, AZ 85027
-Tax Parcel No.: 209-23-024 0
-The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
-the street address and other common designation, if any, shown herein.
-Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
-possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
-interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
-thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts created by said Deed
-of Trust.
-(Notice </t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2411,7 +2073,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20230098051</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -2422,7 +2088,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4931 E Sharon Dr</t>
+          <t>4931 E Sharon Dr Scottsdale</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2451,11 +2117,7 @@
           <t>$117,930.00</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>2023009805</t>
@@ -2463,7 +2125,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>July 15, 2026</t>
+          <t>02/27/2023</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2482,30 +2144,13 @@
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Lot 920, Sunburst Estates Two, according to the plat of record in the office of the County Recorder of Maricopa
-County, Arizona, recorded in Book 189 of Maps, Page 7.
-The street address/location of the real property described above is purported to be:
-4931 E Sharon Dr
-Scottsdale, AZ 85254-3527
-Tax Parcel No.: 167-05-388 0
-The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
-the street address and other common designation, if any, shown herein.
-Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
-possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
-interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
-thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts created by said Deed
-of Trust.
-(Notice of S</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2525,17 +2170,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Antonio</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20061678996</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -2544,12 +2185,12 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6302 West Windsor Blvd.</t>
+          <t>4817 West Almeria Road Phoenix</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2559,7 +2200,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85301</t>
+          <t>85035</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2573,11 +2214,7 @@
           <t>$167,200.00</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>2006167899</t>
@@ -2585,7 +2222,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>July 22, 2026</t>
+          <t>12/26/2006</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2603,32 +2240,10 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Antonio A. Rodriguez, Jr., an unmarried man</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>Lot 68, of WEDGEWOOD PARK UNIT EIGHT, according to Book 134 of Maps, Page 39, records of Maricopa
-County, Arizona.
-More Correctly Described As:
-Lot 68, of WEDGEWOOD PARK UNIT 8, according to Book 134 of Maps, Page 39, records of Maricopa County,
-Arizona.
-The street address/location of the real property described above is purported to be:
-4817 West Almeria Road
-Phoenix, AZ 85035
-Tax Parcel No.: 103-20-587 6
-The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
-the street address and other common designation, if any, shown herein.
-Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
-possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
-interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
-thereon as proved in said Note, plus fees, charges and</t>
-        </is>
-      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2652,34 +2267,22 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Jaime</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Sole</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Separate</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Property</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20210885821</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>41121 W Montebello Ave</t>
+          <t>41121 W Montebcllo Ave Tonopah</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2708,11 +2311,7 @@
           <t>$285,000.00</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>2021088582</t>
@@ -2720,7 +2319,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>July 30, 2026</t>
+          <t>08/16/2021</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -2738,29 +2337,10 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Jaime G Lopez, a married man as his sole and separate property</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>Lot 454, of WEST PHOENIX ESTATES UNIT FOUR AMENDED, according to the Plat of Record in the Office of
-the County Recorder of Maricopa County, Arizona, recorded in Book 129 of Maps, Page 46, of Official Records.
-The street address/location of the real property described above is purported to be:
-41121 W Montebcllo Ave
-Tonopah, AZ 85354
-Tax Parcel No.: 506-35-036 8
-The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
-the street address and other common designation, if any, shown herein.
-Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
-possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
-interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
-thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts cr</t>
-        </is>
-      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2784,7 +2364,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20220520030</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -2795,7 +2379,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>302 E Mohave St</t>
+          <t>302 E Mohave St Phoenix</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2824,11 +2408,7 @@
           <t>$262,350.00</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>2022052003</t>
@@ -2836,7 +2416,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>July 22, 2026</t>
+          <t>06/22/2022</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2857,11 +2437,11 @@
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2881,17 +2461,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Jorge</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20180467465</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -2900,7 +2476,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23976 W Pecan Road</t>
+          <t>23976 W Pecan Road Buckeye</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2929,11 +2505,7 @@
           <t>$206,196.00</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>2018046746</t>
@@ -2941,7 +2513,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>August 6, 2026</t>
+          <t>06/19/2018</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2959,31 +2531,10 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Jorge A Cornejo, an unmarried man</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lot 202, of RIATA WEST UNIT 1, according to the Plat of Record in the Office of the County Recorder of Maricopa
-County, Arizona, recorded in Book 842 of Maps, Page 16.
-The street address/location of the real property described above is purported to be:
-23976 W Pecan Road
-Buckeye, AZ, 85326
-Tax Parcel No.: 504-75-530 1
-The undersigned Trustee, Leonard J. McDonald, Attorney at Law, disclaims any liability for any incorrectness of
-the street address and other common designation, if any, shown herein.
-Said sale will be made in an “as is” condition, but without covenant or warranty, expressed or implied, regarding title,
-possession or encumbrances, to satisfy the indebtedness secured by said Deed of Trust, advances thereunder, with
-interest as provided therein, and the unpaid principal balance of the Note secured by said Deed of Trust with interest
-thereon as proved in said Note, plus fees, charges and expenses of the Trustee and of the trusts created by said Deed
-of Trust.
-(Notice of Sale </t>
-        </is>
-      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
       <c r="Y23" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3007,17 +2558,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>(As</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Trust)</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20080659188</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
@@ -3069,30 +2616,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>LOT 166, ENCHANTED VILLAGE, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE OF
-THE COUNTY RECORDER OF MARICOPA COUNTY, ARIZONA, RECORDED IN BOOK 107 OF
-MAPS, PAGE 14.
-The successor trustee appointed herein qualifies as trustee of the Trust Deed in the trustee’s capacity as a
-member of the Arizona State Bar as required pursuant to ARS 33-803(A)(2).
-ACCORDING TO THE DEED OF TRUST OR UPON INFORMATION SUPPLIED BY THE BENEFICIARY,
-THE FOLLOWING INFORMATION IS PROVIDED PURSUANT TO A.R.S. SECTION 33-808(C):
-Street address or identifiable location: 1122 NORTH WELD CIRCLE
-MESA, Arizona 85203</t>
-        </is>
-      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_property_address;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3117,31 +2648,15 @@
           <t>20150019725</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>(S):</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ii</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Andria</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2778 NORTH 150TH LANE, GOODYEAR, AZ 85395 Tax Parcel Number: 508-14-199</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -3168,7 +2683,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>7/22/2026</t>
+          <t>1/6/2015</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -3186,24 +2701,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>(s): TYRONE DANIEL WEST II AND ANDRIA</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>LOT 191, GOODYEAR PLANNED REGIONAL CENTER PARCEL 10,
-ACCORDING TO BOOK 648 OF MAPS, PAGE 15, RECORDS OF
-MARICOPA COUNTY, ARIZONA.</t>
-        </is>
-      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3228,31 +2733,15 @@
           <t>20211366018</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>(S):</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Sole</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Separate</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2799 E BALSAM DR, CHANDLER, AZ 85286 Tax Parcel Number: 303-43-776, 303-43-776 6</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -3279,7 +2768,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>12/21/2021</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -3297,26 +2786,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>(s): Ariel Carlos, a married man, as his sole and separate</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>LOT 96, OF ABRALEE MEADOW, ACCORDING TO THE PLAT OF
-RECORD IN THE OFFICE OF THE COUNTY RECORDER OF MARICOPA
-COUNTY, ARIZONA, RECORDED IN BOOK 652 OF MAPS, PAGE 23
-AND CERTIFICATE OF CORRECTION RECORDED IN RECORDING NO.
-2004-1261016</t>
-        </is>
-      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3341,35 +2818,15 @@
           <t>20250315111</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>(S):</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Brent</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Teresa</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Hernandez-Brent</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>3636 W LAREDO ST, CHANDLER, AZ 85226 Tax Parcel Number: 301-64-666</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -3396,7 +2853,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>7/23/2026</t>
+          <t>8/9/2012</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
@@ -3414,25 +2871,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>(s): Paul A. Brent and Teresa D. Hernandez-Brent</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Lot 210, of Copperfield Estates, according to the plat of record in the Office of
-the County Recorder of Maricopa County, Arizona, recorded in Book 272 of
-Maps, Page 11 and Affidavit of Correction recorded in Instrument No. 84-
-412077. :</t>
-        </is>
-      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3452,43 +2898,23 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>(As</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Trust)</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20211162698</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>9018 W HILTON AVE</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>TOLLESON</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>85353</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -3530,30 +2956,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>LOT 175, OF 91ST AVENUE AND LOWER BUCKEYE ROAD, ACCORDING TO THE PLAT OF
-RECORD IN THE OFFICE OF THE COUNTY RECORDER OF MARICOPA COUNTY, ARIZONA,
-RECORDED IN BOOK 648 OF MAPS, PAGE 34.
-The successor trustee appointed herein qualifies as trustee of the Trust Deed in the trustee’s capacity as a
-member of the Arizona State Bar as required pursuant to ARS 33-803(A)(2).
-ACCORDING TO THE DEED OF TRUST OR UPON INFORMATION SUPPLIED BY THE BENEFICIARY,
-THE FOLLOWING INFORMATION IS PROVIDED PURSUANT TO A.R.S. SECTION 33-808(C):
-Street address or identifiable location: 9018 W HILTON AVE
-TOLLESON, Arizona 85353</t>
-        </is>
-      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3629,7 +3039,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>. The purchaser at the</t>
+          <t>08/29/2024</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3648,24 +3058,13 @@
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>LOT 32, OF TATUM HIGHLANDS PARCEL 19, ACCORDING TO THE PLAT OF RECORD IN THE OFFICE
-OF THE COUNTY RECORDER OF MARICOPA COUNTY, ARIZONA, RECORDED IN BOOK 392 OF
-MAPS, PAGE 15;EXCEPT ALL OIL, GAS, OTHER HYDROCARBON SUBSTANCES, HELIUM OR OTHER
-SUBSTANCES OF A GASEOUS NATURE, COAL, METALS, MINERALS, FOSSILS, FERTILIZER OF
-EVERY NAME AND DESCRIPTION, AND EXCEPT ALL MATERIAL WHICH MAY BE ESSENTIAL TO THE
-PRODUCTION OF FISSIONABLE MATERIALS AS RESERVED PURSUANT TO RECORDED
-INSTRUMENT IN FAVOR OF THE UNITED STATES OF AMERICA OR THE STATE OF ARIZONA,
-PURSUANT TO THE PROVISIONS OF ARIZONA REVISED STATUTES 37-231.</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_owner;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3690,50 +3089,18 @@
           <t>20070149857</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>(S):</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Tany!</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Colette</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Ebail</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>7110 SOUTH CHAMPAGNE WAY</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>GILBERT</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>85297</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>Maricopa</t>
@@ -3757,7 +3124,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Sale</t>
+          <t>1/29/2007</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3775,28 +3142,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>(s): CORNELIUS E TANY! AND COLETTE T EBAIL</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>Purported Street Address:
-7/22/2026 at 12:00PM
-In the courtyard by the main entrance of the Superior Court Building,
-located at 201 West Jefferson, Phoenix, AZ 85003
-LOT 2, SEVILLE 21, ACCORDING TO BOOK 644 OF MAPS, PAGE 34,
-RECORDS OF MARICOPA COUNTY, ARIZONA,
-7110 SOUTH CHAMPAGNE WAY, GILBERT, AZ, 85297</t>
-        </is>
-      </c>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
       <c r="Y30" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3821,27 +3174,15 @@
           <t>20211006457</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>(S):</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Man</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>7264 N 128TH AVE, GLENDALE, AZ, 85307 Tax Parcel Number: 501-53-449</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -3868,7 +3209,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>8/6/2026</t>
+          <t>9/14/2021</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3886,24 +3227,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>(s): ROBERT L HENDERSON JR, SINGLE MAN</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>LOT 54, LUKE LANDING, ACCORDING TO THE FINAL PLAT
-RECORDED IN BOOK 1462 MAPS, PAGE 23, RECORDS OF MARICOPA
-COUNTY, ARIZONA.</t>
-        </is>
-      </c>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>ocr_fallback;missing_trustee</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -422,11 +422,11 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -434,9 +434,9 @@
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
@@ -447,7 +447,7 @@
     <col width="60" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260222588</t>
+          <t>20260225916</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -652,27 +652,36 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>(s): SPS PLATINUM PROPERTIES, LLC, AN
-ARIZONA LIMITED LIABILIFY COMPANY
-20260222588
-Name and Address of</t>
+          <t>STERLING M. GRANT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$250,000.00</t>
+          <t>$236,880.00</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Reinstatement Line: (866) 645-7711 Ext 5318</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>19079 E SEAGULL DR</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -682,42 +691,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>314-05-709</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>$236,880.00</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2022060328</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>7/25/2022</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>8/8/2018</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>20180610512</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222588</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225916</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222588.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225916.pdf</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222588.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225916.pdf</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -725,14 +746,14 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260222588.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225916.txt</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260222606</t>
+          <t>20260226177</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -742,7 +763,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -757,20 +778,36 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PEGGY LEE KNIGHT,</t>
+          <t>RONALD HODNE, AN UNMARRIED MAN, AND LA TOYA GUEVARA, AN UNMARRIED WOMAN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$ 630,000.00</t>
+          <t>$690,900.00</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13910 S 180TH AVE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -780,57 +817,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>400-82-358</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>$690,900.00</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2024005679</t>
+          <t>2023057015</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>01/31/2024</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>20230570155</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222606</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226177</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222606.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226177.pdf</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222606.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226177.pdf</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260222606.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226177.txt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260222631</t>
+          <t>20260226185</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -840,7 +889,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -855,21 +904,36 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DONALD J. ECHOLS AND COLLEEN A. ECHOLS, HUSBAND AND WIFE
-Name and Address of the</t>
+          <t>BRIAN JAMISON</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$285,000.00</t>
+          <t>$330,000.00</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8126 W WATKINS ST</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85043</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -879,57 +943,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>104-33-181</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>$330,000.00</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>101-1084974</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>6/3/2021</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>20210626779</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222631</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226185</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222631.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226185.pdf</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222631.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226185.pdf</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260222631.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226185.txt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260222700</t>
+          <t>20260226190</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -939,7 +1015,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -954,25 +1030,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MASON BODROG, AN UNMARRIED MAN
-Name and Address of the</t>
+          <t>CANDICE AUGE AND TODD AUGE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$444,795.00</t>
+          <t>$285,000.00</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>4202 E EVERETT DR</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -982,7 +1057,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85003</t>
+          <t>85032</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -994,42 +1069,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>215-71-184</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2023048095</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+          <t>3/3/2022</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>20220200328</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222700</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226190</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222700.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226190.pdf</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222700.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226190.pdf</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1037,24 +1124,24 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260222700.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226190.txt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260222835</t>
+          <t>20260226195</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>N/TR SALE+</t>
+          <t>N/TR SALE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1069,36 +1156,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>’s Stated Name and Address: Salt River Point TT, LLC, 
-Floor 25, New York, NY 
-Current</t>
+          <t>HELEN E CHARLES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>$55,250,000</t>
+          <t>$246,500.00</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>COMMONLY KNOWN AS: 1130</t>
+          <t>9810 N BALBOA DR</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>SUN CITY</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85201</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1110,42 +1195,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>142-84-801</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>$246,500.00</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>019-0625397</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>5/3/2029</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+          <t>7/29/2021</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>20210829918</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222835</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226195</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222835.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226195.pdf</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222835.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226195.pdf</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG6" t="n">
@@ -1153,14 +1250,14 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260222835.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226195.txt</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260222909</t>
+          <t>20260226197</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1170,7 +1267,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1185,35 +1282,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rommel Eugenio Cordova, an unmarried man
-Current</t>
+          <t>YOLANDA MCKIM AND BILLY MCKIM, WIFE AND HUSBAND AS COMMUNITY PROPERTY</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>$304,385</t>
+          <t>$335,805.00</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue</t>
+          <t>3937 W MYRTLE AVE</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85004</t>
+          <t>85051</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1225,42 +1321,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>151-26-142</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>$335,805.00</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2022069546</t>
+          <t>2021066036</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>09/07/2022</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>20210660360</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260222909</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226197</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260222909.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226197.pdf</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260222909.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226197.pdf</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG7" t="n">
@@ -1268,14 +1376,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260222909.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226197.txt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260223068</t>
+          <t>20260226200</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1285,7 +1393,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1300,22 +1408,36 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ALEXIS M JAUREGU! RODRIGUEZ, AN UNMARRIED MAN, AND IYOANA G CHAVEZ, AN
-UNMARRIED WOMAN
-Name and Address of the</t>
+          <t>ROBERT FARMER</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>$294,566.00</t>
+          <t>$205,128.00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14300 W BELL RD UNIT 52</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SURPRISE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85374</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1325,57 +1447,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>503-59-212B</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>$205,128.00</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2021131699</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+          <t>3/2/2023</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>20230106079</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223068</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226200</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223068.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226200.pdf</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223068.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226200.pdf</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260223068.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226200.txt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260223111</t>
+          <t>20260226202</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1385,7 +1519,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1400,26 +1534,24 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Margie C. Yates, an unmarried woman, 
-85204
-Notice of</t>
+          <t>NIRA WANNARKA AND WILLIAM DIXON, WIFE AND HUSBAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$100,000.00</t>
+          <t>$381,562.00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2390 E. Camelback Road</t>
+          <t>2330 W SPENCER RUN</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1429,7 +1561,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>85016</t>
+          <t>85041</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1441,38 +1573,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>105-65-525105-65-525</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>$381,562.00</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>(602) 222-5711</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+          <t>2022061067</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>20220610672</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223111</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226202</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223111.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226202.pdf</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223111.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226202.pdf</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1480,14 +1628,14 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260223111.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226202.txt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260223127</t>
+          <t>20260226317</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1497,7 +1645,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1512,20 +1660,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LOGAN HAINLEN, AN UNMARRIED MAN, AND APRILYN STREETY, AN UNMARRIED WOMAN
-Name and Address of the</t>
+          <t>(as shown on the Deed of Trust) GOOD NEWS GROUP, LLC, AN ARIZONA LIMITED LIABILITY COMPANY AND ROSS FERRARO AND EMILY FERRARO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>$322,200.00</t>
+          <t>$374,000.00</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>201 W. Jefferson Street</t>
+          <t>201 W. Jefferson</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1552,42 +1699,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>155-53-014</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>$374,000.00</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2023050742</t>
+          <t>949-427-2010</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
+          <t>4/26/2023</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>20230215291</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223127</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226317</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223127.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226317.pdf</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223127.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226317.pdf</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1595,14 +1754,14 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260223127.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226317.txt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260223286</t>
+          <t>20260226412</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1612,7 +1771,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1627,21 +1786,36 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>JOSEPH PARKINSON AND ALEXIS PARKINSON, HUSBAND AND WIFE
-Name and Address of the</t>
+          <t>CAROLINE ANN BRICKELL AND SEAN GENZMER</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>$766,550.00</t>
+          <t>$252,340.00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>21003 N 123RD DR</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1651,57 +1825,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>232-14-036</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>$252,340.00</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2024031829</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
+          <t>12/23/2021</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>20211376027</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223286</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226412</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223286.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226412.pdf</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223286.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226412.pdf</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260223286.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226412.txt</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260223322</t>
+          <t>20260226657</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1711,7 +1897,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1726,25 +1912,36 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ROBERTO GAMINO, A SINGLE MAN
-Name and Address of Beneficia
-CASTLE &amp; COOKE MORTGAGE, LLC
-clo Servbank, N.A.
-Phoenix, AZ 85034
-Name and Address of</t>
+          <t>an unmarried woman</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>$82,500.00</t>
+          <t>$238,500.00</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11122 W Montana Ave.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Youngtown</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85363</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1754,57 +1951,65 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Numbers</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>$238,500.00</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2018030338</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
+          <t>024-0111013</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>20260226657</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223322</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226657</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223322.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226657.pdf</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223322.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226657.pdf</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260223322.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226657.txt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260223541</t>
+          <t>20260226771</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1814,7 +2019,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1829,27 +2034,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mary Watola, a single woman, 
-Scottsdale, AZ 85251.
-ORIGINAL PRINCIPAL BALANCE: $250,000.00
-TAX PARCEL NUMBER: 1] 3-25 ~ 66 7B</t>
+          <t>BOBBI SCHULTZ AS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$250,000.00</t>
+          <t>$275,000.00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5420 W. Onyx Ave.</t>
+          <t>10437 W CHERYL DR</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Glendale</t>
+          <t>SUN, CITY</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1859,7 +2061,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85302</t>
+          <t>85351</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1871,38 +2073,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>$275,000.00</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>022-0774491</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+          <t>2022071684</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>09/16/2022</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>20220716841</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260223541</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226771</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260223541.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226771.pdf</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260223541.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226771.pdf</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG13" t="n">
@@ -1910,14 +2128,14 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260223541.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226771.txt</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260224183</t>
+          <t>20260226956</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1927,7 +2145,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1942,60 +2160,34 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>(as shown on the Deed of Trust)
-MICHELLE INEZ MIRABELLA, AN UNMARRIED WOMAN AND CRAIG STEVEN NETH, AN
-UNMARRIED MAN
-MESA, AZ 85207
-20260224183
-NOTICE OF</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>'S SALE
-The following legally described trust property will be sold, pursuant to the power of sale under that certain
-Deed of Trust dated 11/30/2022 and recorded on 12/1/2022, as Instrument No. 20220867985, Deed of Trust
-Rerecorded on 3/5/2026 as Instrument No. 20260127496 to correct errors in the legal description, in the office of the
-County Recorder of Maricopa County, Arizona, NOTICE! IF YOU BELIEVE THERE IS A DEFENSE TO
-THE TRUSTEE SALE OR IF YOU HAVE AN OBJECTION TO THE TRUSTEE SALE, YOU MUST FILE
-AN ACTION AND OBTAIN A COURT ORDER PURSUANT TO RULE 65, ARIZONA RULES OF CIVIL
-PROCEDURE, STOPPING THE SALE NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME OF
-THE LAST BUSINESS DAY BEFORE THE SCHEDULED DATE OF THE SALE, OR YOU MAY HAVE
-WAIVED ANY DEFENSES OR OBJECTIONS TO THE SALE. UNLESS YOU OBTAIN AN ORDER, THE
-SALE WILL BE FINAL AND WILL OCCUR at public auction to the highest bidder in the Courtyard, by the
-main entrance of the Superior Court Building, 201 West Jefferson, Phoenix, Arizona 85003, on 7/21/2026 at
-12:00 PM of said day:
-LOT 26, OF PARADISE VILLAGE II, ACCORDING TO BOOK 484 OF MAPS, PAGE 49 AND RE-
-RECORDED IN BOOK 495 OF MAPS, PAGE 3, RECORDS OF MARICOPA COUNTY, ARIZONA.
-Per A.R.S. Section 33-803 (A)(2) the successor trustee appointed here qualifies as a Trustee of the trust deed in the
-Trustee's capacity as a member of the State Bar of Arizona.
-ACCORDING TO THE DEED OF TRUST OR UPON INFORMATION SUPPLIED BY THE</t>
-        </is>
-      </c>
+          <t>LUIS ALONSO MIRANDA GOMEZ, A MARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>$381,954.00</t>
+          <t>$122,042.00</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3550 N. Central Ave.</t>
+          <t>520 E HARRISON DR</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>AVONDALE</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>85012</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2007,78 +2199,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>'S SALE
-The following legally described trust property will be sold, pursuant to the power of sale under that certain
-Deed of Trust dated 11/30/2022 and recorded on 12/1/2022, as Instrument No. 20220867985, Deed of Trust
-Rerecorded on 3/5/2026 as Instrument No. 20260127496 to correct errors in the legal description, in the office of the
-County Recorder of Maricopa County, Arizona, NOTICE! IF YOU BELIEVE THERE IS A DEFENSE TO
-THE TRUSTEE SALE OR IF YOU HAVE AN OBJECTION TO THE TRUSTEE SALE, YOU MUST FILE
-AN ACTION AND OBTAIN A COURT ORDER PURSUANT TO RULE 65, ARIZONA RULES OF CIVIL
-PROCEDURE, STOPPING THE SALE NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME OF
-THE LAST BUSINESS DAY BEFORE THE SCHEDULED DATE OF THE SALE, OR YOU MAY HAVE
-WAIVED ANY DEFENSES OR OBJECTIONS TO THE SALE. UNLESS YOU OBTAIN AN ORDER, THE
-SALE WILL BE FINAL AND WILL OCCUR at public auction to the highest bidder in the Courtyard, by the
-main entrance of the Superior Court Building, 201 West Jefferson, Phoenix, Arizona 85003, on 7/21/2026 at
-12:00 PM of said day:
-LOT 26, OF PARADISE VILLAGE II, ACCORDING TO BOOK 484 OF MAPS, PAGE 49 AND RE-
-RECORDED IN BOOK 495 OF MAPS, PAGE 3, RECORDS OF MARICOPA COUNTY, ARIZONA.
-Per A.R.S. Section 33-803 (A)(2) the successor trustee appointed here qualifies as a Trustee of the trust deed in the
-Trustee's capacity as a member of the State Bar of Arizona.
-ACCORDING TO THE DEED OF TRUST OR UPON INFORMATION SUPPLIED BY THE</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>$122,042.00</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2022086798</t>
+          <t>2018083116</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>11/30/2022</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
+          <t>11/07/2018</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>20180831169</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224183</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226956</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224183.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226956.pdf</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224183.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226956.pdf</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260224183.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226956.txt</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260224205</t>
+          <t>20260226960</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2088,7 +2271,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2103,35 +2286,34 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jerry Beck, a single man
-Current</t>
+          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON, HUSBAND AND WIFE AND ANTHONY DE LEON, AN UNMARRIED MAN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>$302,421.00</t>
+          <t>$323,000.00</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue</t>
+          <t>30306 WEST PORTLAND STREET</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>BUCKEYE</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>85004</t>
+          <t>85396</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2143,42 +2325,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>504-15-159</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>$323,000.00</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2021062196</t>
+          <t>2022084779</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>06/04/2021</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr"/>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>20220847791</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224205</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226960</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224205.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226960.pdf</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224205.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226960.pdf</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG15" t="n">
@@ -2186,14 +2380,14 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260224205.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226960.txt</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260224218</t>
+          <t>20260227028</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2203,7 +2397,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2218,35 +2412,34 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cynthia L Walsh, an unmarried woman
-Current</t>
+          <t>JASON DANIEL MURRAY AND AMBER MURRAY, HUSBAND AND WIFE AS JOINT TENANTS WITH RIGHT OF SURVIVORSHIP</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>$104,000.00</t>
+          <t>$235,653.00</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue</t>
+          <t>3307 W ECHO LN</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>85004</t>
+          <t>85051</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2258,42 +2451,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>$235,653.00</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2021093457</t>
+          <t>2022086524</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>08/30/2021</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr"/>
+          <t>11/30/2022</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>20220865242</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224218</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227028</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224218.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227028.pdf</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224218.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227028.pdf</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG16" t="n">
@@ -2301,14 +2506,14 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260224218.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227028.txt</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260224386</t>
+          <t>20260227091</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2318,7 +2523,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2333,26 +2538,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jorge Guzman, an unmarried man, 
-Rowland Heights, CA 91748
-Name and Address of</t>
+          <t>JORDAN OLIVA, A SINGLE MAN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$465,000.00</t>
+          <t>$427,696.00</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2150 E: Brown Road</t>
+          <t>22229 E VIA DEL PALO</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>QUEEN, CREEK</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2362,7 +2565,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>85213</t>
+          <t>85142</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2374,42 +2577,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>$427,696.00</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2003000098</t>
+          <t>2021116172</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>04/15/2026</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr"/>
+          <t>10/28/2021</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>20211161722</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224386</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227091</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224386.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227091.pdf</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224386.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227091.pdf</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG17" t="n">
@@ -2417,14 +2632,14 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260224386.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227091.txt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260224598</t>
+          <t>20260227136</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2434,7 +2649,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2449,35 +2664,34 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomas A. Dehne, single, as his sole and separate property
-Current</t>
+          <t>RUSTY ROBERTS AND NICHOLE ROBERTS, HUSBAND AND WIFE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>$1,295,280.00</t>
+          <t>$1,138,564.00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue</t>
+          <t>8145 W CAMINO DE ORO</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>PEORIA</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>85004</t>
+          <t>85383</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2489,42 +2703,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>$1,138,564.00</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>007-0195094</t>
+          <t>2023015469</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>02/16/2007</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr"/>
+          <t>03/28/2023</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>20230154699</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224598</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227136</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224598.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227136.pdf</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224598.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227136.pdf</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG18" t="n">
@@ -2532,14 +2758,14 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260224598.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227136.txt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260224897</t>
+          <t>20260227218</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2549,7 +2775,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2564,35 +2790,34 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Travis Partridge, an unmarried man
-Current</t>
+          <t>RYMAX DEVELOPMENT, L.L.C., AN ARIZONA LIMITED LIABILITY COMPANY</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>$117,930.00</t>
+          <t>$480,000.00</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue</t>
+          <t>18245 N PIMA ROAD UNIT 1049</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>SCOTTSDALE</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>85004</t>
+          <t>85040</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2604,42 +2829,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>113-25-059</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>$480,000.00</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2023009805</t>
+          <t>2024056527</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>02/27/2023</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr"/>
+          <t>10/23/2024</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>20240565279</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224897</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227218</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224897.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227218.pdf</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224897.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227218.pdf</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG19" t="n">
@@ -2647,14 +2884,14 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260224897.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227218.txt</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260224899</t>
+          <t>20260227219</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2664,7 +2901,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2679,37 +2916,20 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antonio A. Rodriguez, Jr., an unmarried man
-Current</t>
+          <t>TITAN FAMILY REALESTATE LLC, a Arizona limited liability company</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>$167,200.00</t>
+          <t>$110,000.00</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>1850 North Central Avenue</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>85004</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -2719,57 +2939,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>102-84-270</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>$110,000.00</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2006167899</t>
+          <t>2026001494</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>12/26/2006</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr"/>
+          <t>1/09/2026</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>20260014942</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224899</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227219</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224899.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227219.pdf</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224899.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227219.pdf</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260224899.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227219.txt</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260224933</t>
+          <t>20260227220</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2779,7 +3011,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2794,37 +3026,20 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jaime G Lopez, a married man as his sole and separate property
-Current</t>
+          <t>Graciela Bucio Perez an unmarried woman</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>$285,000.00</t>
+          <t>$176,000.00</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>1850 North Central Avenue</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>85004</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -2834,57 +3049,69 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>206-20-159</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>$176,000.00</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2021088582</t>
+          <t>2024014138</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>08/16/2021</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr"/>
+          <t>3/19/2024</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>20240141383</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224933</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227220</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224933.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227220.pdf</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224933.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227220.pdf</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260224933.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227220.txt</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260224934</t>
+          <t>20260227284</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2894,7 +3121,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2909,35 +3136,34 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Domanick O Lucious, an unmarried man
-Current</t>
+          <t>JOSEPH VERDUZCO, A MARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>$262,350.00</t>
+          <t>$294,405.00</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue</t>
+          <t>2830 S. CHATSWORTH</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>MESA</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>85004</t>
+          <t>85212</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -2949,42 +3175,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>309-19-162</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>$294,405.00</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2022052003</t>
+          <t>2018017439</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>06/22/2022</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr"/>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>20180174392</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224934</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227284</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224934.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227284.pdf</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224934.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227284.pdf</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG22" t="n">
@@ -2992,14 +3230,14 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260224934.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227284.txt</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260224938</t>
+          <t>20260227302</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3009,7 +3247,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3024,35 +3262,34 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jorge A Cornejo, an unmarried man
-Current</t>
+          <t>/GRANTOR: (as of the recording of the Notice of</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>$206,196.00</t>
+          <t>$10,000,000.00</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1850 North Central Avenue</t>
+          <t>7508 N. 59th Avenue</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>85004</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3064,42 +3301,50 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>IDENTIFIABLE</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>$10,000,000.00</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2018046746</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>06/19/2018</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr"/>
+          <t>2024043257</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>20240432575</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260224938</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227302</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260224938.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227302.pdf</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260224938.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227302.pdf</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG23" t="n">
@@ -3107,14 +3352,14 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260224938.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227302.txt</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260225129</t>
+          <t>20260227512</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3124,7 +3369,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3139,24 +3384,19 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>(as shown on the Deed of Trust)
-CLAYTON M. WOODRUFF AND DOROTHY J. WOODRUFF, HUSBAND AND WIFE
-SUN CITY, AZ 85373
-20260225129
-TS#: 26-
-NOTICE OF</t>
+          <t>(s): BRENDA FAE HUBBARD, A MARRIED WOMAN AS HER SOLE AND SEPARATE PROPERTY</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>$147,000.00</t>
+          <t>$192,449.00</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Street address or identifiable location: 1122 NORTH WELD CIRCLE</t>
+          <t>9113 E BUTTERNUT AVE</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3166,12 +3406,12 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>85203</t>
+          <t>85208</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3183,42 +3423,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>218-41-190</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>$192,449.00</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>949-427-2010</t>
+          <t>2022061027</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>7/15/2008</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr"/>
+          <t>7/28/2022</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>20220610270</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225129</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227512</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225129.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227512.pdf</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225129.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227512.pdf</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG24" t="n">
@@ -3226,14 +3478,14 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225129.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227512.txt</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260225192</t>
+          <t>20260227521</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3243,7 +3495,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3258,30 +3510,36 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>(s): TYRONE DANIEL WEST II AND ANDRIA
-ELANIA WEST, HUSBAND AND WIFE, AS
-20260225192
-COMMUNITY PROPERTY WITH RIGHT OF
-SURVIVORSHIP
-85395
-Name and Address of</t>
+          <t>(s): ZHONG K WANG AND FRANCIS N PRICE, AND UNMARRIED MAN AND FRANCIS PRICE, AN UNMARRIED WOMAN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>$353,100.00</t>
+          <t>$200,000.00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Reinstatement Line: (866) 645-7711 Ext 5318</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+          <t>12546 W MANDALAY LANE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>EL, MIRAGE</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -3291,42 +3549,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>509-13-497</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>$200,000.00</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2015001972</t>
+          <t>2019003016</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1/6/2015</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr"/>
+          <t>1/15/2019</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>20190030161</t>
+        </is>
+      </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225192</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227521</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225192.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227521.pdf</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225192.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227521.pdf</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG25" t="n">
@@ -3334,14 +3604,14 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225192.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227521.txt</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260225194</t>
+          <t>20260227539</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3351,7 +3621,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3366,27 +3636,40 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>(s): Ariel Carlos, a married man, as his sole and separate
-property
-20260225194
-Name and Address of</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Wayne Carpenter, a single person</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>$455,000.00</t>
+          <t>$50,000.00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Reinstatement Line: (866) 645-7711 Ext 5318</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+          <t>7486 S Sundown Ct</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -3397,56 +3680,68 @@
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>$50,000.00</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2021136601</t>
+          <t>2025032204</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>12/21/2021</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr"/>
+          <t>06/04/2025</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>20250322044</t>
+        </is>
+      </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225194</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227539</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225194.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227539.pdf</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225194.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227539.pdf</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225194.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227539.txt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260225195</t>
+          <t>20260227902</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3456,7 +3751,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3471,27 +3766,36 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>(s): Paul A. Brent and Teresa D. Hernandez-Brent,
-husband and wife
-20260225195
-Name and Address of</t>
+          <t>in favor of WELLS FARGO BANK, N.A. as</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>$185,739.00</t>
+          <t>$337,252.80</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Reinstatement Line: (866) 645-7711 Ext 5318</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+          <t>21823 NORTH MAYA COURT</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -3501,42 +3805,54 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>232-31-246</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>$337,252.80</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>012-0812180</t>
+          <t>005-1708272</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>8/9/2012</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr"/>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>20150216695</t>
+        </is>
+      </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225195</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227902</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225195.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227902.pdf</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225195.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227902.pdf</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG27" t="n">
@@ -3544,14 +3860,14 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225195.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227902.txt</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260225265</t>
+          <t>20260227926</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3561,7 +3877,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3576,40 +3892,38 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>(as shown on the Deed of Trust)
-SERGIO VILLAGOMEZ PADILLA, AN UNMARRIED MAN AND MARIA VILLAGOMEZ, AN
-UNMARRIED WOMAN, AS JOINT TENANTS WITH RIGHT OF SURVIVORSHIP
-TOLLESON, ARIZONA 85353
-20260225265
-TS#: 26-
-NOTICE OF</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Frances Garcia, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>$373,117.00</t>
+          <t>$68,000.00</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Street address or identifiable location: 9018 W HILTON AVE</t>
+          <t>2802 West Madison Street</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>TOLLESON</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Arizona</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>85353</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3622,56 +3936,68 @@
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>$68,000.00</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>949-427-2010</t>
+          <t>2007055829</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>10/28/2021</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr"/>
+          <t>05/14/2007</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>20070558292</t>
+        </is>
+      </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225265</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227926</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225265.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227926.pdf</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225265.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227926.pdf</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225265.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227926.txt</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260225382</t>
+          <t>20260227939</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3681,7 +4007,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3696,22 +4022,40 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SERENA SHAO AND SAMUEL TANG, WIFE AND HUSBAND AS COMMUNITY PROPERTY WITH
-RIGHT OF SURVIVORSHIP
-Name and Address of the</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Luis Vincente Gurrola Martinez, a single man</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>$596,000.00</t>
+          <t>$233,100.00</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4107 W Krall St</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
@@ -3722,56 +4066,68 @@
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>$233,100.00</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2022047895</t>
+          <t>2021064449</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr"/>
+          <t>06/11/2021</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>20210644498</t>
+        </is>
+      </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225382</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227939</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225382.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227939.pdf</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225382.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227939.pdf</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225382.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227939.txt</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260225528</t>
+          <t>20260227955</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3781,7 +4137,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3796,30 +4152,40 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>(s): CORNELIUS E TANY! AND COLETTE T EBAIL,
-HUSBAND AND WIFE
-in the office of the County
-20260225528
-7110S CHAMPAGNE WAY, xxx, GILBERT, AZ
-85297
-Name and Address of</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Christine Lea Kurtz-Ford, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>$550,800.00</t>
+          <t>$121,000.00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Reinstatement Line: (866) 645-7711 Ext 5318</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+          <t>630 E Jensen St Unit 138</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85203</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -3830,56 +4196,68 @@
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>$121,000.00</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2007014985</t>
+          <t>2020092366</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>1/29/2007</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr"/>
+          <t>09/29/2020</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>20200923660</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225528</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227955</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225528.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227955.pdf</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225528.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227955.pdf</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225528.txt</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227955.txt</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260225555</t>
+          <t>20260227961</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3889,7 +4267,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3904,27 +4282,40 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>(s): ROBERT L HENDERSON JR, SINGLE MAN
-85260
-20260225555
-Name and Address of ‘</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Martin V Valadez, a single man and Velazquez David Valadez, a single man</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>$392,950.00</t>
+          <t>$380,000.00</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Reinstatement Line: (866) 645-7711 Ext 5318</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+          <t>3708 West Berridge Lane</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
@@ -3935,49 +4326,1187 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>$380,000.00</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2021100645</t>
+          <t>2023055878</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>9/14/2021</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
+          <t>10/27/2023</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>20230558787</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225555</t>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227961</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225555.pdf</t>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227961.pdf</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225555.pdf</t>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227961.pdf</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>["ocr_fallback"]</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227961.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260227974</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Richard L Bristol and Grace A Bristol, husband and wife</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>$149,055.00</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>20803 W Bradley Road</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Wittmann</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>85361</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>$149,055.00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2016024986</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>04/15/2016</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>20160249869</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227974</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227974.pdf</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227974.pdf</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>ocr_fallback</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227974.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260228010</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>in which LB Assets 8, LLC, an Arizona limited liability company, is the named</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>$725,000.00</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>509-18-83</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>$725,000.00</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>024-0637955</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>20260228010</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228010</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228010.pdf</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228010.pdf</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>ocr_fallback</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228010.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260228017</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rene Campa, an unmarried woman, and Sebastian Campa, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>$368,207.00</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>5214 W Cholla St</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85304</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>$368,207.00</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2023023536</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>05/05/2023</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>20230235369</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228017</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228017.pdf</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228017.pdf</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>ocr_fallback</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228017.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260228048</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lynda Peretz, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>$187,000.00</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>325 E. Anderson Ave.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>$187,000.00</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>008-0102507</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>02/05/2008</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>20080235349</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228048</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228048.pdf</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228048.pdf</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>ocr_fallback</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228048.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260228059</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>RICHARDO MONTES IBARBOL AND ABAGAIL ALEXXIS MENDEZ AND MARIA THERESA IBARBOL CRUZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>$380,972.00</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>201 W. JEFFERSON STREET</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>85003</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>152-19-145</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>$380,972.00</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>9/1/2023</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>20230467168</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228059</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228059.pdf</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228059.pdf</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>ocr_fallback</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>50</v>
       </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225555.txt</t>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228059.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260228370</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>YAVIN JAY CRANSHAW, A SINGLE MAN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>$363,298.00</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4454 W PIUTE AVE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>$363,298.00</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2021090453</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>08/20/2021</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>20210904536</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228370</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228370.pdf</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228370.pdf</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>ocr_fallback</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228370.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260228380</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JUAN CARRANZA, UNMARRIED</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>$286,805.00</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>19559 W LINCOLN STREET</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>BUCKEYE</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>$286,805.00</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2019073407</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>09/18/2019</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>20190734079</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228380</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228380.pdf</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228380.pdf</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>ocr_fallback</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228380.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260228499</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>(s): BLANCA M ARMENTA QUINONEZ, AN UNMARRIED WOMAN AND MICHAEL G ARMENTA, AN UNMARRIED MAN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>$280,819.00</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2108 W HADLEY ST</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>109-64-004</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>$280,819.00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2024007620</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>2/14/2024</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>20240076207</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228499</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228499.pdf</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228499.pdf</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>ocr_fallback</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228499.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260228514</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>(s): Andrew S Kulin and Kasie M Lambros, husband and wife as community property with rights of survivorship</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>$372,000.00</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1923 E PRESIDIO RD</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>166-41-057</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>$372,000.00</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2021094267</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>8/30/2021</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>20210942675</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228514</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228514.pdf</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228514.pdf</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>ocr_fallback</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>50</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228514.txt</t>
         </is>
       </c>
     </row>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -421,12 +421,12 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="29" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -434,10 +434,10 @@
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
@@ -446,10 +446,10 @@
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="60" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
-    <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,38 +650,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>STERLING M. GRANT</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>$236,880.00</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>19079 E SEAGULL DR</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>QUEEN CREEK</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>85142</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -691,32 +667,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>314-05-709</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>$236,880.00</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>8/8/2018</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>20180610512</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -731,24 +687,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225916.pdf</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225916.pdf</t>
-        </is>
-      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225916.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -776,38 +724,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>RONALD HODNE, AN UNMARRIED MAN, AND LA TOYA GUEVARA, AN UNMARRIED WOMAN</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>$690,900.00</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>13910 S 180TH AVE</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>GOODYEAR</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>85338</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -817,32 +741,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>400-82-358</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>$690,900.00</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2023057015</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>20230570155</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -857,24 +761,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226177.pdf</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226177.pdf</t>
-        </is>
-      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226177.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -902,38 +798,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>BRIAN JAMISON</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>$330,000.00</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>8126 W WATKINS ST</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>85043</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -943,32 +815,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>104-33-181</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>$330,000.00</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>6/3/2021</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>20210626779</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -983,24 +835,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226185.pdf</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226185.pdf</t>
-        </is>
-      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226185.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1028,38 +872,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CANDICE AUGE AND TODD AUGE</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$285,000.00</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>4202 E EVERETT DR</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>85032</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -1069,32 +889,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>215-71-184</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>$285,000.00</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>3/3/2022</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>20220200328</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1109,24 +909,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226190.pdf</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226190.pdf</t>
-        </is>
-      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226190.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1154,38 +946,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HELEN E CHARLES</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>$246,500.00</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>9810 N BALBOA DR</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>SUN CITY</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>85351</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1195,32 +963,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>142-84-801</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>$246,500.00</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>7/29/2021</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>20210829918</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1235,24 +983,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226195.pdf</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226195.pdf</t>
-        </is>
-      </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226195.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1280,38 +1020,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>YOLANDA MCKIM AND BILLY MCKIM, WIFE AND HUSBAND AS COMMUNITY PROPERTY</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>$335,805.00</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>3937 W MYRTLE AVE</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>85051</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1321,32 +1037,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>151-26-142</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>$335,805.00</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2021066036</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>20210660360</t>
-        </is>
-      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
@@ -1361,24 +1057,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226197.pdf</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226197.pdf</t>
-        </is>
-      </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226197.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1406,38 +1094,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ROBERT FARMER</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>$205,128.00</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>14300 W BELL RD UNIT 52</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>SURPRISE</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>85374</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1447,32 +1111,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>503-59-212B</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>$205,128.00</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>3/2/2023</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>20230106079</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1487,24 +1131,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226200.pdf</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226200.pdf</t>
-        </is>
-      </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226200.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1532,38 +1168,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NIRA WANNARKA AND WILLIAM DIXON, WIFE AND HUSBAND</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$381,562.00</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2330 W SPENCER RUN</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1573,32 +1185,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>105-65-525105-65-525</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>$381,562.00</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2022061067</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>20220610672</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1613,24 +1205,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226202.pdf</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226202.pdf</t>
-        </is>
-      </c>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226202.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1658,38 +1242,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust) GOOD NEWS GROUP, LLC, AN ARIZONA LIMITED LIABILITY COMPANY AND ROSS FERRARO AND EMILY FERRARO</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>$374,000.00</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -1699,32 +1259,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>155-53-014</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>$374,000.00</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>949-427-2010</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>4/26/2023</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>20230215291</t>
-        </is>
-      </c>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -1739,24 +1279,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226317.pdf</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226317.pdf</t>
-        </is>
-      </c>
+      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226317.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1784,38 +1316,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CAROLINE ANN BRICKELL AND SEAN GENZMER</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>$252,340.00</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>21003 N 123RD DR</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>SUN CITY WEST</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>85375</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1825,32 +1333,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>232-14-036</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>$252,340.00</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>12/23/2021</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>20211376027</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
@@ -1865,24 +1353,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226412.pdf</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226412.pdf</t>
-        </is>
-      </c>
+      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226412.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1910,38 +1390,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>$238,500.00</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>11122 W Montana Ave.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Youngtown</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>85363</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1951,28 +1407,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Numbers</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>$238,500.00</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>024-0111013</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>20260226657</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -1987,24 +1427,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226657.pdf</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226657.pdf</t>
-        </is>
-      </c>
+      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226657.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2032,38 +1464,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>BOBBI SCHULTZ AS</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$275,000.00</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>10437 W CHERYL DR</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>SUN, CITY</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>85351</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -2073,32 +1481,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>$275,000.00</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2022071684</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>09/16/2022</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>20220716841</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -2113,24 +1501,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226771.pdf</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226771.pdf</t>
-        </is>
-      </c>
+      <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226771.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2158,38 +1538,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>LUIS ALONSO MIRANDA GOMEZ, A MARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>$122,042.00</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>520 E HARRISON DR</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>AVONDALE</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>85323</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2199,32 +1555,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>$122,042.00</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2018083116</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>11/07/2018</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>20180831169</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
@@ -2239,24 +1575,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226956.pdf</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226956.pdf</t>
-        </is>
-      </c>
+      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226956.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2284,38 +1612,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON, HUSBAND AND WIFE AND ANTHONY DE LEON, AN UNMARRIED MAN</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>$323,000.00</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>30306 WEST PORTLAND STREET</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>BUCKEYE</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>85396</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -2325,32 +1629,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>504-15-159</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>$323,000.00</t>
-        </is>
-      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2022084779</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>20220847791</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
@@ -2365,24 +1649,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226960.pdf</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226960.pdf</t>
-        </is>
-      </c>
+      <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226960.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2410,38 +1686,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>JASON DANIEL MURRAY AND AMBER MURRAY, HUSBAND AND WIFE AS JOINT TENANTS WITH RIGHT OF SURVIVORSHIP</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>$235,653.00</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>3307 W ECHO LN</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>85051</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -2451,32 +1703,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>$235,653.00</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2022086524</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>11/30/2022</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>20220865242</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
@@ -2491,24 +1723,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227028.pdf</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227028.pdf</t>
-        </is>
-      </c>
+      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227028.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2536,38 +1760,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>JORDAN OLIVA, A SINGLE MAN</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>$427,696.00</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>22229 E VIA DEL PALO</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>QUEEN, CREEK</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>85142</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -2577,32 +1777,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>$427,696.00</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2021116172</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>10/28/2021</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>20211161722</t>
-        </is>
-      </c>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
@@ -2617,24 +1797,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227091.pdf</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227091.pdf</t>
-        </is>
-      </c>
+      <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227091.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2662,38 +1834,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>RUSTY ROBERTS AND NICHOLE ROBERTS, HUSBAND AND WIFE</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>$1,138,564.00</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>8145 W CAMINO DE ORO</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>PEORIA</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>85383</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -2703,32 +1851,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>$1,138,564.00</t>
-        </is>
-      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2023015469</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>03/28/2023</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>20230154699</t>
-        </is>
-      </c>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
@@ -2743,24 +1871,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227136.pdf</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227136.pdf</t>
-        </is>
-      </c>
+      <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227136.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2788,38 +1908,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>RYMAX DEVELOPMENT, L.L.C., AN ARIZONA LIMITED LIABILITY COMPANY</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>$480,000.00</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>18245 N PIMA ROAD UNIT 1049</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>SCOTTSDALE</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>85040</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -2829,32 +1925,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>113-25-059</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>$480,000.00</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2024056527</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>10/23/2024</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>20240565279</t>
-        </is>
-      </c>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
@@ -2869,24 +1945,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227218.pdf</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227218.pdf</t>
-        </is>
-      </c>
+      <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227218.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2914,17 +1982,9 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>TITAN FAMILY REALESTATE LLC, a Arizona limited liability company</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>$110,000.00</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -2939,32 +1999,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>102-84-270</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>$110,000.00</t>
-        </is>
-      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026001494</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>1/09/2026</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>20260014942</t>
-        </is>
-      </c>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
@@ -2979,24 +2019,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227219.pdf</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227219.pdf</t>
-        </is>
-      </c>
+      <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227219.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3024,17 +2056,9 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Graciela Bucio Perez an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>$176,000.00</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -3049,32 +2073,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>206-20-159</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>$176,000.00</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2024014138</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>3/19/2024</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>20240141383</t>
-        </is>
-      </c>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
@@ -3089,24 +2093,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227220.pdf</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227220.pdf</t>
-        </is>
-      </c>
+      <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227220.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3134,38 +2130,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>JOSEPH VERDUZCO, A MARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>$294,405.00</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2830 S. CHATSWORTH</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>MESA</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>85212</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -3175,32 +2147,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>309-19-162</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>$294,405.00</t>
-        </is>
-      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>2018017439</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>20180174392</t>
-        </is>
-      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
@@ -3215,24 +2167,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227284.pdf</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227284.pdf</t>
-        </is>
-      </c>
+      <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227284.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3260,38 +2204,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>/GRANTOR: (as of the recording of the Notice of</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>$10,000,000.00</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>7508 N. 59th Avenue</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>85301</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -3301,28 +2221,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>IDENTIFIABLE</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>$10,000,000.00</t>
-        </is>
-      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>2024043257</t>
-        </is>
-      </c>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>20240432575</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
@@ -3337,24 +2241,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227302.pdf</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227302.pdf</t>
-        </is>
-      </c>
+      <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227302.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3382,38 +2278,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>(s): BRENDA FAE HUBBARD, A MARRIED WOMAN AS HER SOLE AND SEPARATE PROPERTY</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>$192,449.00</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>9113 E BUTTERNUT AVE</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>MESA</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>85208</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -3423,32 +2295,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>218-41-190</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>$192,449.00</t>
-        </is>
-      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>2022061027</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>7/28/2022</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>20220610270</t>
-        </is>
-      </c>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
@@ -3463,24 +2315,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227512.pdf</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227512.pdf</t>
-        </is>
-      </c>
+      <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227512.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3508,38 +2352,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>(s): ZHONG K WANG AND FRANCIS N PRICE, AND UNMARRIED MAN AND FRANCIS PRICE, AN UNMARRIED WOMAN</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>$200,000.00</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>12546 W MANDALAY LANE</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>EL, MIRAGE</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>85335</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -3549,32 +2369,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>509-13-497</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>$200,000.00</t>
-        </is>
-      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>2019003016</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>1/15/2019</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>20190030161</t>
-        </is>
-      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
@@ -3589,24 +2389,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227521.pdf</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227521.pdf</t>
-        </is>
-      </c>
+      <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227521.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3634,42 +2426,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Wayne Carpenter, a single person</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>$50,000.00</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>7486 S Sundown Ct</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Buckeye</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>85326</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -3680,31 +2444,11 @@
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>$50,000.00</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>2025032204</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>06/04/2025</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>20250322044</t>
-        </is>
-      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
@@ -3719,24 +2463,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227539.pdf</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227539.pdf</t>
-        </is>
-      </c>
+      <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227539.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3764,38 +2500,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>in favor of WELLS FARGO BANK, N.A. as</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>$337,252.80</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>21823 NORTH MAYA COURT</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>SUN CITY WEST</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>85375</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -3805,32 +2517,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>232-31-246</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>$337,252.80</t>
-        </is>
-      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>005-1708272</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>20150216695</t>
-        </is>
-      </c>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
@@ -3845,24 +2537,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227902.pdf</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227902.pdf</t>
-        </is>
-      </c>
+      <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227902.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3890,42 +2574,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Frances Garcia, an unmarried woman</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>$68,000.00</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2802 West Madison Street</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>85009</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -3936,31 +2592,11 @@
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>$68,000.00</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>2007055829</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>05/14/2007</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>20070558292</t>
-        </is>
-      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
@@ -3975,24 +2611,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227926.pdf</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227926.pdf</t>
-        </is>
-      </c>
+      <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227926.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4020,42 +2648,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Luis Vincente Gurrola Martinez, a single man</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>$233,100.00</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>4107 W Krall St</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>85019</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
@@ -4066,31 +2666,11 @@
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>$233,100.00</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>2021064449</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>06/11/2021</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>20210644498</t>
-        </is>
-      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
@@ -4105,24 +2685,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227939.pdf</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227939.pdf</t>
-        </is>
-      </c>
+      <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227939.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4150,42 +2722,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Christine Lea Kurtz-Ford, an unmarried woman</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>$121,000.00</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>630 E Jensen St Unit 138</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>85203</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -4196,31 +2740,11 @@
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>$121,000.00</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2020092366</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>09/29/2020</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>20200923660</t>
-        </is>
-      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
@@ -4235,24 +2759,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227955.pdf</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227955.pdf</t>
-        </is>
-      </c>
+      <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227955.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4280,42 +2796,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Martin V Valadez, a single man and Velazquez David Valadez, a single man</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>$380,000.00</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>3708 West Berridge Lane</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>85019</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
@@ -4326,31 +2814,11 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>$380,000.00</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>2023055878</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>10/27/2023</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>20230558787</t>
-        </is>
-      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
@@ -4365,24 +2833,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227961.pdf</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227961.pdf</t>
-        </is>
-      </c>
+      <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227961.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4410,42 +2870,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Richard L Bristol and Grace A Bristol, husband and wife</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>$149,055.00</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>20803 W Bradley Road</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Wittmann</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>85361</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
@@ -4456,31 +2888,11 @@
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>$149,055.00</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>2016024986</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>04/15/2016</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>20160249869</t>
-        </is>
-      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
@@ -4495,24 +2907,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227974.pdf</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227974.pdf</t>
-        </is>
-      </c>
+      <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227974.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4540,17 +2944,9 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>in which LB Assets 8, LLC, an Arizona limited liability company, is the named</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>$725,000.00</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -4565,28 +2961,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>509-18-83</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>$725,000.00</t>
-        </is>
-      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>024-0637955</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>20260228010</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -4601,24 +2981,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228010.pdf</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228010.pdf</t>
-        </is>
-      </c>
+      <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228010.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4646,42 +3018,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Rene Campa, an unmarried woman, and Sebastian Campa, an unmarried man</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>$368,207.00</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>5214 W Cholla St</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>85304</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
@@ -4692,31 +3036,11 @@
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>$368,207.00</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>2023023536</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>05/05/2023</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>20230235369</t>
-        </is>
-      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
@@ -4731,24 +3055,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228017.pdf</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228017.pdf</t>
-        </is>
-      </c>
+      <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228017.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4776,42 +3092,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Lynda Peretz, an unmarried woman</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>$187,000.00</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>325 E. Anderson Ave.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>85022</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -4822,31 +3110,11 @@
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>$187,000.00</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>008-0102507</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>02/05/2008</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>20080235349</t>
-        </is>
-      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
@@ -4861,24 +3129,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228048.pdf</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228048.pdf</t>
-        </is>
-      </c>
+      <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228048.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4906,38 +3166,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>RICHARDO MONTES IBARBOL AND ABAGAIL ALEXXIS MENDEZ AND MARIA THERESA IBARBOL CRUZ</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>$380,972.00</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>201 W. JEFFERSON STREET</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
@@ -4947,32 +3183,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>152-19-145</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>$380,972.00</t>
-        </is>
-      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>9/1/2023</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>20230467168</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
@@ -4987,24 +3203,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228059.pdf</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228059.pdf</t>
-        </is>
-      </c>
+      <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228059.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5032,38 +3240,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>YAVIN JAY CRANSHAW, A SINGLE MAN</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>$363,298.00</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>4454 W PIUTE AVE</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>GLENDALE</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>85308</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -5073,32 +3257,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>$363,298.00</t>
-        </is>
-      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>2021090453</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>08/20/2021</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>20210904536</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
@@ -5113,24 +3277,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228370.pdf</t>
         </is>
       </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228370.pdf</t>
-        </is>
-      </c>
+      <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228370.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5158,38 +3314,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>JUAN CARRANZA, UNMARRIED</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>$286,805.00</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>19559 W LINCOLN STREET</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>BUCKEYE</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>85326</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
@@ -5199,32 +3331,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>$286,805.00</t>
-        </is>
-      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>2019073407</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>09/18/2019</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>20190734079</t>
-        </is>
-      </c>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
@@ -5239,24 +3351,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228380.pdf</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228380.pdf</t>
-        </is>
-      </c>
+      <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228380.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5284,38 +3388,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>(s): BLANCA M ARMENTA QUINONEZ, AN UNMARRIED WOMAN AND MICHAEL G ARMENTA, AN UNMARRIED MAN</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>$280,819.00</t>
-        </is>
-      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2108 W HADLEY ST</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>85009</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
@@ -5325,32 +3405,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>109-64-004</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>$280,819.00</t>
-        </is>
-      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>2024007620</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>2/14/2024</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>20240076207</t>
-        </is>
-      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
@@ -5365,24 +3425,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228499.pdf</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228499.pdf</t>
-        </is>
-      </c>
+      <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228499.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5410,38 +3462,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>(s): Andrew S Kulin and Kasie M Lambros, husband and wife as community property with rights of survivorship</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>$372,000.00</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>1923 E PRESIDIO RD</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>85022</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
@@ -5451,32 +3479,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>166-41-057</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>$372,000.00</t>
-        </is>
-      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>2021094267</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>8/30/2021</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>20210942675</t>
-        </is>
-      </c>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -5491,24 +3499,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228514.pdf</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228514.pdf</t>
-        </is>
-      </c>
+      <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228514.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -444,7 +444,7 @@
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="14" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
-    <col width="60" customWidth="1" min="29" max="29"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
@@ -677,11 +677,7 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260225916</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225916.pdf</t>
@@ -751,11 +747,7 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226177</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226177.pdf</t>
@@ -825,11 +817,7 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226185</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226185.pdf</t>
@@ -899,11 +887,7 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226190</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226190.pdf</t>
@@ -973,11 +957,7 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226195</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226195.pdf</t>
@@ -1047,11 +1027,7 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226197</t>
-        </is>
-      </c>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226197.pdf</t>
@@ -1121,11 +1097,7 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226200</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226200.pdf</t>
@@ -1195,11 +1167,7 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226202</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226202.pdf</t>
@@ -1269,11 +1237,7 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226317</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226317.pdf</t>
@@ -1343,11 +1307,7 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226412</t>
-        </is>
-      </c>
+      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226412.pdf</t>
@@ -1417,11 +1377,7 @@
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226657</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226657.pdf</t>
@@ -1491,11 +1447,7 @@
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226771</t>
-        </is>
-      </c>
+      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226771.pdf</t>
@@ -1565,11 +1517,7 @@
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226956</t>
-        </is>
-      </c>
+      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226956.pdf</t>
@@ -1639,11 +1587,7 @@
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260226960</t>
-        </is>
-      </c>
+      <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226960.pdf</t>
@@ -1713,11 +1657,7 @@
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227028</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227028.pdf</t>
@@ -1787,11 +1727,7 @@
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227091</t>
-        </is>
-      </c>
+      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227091.pdf</t>
@@ -1861,11 +1797,7 @@
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227136</t>
-        </is>
-      </c>
+      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227136.pdf</t>
@@ -1935,11 +1867,7 @@
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227218</t>
-        </is>
-      </c>
+      <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227218.pdf</t>
@@ -2009,11 +1937,7 @@
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227219</t>
-        </is>
-      </c>
+      <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227219.pdf</t>
@@ -2083,11 +2007,7 @@
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227220</t>
-        </is>
-      </c>
+      <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227220.pdf</t>
@@ -2157,11 +2077,7 @@
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227284</t>
-        </is>
-      </c>
+      <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227284.pdf</t>
@@ -2231,11 +2147,7 @@
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227302</t>
-        </is>
-      </c>
+      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227302.pdf</t>
@@ -2305,11 +2217,7 @@
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227512</t>
-        </is>
-      </c>
+      <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227512.pdf</t>
@@ -2379,11 +2287,7 @@
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227521</t>
-        </is>
-      </c>
+      <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227521.pdf</t>
@@ -2453,11 +2357,7 @@
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227539</t>
-        </is>
-      </c>
+      <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227539.pdf</t>
@@ -2527,11 +2427,7 @@
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227902</t>
-        </is>
-      </c>
+      <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227902.pdf</t>
@@ -2601,11 +2497,7 @@
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227926</t>
-        </is>
-      </c>
+      <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227926.pdf</t>
@@ -2675,11 +2567,7 @@
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227939</t>
-        </is>
-      </c>
+      <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227939.pdf</t>
@@ -2749,11 +2637,7 @@
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227955</t>
-        </is>
-      </c>
+      <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227955.pdf</t>
@@ -2823,11 +2707,7 @@
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227961</t>
-        </is>
-      </c>
+      <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227961.pdf</t>
@@ -2897,11 +2777,7 @@
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260227974</t>
-        </is>
-      </c>
+      <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227974.pdf</t>
@@ -2971,11 +2847,7 @@
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228010</t>
-        </is>
-      </c>
+      <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228010.pdf</t>
@@ -3045,11 +2917,7 @@
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228017</t>
-        </is>
-      </c>
+      <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228017.pdf</t>
@@ -3119,11 +2987,7 @@
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228048</t>
-        </is>
-      </c>
+      <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228048.pdf</t>
@@ -3193,11 +3057,7 @@
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228059</t>
-        </is>
-      </c>
+      <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228059.pdf</t>
@@ -3267,11 +3127,7 @@
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228370</t>
-        </is>
-      </c>
+      <c r="AC37" t="inlineStr"/>
       <c r="AD37" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228370.pdf</t>
@@ -3341,11 +3197,7 @@
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228380</t>
-        </is>
-      </c>
+      <c r="AC38" t="inlineStr"/>
       <c r="AD38" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228380.pdf</t>
@@ -3415,11 +3267,7 @@
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228499</t>
-        </is>
-      </c>
+      <c r="AC39" t="inlineStr"/>
       <c r="AD39" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228499.pdf</t>
@@ -3489,11 +3337,7 @@
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>https://recorder.maricopa.gov/recording/document-details?id=20260228514</t>
-        </is>
-      </c>
+      <c r="AC40" t="inlineStr"/>
       <c r="AD40" t="inlineStr">
         <is>
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228514.pdf</t>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -421,12 +421,12 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -434,10 +434,10 @@
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
@@ -446,10 +446,10 @@
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,14 +650,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>STERLING M. GRANT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Trust dated 8/8/2018 and recorded on 8/13/2018, as Instrument No. 20180610512, in the office of the County</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>$236,880.00</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19079 E SEAGULL DR</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -667,12 +695,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>314-05-709</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>$236,880.00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Trust dated 8/8/2018 and recorded on 8/13/2018, as Instrument No. 20180610512, in the office of the County</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>8/8/2018</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>20180610512</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -683,16 +735,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225916.pdf</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225916.pdf</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225916.txt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -720,14 +780,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RONALD HODNE, AN UNMARRIED MAN, AND LA TOYA GUEVARA, AN UNMARRIED WOMAN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>$690,900.00</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13910 S 180TH AVE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -737,12 +825,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>400-82-358</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>$690,900.00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2023057015</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>20230570155</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -753,16 +865,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226177.pdf</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226177.pdf</t>
+        </is>
+      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226177.txt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -790,14 +910,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BRIAN JAMISON</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Trust dated 6/3/2021 and recorded on 6/7/2021, as Instrument No. 20210626779, the subject Deed of Trust was</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>$330,000.00</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8126 W WATKINS ST</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85043</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -807,12 +955,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>104-33-181</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>$330,000.00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Trust dated 6/3/2021 and recorded on 6/7/2021, as Instrument No. 20210626779, the subject Deed of Trust was</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>20210626779</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -823,16 +995,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226185.pdf</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226185.pdf</t>
+        </is>
+      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226185.txt</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -860,14 +1040,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CANDICE AUGE AND TODD AUGE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trust dated 3/3/2022 and recorded on 3/4/2022, as Instrument No. 20220200328, in the office of the County</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4202 E EVERETT DR</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85032</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -877,12 +1085,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>215-71-184</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Trust dated 3/3/2022 and recorded on 3/4/2022, as Instrument No. 20220200328, in the office of the County</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>20220200328</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -893,16 +1125,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226190.pdf</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226190.pdf</t>
+        </is>
+      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226190.txt</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -930,14 +1170,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HELEN E CHARLES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Trust dated 7/29/2021 and recorded on 7/30/2021, as Instrument No. 20210829918, in the office of the County</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>$246,500.00</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>9810 N BALBOA DR</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SUN CITY</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -947,12 +1215,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>142-84-801</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>$246,500.00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Trust dated 7/29/2021 and recorded on 7/30/2021, as Instrument No. 20210829918, in the office of the County</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>20210829918</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -963,16 +1255,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226195.pdf</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226195.pdf</t>
+        </is>
+      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226195.txt</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1000,14 +1300,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YOLANDA MCKIM AND BILLY MCKIM, WIFE AND HUSBAND AS COMMUNITY PROPERTY</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>$335,805.00</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3937 W MYRTLE AVE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1017,12 +1345,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>151-26-142</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>$335,805.00</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2021066036</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>20210660360</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
@@ -1033,16 +1385,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226197.pdf</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226197.pdf</t>
+        </is>
+      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226197.txt</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1070,14 +1430,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ROBERT FARMER</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Trust dated 3/2/2023 and recorded on 3/2/2023, as Instrument No. 20230106079, in the office of the County</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>$205,128.00</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14300 W BELL RD UNIT 52</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SURPRISE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85374</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1087,12 +1475,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>503-59-212B</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>$205,128.00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Trust dated 3/2/2023 and recorded on 3/2/2023, as Instrument No. 20230106079, in the office of the County</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>20230106079</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1103,16 +1515,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226200.pdf</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226200.pdf</t>
+        </is>
+      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226200.txt</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1140,14 +1560,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NIRA WANNARKA AND WILLIAM DIXON, WIFE AND HUSBAND</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$381,562.00</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2330 W SPENCER RUN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1157,12 +1605,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>105-65-525105-65-525</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>$381,562.00</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2022061067</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>20220610672</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1173,16 +1645,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226202.pdf</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226202.pdf</t>
+        </is>
+      </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226202.txt</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1210,9 +1690,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GOOD NEWS GROUP, LLC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Deed of Trust dated 4/26/2023 and recorded on 4/27/2023 as Instrument # 20230215291, in the office of the County</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>$374,000.00</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1227,12 +1719,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>155-53-014</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>$374,000.00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Deed of Trust dated 4/26/2023 and recorded on 4/27/2023 as Instrument # 20230215291, in the office of the County</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>949-427-2010</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>4/26/2023</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>20230215291</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -1243,16 +1759,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226317.pdf</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226317.pdf</t>
+        </is>
+      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226317.txt</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1280,14 +1804,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CAROLINE ANN BRICKELL AND SEAN GENZMER</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Trust dated 12/23/2021 and recorded on 12/29/2021, as Instrument No. 20211376027, in the office of the County</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>$252,340.00</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>21003 N 123RD DR</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1297,12 +1849,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>232-14-036</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>$252,340.00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Trust dated 12/23/2021 and recorded on 12/29/2021, as Instrument No. 20211376027, in the office of the County</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>7/30/2026</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>20211376027</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
@@ -1313,16 +1889,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226412.pdf</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226412.pdf</t>
+        </is>
+      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226412.txt</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1350,14 +1934,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>that certain Deed of Trust and Assignment of Rents ("Deed of Trust") dated February 29, 2024</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>$238,500.00</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11122 W Montana Ave.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Youngtown</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85363</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1367,12 +1979,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Numbers</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>$238,500.00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>that certain Deed of Trust and Assignment of Rents ("Deed of Trust") dated February 29, 2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>024-0111013</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>20260226657</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -1383,16 +2015,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226657.pdf</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226657.pdf</t>
+        </is>
+      </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226657.txt</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1420,14 +2060,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BOBBI SCHULTZ AS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 09/16/2022 in Instrument No. 20220716841, records of MARICOPA County</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$275,000.00</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10437 W CHERYL DR</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SUN, CITY</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1437,12 +2105,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>$275,000.00</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 09/16/2022 in Instrument No. 20220716841, records of MARICOPA County</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2022071684</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>09/16/2022</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>20220716841</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -1453,16 +2145,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226771.pdf</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226771.pdf</t>
+        </is>
+      </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226771.txt</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1490,14 +2190,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>LUIS ALONSO MIRANDA GOMEZ, A MARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 11/07/2018 in Instrument No. 20180831169, records of MARICOPA County</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>$122,042.00</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>520 E HARRISON DR</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>AVONDALE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -1507,12 +2235,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>$122,042.00</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 11/07/2018 in Instrument No. 20180831169, records of MARICOPA County</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2018083116</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>11/07/2018</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>20180831169</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
@@ -1523,16 +2275,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226956.pdf</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226956.pdf</t>
+        </is>
+      </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226956.txt</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1560,14 +2320,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON, HUSBAND AND WIFE AND ANTHONY DE LEON, AN UNMARRIED MAN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>$323,000.00</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30306 WEST PORTLAND STREET</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>BUCKEYE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85396</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1577,12 +2365,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>504-15-159</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>$323,000.00</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2022084779</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>20220847791</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
@@ -1593,16 +2405,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226960.pdf</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226960.pdf</t>
+        </is>
+      </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226960.txt</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1630,14 +2450,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JASON DANIEL MURRAY AND AMBER MURRAY, HUSBAND AND WIFE AS JOINT TENANTS WITH RIGHT OF SURVIVORSHIP</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 11/30/2022 in Instrument No. 20220865242, records of MARICOPA County</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>$235,653.00</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3307 W ECHO LN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1647,12 +2495,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>$235,653.00</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 11/30/2022 in Instrument No. 20220865242, records of MARICOPA County</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2022086524</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>11/30/2022</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>20220865242</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
@@ -1663,16 +2535,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227028.pdf</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227028.pdf</t>
+        </is>
+      </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227028.txt</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1700,14 +2580,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>JORDAN OLIVA, A SINGLE MAN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 10/28/2021 in Instrument No. 20211161722, records of MARICOPA County</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$427,696.00</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22229 E VIA DEL PALO</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>QUEEN, CREEK</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -1717,12 +2625,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>$427,696.00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 10/28/2021 in Instrument No. 20211161722, records of MARICOPA County</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2021116172</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>10/28/2021</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>20211161722</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
@@ -1733,16 +2665,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227091.pdf</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227091.pdf</t>
+        </is>
+      </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227091.txt</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1770,14 +2710,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RUSTY ROBERTS AND NICHOLE ROBERTS, HUSBAND AND WIFE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 03/28/2023 in Instrument No. 20230154699, Book XX, Page XX, records of</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>$1,138,564.00</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8145 W CAMINO DE ORO</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PEORIA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85383</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -1787,12 +2755,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>$1,138,564.00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 03/28/2023 in Instrument No. 20230154699, Book XX, Page XX, records of</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2023015469</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>03/28/2023</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>20230154699</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
@@ -1803,16 +2795,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227136.pdf</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227136.pdf</t>
+        </is>
+      </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227136.txt</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1840,14 +2840,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>RYMAX DEVELOPMENT, L.L.C.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>TS# 26-055 Loan Number: 13124</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>$480,000.00</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18245 N PIMA ROAD UNIT 1049</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SCOTTSDALE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -1857,12 +2885,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>113-25-059</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>$480,000.00</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>TS# 26-055 Loan Number: 13124</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2024056527</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>10/23/2024</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>20240565279</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
@@ -1873,16 +2925,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227218.pdf</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227218.pdf</t>
+        </is>
+      </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227218.txt</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1910,9 +2970,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TITAN FAMILY REALESTATE LLC</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>TS# 26-074 Loan No. 71617</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>$110,000.00</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1927,12 +2999,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>102-84-270</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>$110,000.00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>TS# 26-074 Loan No. 71617</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026001494</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1/09/2026</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>20260014942</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
@@ -1943,16 +3039,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227219.pdf</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227219.pdf</t>
+        </is>
+      </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227219.txt</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1980,9 +3084,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Graciela Bucio Perez an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>TS# 26-075 Loan No. 40366</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>$176,000.00</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1997,12 +3113,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>206-20-159</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>$176,000.00</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>TS# 26-075 Loan No. 40366</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2024014138</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>3/19/2024</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>20240141383</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
@@ -2013,16 +3153,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227220.pdf</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227220.pdf</t>
+        </is>
+      </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227220.txt</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2050,14 +3198,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JOSEPH VERDUZCO, A MARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>$294,405.00</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2830 S. CHATSWORTH</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85212</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -2067,12 +3243,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>309-19-162</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>$294,405.00</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Corps</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2018017439</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>20180174392</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
@@ -2083,16 +3283,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227284.pdf</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227284.pdf</t>
+        </is>
+      </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227284.txt</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2120,14 +3328,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>/GRANTOR: (as of the recording of the Notice of</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>under that certain Deed of Trust, Assignment of Leases and Rents and Security Agreement</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>$10,000,000.00</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7508 N. 59th Avenue</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -2137,12 +3373,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>IDENTIFIABLE</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>$10,000,000.00</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>under that certain Deed of Trust, Assignment of Leases and Rents and Security Agreement</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2024043257</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>20240432575</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
@@ -2153,16 +3409,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227302.pdf</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227302.pdf</t>
+        </is>
+      </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227302.txt</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2190,14 +3454,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BRENDA FAE HUBBARD, A MARRIED WOMAN AS HER SOLE AND SEPARATE PROPERTY</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Trust dated 7/28/2022 and recorded 7/29/2022 as Instrument No. 20220610270 in the office of the County</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>$192,449.00</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>9113 E BUTTERNUT AVE</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>85208</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -2207,12 +3499,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>218-41-190</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>$192,449.00</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Trust dated 7/28/2022 and recorded 7/29/2022 as Instrument No. 20220610270 in the office of the County</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2022061027</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>20220610270</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
@@ -2223,16 +3539,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227512.pdf</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227512.pdf</t>
+        </is>
+      </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227512.txt</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2260,14 +3584,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ZHONG K WANG AND FRANCIS N PRICE, AND UNMARRIED MAN AND FRANCIS PRICE, AN UNMARRIED WOMAN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Trust dated 1/15/2019 and recorded 1/15/2019 as Instrument No. 20190030161 in the office of the County</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>$200,000.00</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>12546 W MANDALAY LANE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>EL, MIRAGE</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -2277,12 +3629,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>509-13-497</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>$200,000.00</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Trust dated 1/15/2019 and recorded 1/15/2019 as Instrument No. 20190030161 in the office of the County</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2019003016</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>20190030161</t>
+        </is>
+      </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
@@ -2293,16 +3669,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227521.pdf</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227521.pdf</t>
+        </is>
+      </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227521.txt</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2330,14 +3714,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Wayne Carpenter, a single person</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>$50,000.00</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>7486 S Sundown Ct</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -2348,11 +3760,31 @@
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>$50,000.00</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2025032204</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>06/04/2025</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>20250322044</t>
+        </is>
+      </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
@@ -2363,16 +3795,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227539.pdf</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227539.pdf</t>
+        </is>
+      </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227539.txt</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2400,14 +3840,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>in favor of WELLS FARGO BANK, N.A. as</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CORPS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>$337,252.80</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>21823 NORTH MAYA COURT</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -2417,12 +3885,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>232-31-246</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>$337,252.80</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>CORPS</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>005-1708272</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>08/29/2024</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>20150216695</t>
+        </is>
+      </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
@@ -2433,16 +3925,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227902.pdf</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227902.pdf</t>
+        </is>
+      </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227902.txt</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2470,14 +3970,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Frances Garcia, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>$68,000.00</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2802 West Madison Street</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -2488,11 +4016,31 @@
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>$68,000.00</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2007055829</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>05/14/2007</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>20070558292</t>
+        </is>
+      </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
@@ -2503,16 +4051,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227926.pdf</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227926.pdf</t>
+        </is>
+      </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227926.txt</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2540,14 +4096,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Luis Vincente Gurrola Martinez, a single man</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>$233,100.00</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4107 W Krall St</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
@@ -2558,11 +4142,31 @@
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>$233,100.00</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2021064449</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>06/11/2021</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>20210644498</t>
+        </is>
+      </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
@@ -2573,16 +4177,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227939.pdf</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227939.pdf</t>
+        </is>
+      </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227939.txt</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2610,14 +4222,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Christine Lea Kurtz-Ford, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>$121,000.00</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>630 E Jensen St Unit 138</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85203</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -2628,11 +4268,31 @@
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>$121,000.00</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2020092366</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>09/29/2020</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>20200923660</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
@@ -2643,16 +4303,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227955.pdf</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227955.pdf</t>
+        </is>
+      </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227955.txt</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2680,14 +4348,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Martin V Valadez, a single man and Velazquez David Valadez, a single man</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>$380,000.00</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3708 West Berridge Lane</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
@@ -2698,11 +4394,31 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>$380,000.00</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2023055878</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>10/27/2023</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>20230558787</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
@@ -2713,16 +4429,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227961.pdf</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227961.pdf</t>
+        </is>
+      </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227961.txt</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2750,14 +4474,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Richard L Bristol and Grace A Bristol, husband and wife</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>$149,055.00</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>20803 W Bradley Road</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Wittmann</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>85361</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
@@ -2768,11 +4520,31 @@
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>$149,055.00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2016024986</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>04/15/2016</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>20160249869</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
@@ -2783,16 +4555,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227974.pdf</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227974.pdf</t>
+        </is>
+      </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227974.txt</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2820,9 +4600,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>in which LB Assets 8, LLC</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>of Trust dated September 23, 2024, and recorded in the Maricopa County Recorder's Office</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>$725,000.00</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2837,12 +4629,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>509-18-83</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>$725,000.00</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>of Trust dated September 23, 2024, and recorded in the Maricopa County Recorder's Office</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>024-0637955</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>20260228010</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -2853,16 +4665,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228010.pdf</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228010.pdf</t>
+        </is>
+      </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228010.txt</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2890,14 +4710,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rene Campa, an unmarried woman, and Sebastian Campa, an unmarried man</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>$368,207.00</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>5214 W Cholla St</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85304</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
@@ -2908,11 +4756,31 @@
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>$368,207.00</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2023023536</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>05/05/2023</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>20230235369</t>
+        </is>
+      </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
@@ -2923,16 +4791,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228017.pdf</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228017.pdf</t>
+        </is>
+      </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228017.txt</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2960,14 +4836,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lynda Peretz, an unmarried woman</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>$187,000.00</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>325 E. Anderson Ave.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -2978,11 +4882,31 @@
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>$187,000.00</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>008-0102507</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>02/05/2008</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>20080235349</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
@@ -2993,16 +4917,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228048.pdf</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228048.pdf</t>
+        </is>
+      </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228048.txt</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3030,9 +4962,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>RICHARDO MONTES IBARBOL AND ABAGAIL ALEXXIS MENDEZ AND MARIA THERESA IBARBOL CRUZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Trust dated 9/1/2023 and recorded on 9/6/2023, as Instrument No. 20230467168, in the office of the County</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>$380,972.00</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -3047,12 +4991,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>152-19-145</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>$380,972.00</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Trust dated 9/1/2023 and recorded on 9/6/2023, as Instrument No. 20230467168, in the office of the County</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>9/1/2023</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>20230467168</t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
@@ -3063,16 +5031,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228059.pdf</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228059.pdf</t>
+        </is>
+      </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228059.txt</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3100,14 +5076,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>YAVIN JAY CRANSHAW, A SINGLE MAN</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 08/20/2021 in Instrument No. 20210904536, Book XX, Page XX, records of</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>$363,298.00</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4454 W PIUTE AVE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -3117,12 +5121,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>$363,298.00</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 08/20/2021 in Instrument No. 20210904536, Book XX, Page XX, records of</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2021090453</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>08/20/2021</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>20210904536</t>
+        </is>
+      </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
@@ -3133,16 +5161,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228370.pdf</t>
         </is>
       </c>
-      <c r="AE37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228370.pdf</t>
+        </is>
+      </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228370.txt</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3170,14 +5206,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JUAN CARRANZA, UNMARRIED</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 09/18/2019 in Instrument No. 20190734079, Book XX, Page XX, records of</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>$286,805.00</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>19559 W LINCOLN STREET</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>BUCKEYE</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
@@ -3187,12 +5251,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>$286,805.00</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Deed of Trust recorded on 09/18/2019 in Instrument No. 20190734079, Book XX, Page XX, records of</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2019073407</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>09/18/2019</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>20190734079</t>
+        </is>
+      </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
@@ -3203,16 +5291,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228380.pdf</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228380.pdf</t>
+        </is>
+      </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228380.txt</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3240,14 +5336,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BLANCA M ARMENTA QUINONEZ, AN UNMARRIED WOMAN AND MICHAEL G ARMENTA, AN UNMARRIED MAN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Trust dated 2/14/2024 and recorded 2/14/2024 as Instrument No. 20240076207 — in the office of the County</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>$280,819.00</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2108 W HADLEY ST</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
@@ -3257,12 +5381,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>109-64-004</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>$280,819.00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Trust dated 2/14/2024 and recorded 2/14/2024 as Instrument No. 20240076207 — in the office of the County</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2024007620</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>20240076207</t>
+        </is>
+      </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
@@ -3273,16 +5421,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228499.pdf</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228499.pdf</t>
+        </is>
+      </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228499.txt</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3310,14 +5466,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Andrew S Kulin and Kasie M Lambros, husband and wife as community property with rights of survivorship</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Trust dated 8/30/2021 and recorded 8/31/2021 as Instrument No, 20210942675 — in the office of the County</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>$372,000.00</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1923 E PRESIDIO RD</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
@@ -3327,12 +5511,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>166-41-057</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>$372,000.00</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Trust dated 8/30/2021 and recorded 8/31/2021 as Instrument No, 20210942675 — in the office of the County</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2021094267</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>20210942675</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -3343,16 +5551,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228514.pdf</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228514.pdf</t>
+        </is>
+      </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228514.txt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -447,7 +447,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -657,7 +657,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trust dated 8/8/2018 and recorded on 8/13/2018, as Instrument No. 20180610512, in the office of the County</t>
+          <t>CURRENT BENEFICIARY</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Trust dated 8/8/2018 and recorded on 8/13/2018, as Instrument No. 20180610512, in the office of the County</t>
+          <t>CURRENT BENEFICIARY</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -715,11 +715,7 @@
           <t>(866) 931-0036</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>8/8/2018</t>
-        </is>
-      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>20180610512</t>
@@ -742,7 +738,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -787,7 +783,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,7 +833,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -845,11 +841,7 @@
           <t>2023057015</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>20230570155</t>
@@ -872,7 +864,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -917,7 +909,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trust dated 6/3/2021 and recorded on 6/7/2021, as Instrument No. 20210626779, the subject Deed of Trust was</t>
+          <t>CURRENT BENEFICIARY</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -967,7 +959,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Trust dated 6/3/2021 and recorded on 6/7/2021, as Instrument No. 20210626779, the subject Deed of Trust was</t>
+          <t>CURRENT BENEFICIARY</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1047,7 +1039,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trust dated 3/3/2022 and recorded on 3/4/2022, as Instrument No. 20220200328, in the office of the County</t>
+          <t>CURRENT BENEFICIARY</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1097,7 +1089,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Trust dated 3/3/2022 and recorded on 3/4/2022, as Instrument No. 20220200328, in the office of the County</t>
+          <t>CURRENT BENEFICIARY</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1177,7 +1169,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trust dated 7/29/2021 and recorded on 7/30/2021, as Instrument No. 20210829918, in the office of the County</t>
+          <t>ORIGINAL TRUSTOR</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1227,7 +1219,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Trust dated 7/29/2021 and recorded on 7/30/2021, as Instrument No. 20210829918, in the office of the County</t>
+          <t>ORIGINAL TRUSTOR</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1307,7 +1299,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1357,7 +1349,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1365,11 +1357,7 @@
           <t>2021066036</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>20210660360</t>
@@ -1392,7 +1380,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG7" t="n">
@@ -1437,7 +1425,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Trust dated 3/2/2023 and recorded on 3/2/2023, as Instrument No. 20230106079, in the office of the County</t>
+          <t>THE FOLLOWING INFORMATION IS PROVIDED PURSUANT TO A.R.S. SECTION 33-808(C)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1487,7 +1475,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Trust dated 3/2/2023 and recorded on 3/2/2023, as Instrument No. 20230106079, in the office of the County</t>
+          <t>THE FOLLOWING INFORMATION IS PROVIDED PURSUANT TO A.R.S. SECTION 33-808(C)</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1567,7 +1555,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1617,7 +1605,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1625,11 +1613,7 @@
           <t>2022061067</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>20220610672</t>
@@ -1652,7 +1636,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1697,7 +1681,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Deed of Trust dated 4/26/2023 and recorded on 4/27/2023 as Instrument # 20230215291, in the office of the County</t>
+          <t>’s capacity as a</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1731,7 +1715,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Deed of Trust dated 4/26/2023 and recorded on 4/27/2023 as Instrument # 20230215291, in the office of the County</t>
+          <t>’s capacity as a</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1739,11 +1723,7 @@
           <t>949-427-2010</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>4/26/2023</t>
-        </is>
-      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>20230215291</t>
@@ -1766,7 +1746,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1811,7 +1791,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Trust dated 12/23/2021 and recorded on 12/29/2021, as Instrument No. 20211376027, in the office of the County</t>
+          <t>CURRENT BENEFICIARY</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1861,7 +1841,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Trust dated 12/23/2021 and recorded on 12/29/2021, as Instrument No. 20211376027, in the office of the County</t>
+          <t>CURRENT BENEFICIARY</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1934,14 +1914,10 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>an unmarried woman</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>that certain Deed of Trust and Assignment of Rents ("Deed of Trust") dated February 29, 2024</t>
+          <t>Gilbert, Arizona 85234</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1991,7 +1967,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>that certain Deed of Trust and Assignment of Rents ("Deed of Trust") dated February 29, 2024</t>
+          <t>Gilbert, Arizona 85234</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2022,11 +1998,11 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2060,14 +2036,10 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>BOBBI SCHULTZ AS</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 09/16/2022 in Instrument No. 20220716841, records of MARICOPA County</t>
+          <t>OF THE BOBBI SCHULTZ TRUST UNDER TRUST</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2117,7 +2089,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 09/16/2022 in Instrument No. 20220716841, records of MARICOPA County</t>
+          <t>OF THE BOBBI SCHULTZ TRUST UNDER TRUST</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2125,11 +2097,7 @@
           <t>2022071684</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>09/16/2022</t>
-        </is>
-      </c>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
           <t>20220716841</t>
@@ -2152,11 +2120,11 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2197,7 +2165,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 11/07/2018 in Instrument No. 20180831169, records of MARICOPA County</t>
+          <t>common designation, if any, shown herein.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2247,7 +2215,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 11/07/2018 in Instrument No. 20180831169, records of MARICOPA County</t>
+          <t>common designation, if any, shown herein.</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2255,11 +2223,7 @@
           <t>2018083116</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>11/07/2018</t>
-        </is>
-      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>20180831169</t>
@@ -2282,7 +2246,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG14" t="n">
@@ -2327,7 +2291,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2377,7 +2341,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2385,11 +2349,7 @@
           <t>2022084779</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>20220847791</t>
@@ -2412,7 +2372,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG15" t="n">
@@ -2457,7 +2417,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 11/30/2022 in Instrument No. 20220865242, records of MARICOPA County</t>
+          <t>common designation, if any, shown herein.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2507,7 +2467,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 11/30/2022 in Instrument No. 20220865242, records of MARICOPA County</t>
+          <t>common designation, if any, shown herein.</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2515,11 +2475,7 @@
           <t>2022086524</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>11/30/2022</t>
-        </is>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
           <t>20220865242</t>
@@ -2542,7 +2498,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG16" t="n">
@@ -2587,7 +2543,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 10/28/2021 in Instrument No. 20211161722, records of MARICOPA County</t>
+          <t>common designation, if any, shown herein.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2637,7 +2593,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 10/28/2021 in Instrument No. 20211161722, records of MARICOPA County</t>
+          <t>common designation, if any, shown herein.</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2645,11 +2601,7 @@
           <t>2021116172</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>10/28/2021</t>
-        </is>
-      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>20211161722</t>
@@ -2672,7 +2624,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG17" t="n">
@@ -2717,7 +2669,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 03/28/2023 in Instrument No. 20230154699, Book XX, Page XX, records of</t>
+          <t>common designation, if any, shown herein.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2767,7 +2719,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 03/28/2023 in Instrument No. 20230154699, Book XX, Page XX, records of</t>
+          <t>common designation, if any, shown herein.</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2775,11 +2727,7 @@
           <t>2023015469</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>03/28/2023</t>
-        </is>
-      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
           <t>20230154699</t>
@@ -2802,7 +2750,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG18" t="n">
@@ -2847,7 +2795,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TS# 26-055 Loan Number: 13124</t>
+          <t>602-488-1349 ronaldherb@gmail.com</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2897,7 +2845,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>TS# 26-055 Loan Number: 13124</t>
+          <t>602-488-1349 ronaldherb@gmail.com</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2905,11 +2853,7 @@
           <t>2024056527</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>10/23/2024</t>
-        </is>
-      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
           <t>20240565279</t>
@@ -2932,7 +2876,7 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG19" t="n">
@@ -2977,7 +2921,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TS# 26-074 Loan No. 71617</t>
+          <t>602-488-1349 ronaldherb@gmail.com</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3011,7 +2955,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>TS# 26-074 Loan No. 71617</t>
+          <t>602-488-1349 ronaldherb@gmail.com</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3019,11 +2963,7 @@
           <t>2026001494</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>1/09/2026</t>
-        </is>
-      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>20260014942</t>
@@ -3046,7 +2986,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG20" t="n">
@@ -3091,7 +3031,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TS# 26-075 Loan No. 40366</t>
+          <t>602-488-1349 ronaldherb@gmail.com</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3125,7 +3065,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>TS# 26-075 Loan No. 40366</t>
+          <t>602-488-1349 ronaldherb@gmail.com</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3133,11 +3073,7 @@
           <t>2024014138</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>3/19/2024</t>
-        </is>
-      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
           <t>20240141383</t>
@@ -3160,7 +3096,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG21" t="n">
@@ -3205,7 +3141,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3255,7 +3191,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Corps</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3263,11 +3199,7 @@
           <t>2018017439</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
           <t>20180174392</t>
@@ -3290,7 +3222,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG22" t="n">
@@ -3328,14 +3260,10 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>/GRANTOR: (as of the recording of the Notice of</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>under that certain Deed of Trust, Assignment of Leases and Rents and Security Agreement</t>
+          <t>to the highest bidder</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3385,7 +3313,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>under that certain Deed of Trust, Assignment of Leases and Rents and Security Agreement</t>
+          <t>to the highest bidder</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3416,11 +3344,11 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -3461,7 +3389,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Trust dated 7/28/2022 and recorded 7/29/2022 as Instrument No. 20220610270 in the office of the County</t>
+          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3511,7 +3439,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Trust dated 7/28/2022 and recorded 7/29/2022 as Instrument No. 20220610270 in the office of the County</t>
+          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3591,7 +3519,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Trust dated 1/15/2019 and recorded 1/15/2019 as Instrument No. 20190030161 in the office of the County</t>
+          <t>/A gent: QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3641,7 +3569,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Trust dated 1/15/2019 and recorded 1/15/2019 as Instrument No. 20190030161 in the office of the County</t>
+          <t>/A gent: QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3775,11 +3703,7 @@
           <t>2025032204</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>06/04/2025</t>
-        </is>
-      </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
           <t>20250322044</t>
@@ -3802,7 +3726,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG26" t="n">
@@ -3840,14 +3764,10 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>in favor of WELLS FARGO BANK, N.A. as</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORPS</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3897,7 +3817,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>CORPS</t>
+          <t>17100 Gillette Ave</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3905,11 +3825,7 @@
           <t>005-1708272</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>08/29/2024</t>
-        </is>
-      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
           <t>20150216695</t>
@@ -3932,11 +3848,11 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4031,11 +3947,7 @@
           <t>2007055829</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>05/14/2007</t>
-        </is>
-      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
           <t>20070558292</t>
@@ -4058,7 +3970,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG28" t="n">
@@ -4157,11 +4069,7 @@
           <t>2021064449</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>06/11/2021</t>
-        </is>
-      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
           <t>20210644498</t>
@@ -4184,7 +4092,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG29" t="n">
@@ -4283,11 +4191,7 @@
           <t>2020092366</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>09/29/2020</t>
-        </is>
-      </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
           <t>20200923660</t>
@@ -4310,7 +4214,7 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG30" t="n">
@@ -4409,11 +4313,7 @@
           <t>2023055878</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>10/27/2023</t>
-        </is>
-      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
           <t>20230558787</t>
@@ -4436,7 +4336,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG31" t="n">
@@ -4535,11 +4435,7 @@
           <t>2016024986</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>04/15/2016</t>
-        </is>
-      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
           <t>20160249869</t>
@@ -4562,7 +4458,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG32" t="n">
@@ -4600,14 +4496,10 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>in which LB Assets 8, LLC</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>of Trust dated September 23, 2024, and recorded in the Maricopa County Recorder's Office</t>
+          <t>Trustee’s Phone</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4641,7 +4533,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>of Trust dated September 23, 2024, and recorded in the Maricopa County Recorder's Office</t>
+          <t>Trustee’s Phone</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4672,11 +4564,11 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -4771,11 +4663,7 @@
           <t>2023023536</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>05/05/2023</t>
-        </is>
-      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
           <t>20230235369</t>
@@ -4798,7 +4686,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG34" t="n">
@@ -4897,11 +4785,7 @@
           <t>008-0102507</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>02/05/2008</t>
-        </is>
-      </c>
+      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
           <t>20080235349</t>
@@ -4924,7 +4808,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG35" t="n">
@@ -4969,7 +4853,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Trust dated 9/1/2023 and recorded on 9/6/2023, as Instrument No. 20230467168, in the office of the County</t>
+          <t>CURRENT BENEFICIARY</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5003,7 +4887,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>Trust dated 9/1/2023 and recorded on 9/6/2023, as Instrument No. 20230467168, in the office of the County</t>
+          <t>CURRENT BENEFICIARY</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -5011,11 +4895,7 @@
           <t>(866) 931-0036</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>9/1/2023</t>
-        </is>
-      </c>
+      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
         <is>
           <t>20230467168</t>
@@ -5038,7 +4918,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG36" t="n">
@@ -5083,7 +4963,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 08/20/2021 in Instrument No. 20210904536, Book XX, Page XX, records of</t>
+          <t>NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5133,7 +5013,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 08/20/2021 in Instrument No. 20210904536, Book XX, Page XX, records of</t>
+          <t>NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -5141,11 +5021,7 @@
           <t>2021090453</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>08/20/2021</t>
-        </is>
-      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
           <t>20210904536</t>
@@ -5168,7 +5044,7 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG37" t="n">
@@ -5213,7 +5089,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 09/18/2019 in Instrument No. 20190734079, Book XX, Page XX, records of</t>
+          <t>NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5263,7 +5139,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Deed of Trust recorded on 09/18/2019 in Instrument No. 20190734079, Book XX, Page XX, records of</t>
+          <t>NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -5271,11 +5147,7 @@
           <t>2019073407</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>09/18/2019</t>
-        </is>
-      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
           <t>20190734079</t>
@@ -5298,7 +5170,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG38" t="n">
@@ -5343,7 +5215,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Trust dated 2/14/2024 and recorded 2/14/2024 as Instrument No. 20240076207 — in the office of the County</t>
+          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5393,7 +5265,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>Trust dated 2/14/2024 and recorded 2/14/2024 as Instrument No. 20240076207 — in the office of the County</t>
+          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -5473,7 +5345,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Trust dated 8/30/2021 and recorded 8/31/2021 as Instrument No, 20210942675 — in the office of the County</t>
+          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5523,7 +5395,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>Trust dated 8/30/2021 and recorded 8/31/2021 as Instrument No, 20210942675 — in the office of the County</t>
+          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -434,7 +434,7 @@
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="60" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
@@ -652,12 +652,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>STERLING M. GRANT</t>
+          <t>Sterling M. Grant</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CURRENT BENEFICIARY</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>CURRENT BENEFICIARY</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RONALD HODNE, AN UNMARRIED MAN, AND LA TOYA GUEVARA, AN UNMARRIED WOMAN</t>
+          <t>Ronald Hodne, And La Toya Guevara</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2023057015</t>
+          <t>949-252-8300</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
@@ -904,12 +904,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BRIAN JAMISON</t>
+          <t>Brian Jamison</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CURRENT BENEFICIARY</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>CURRENT BENEFICIARY</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CANDICE AUGE AND TODD AUGE</t>
+          <t>Candice Auge And Todd Auge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CURRENT BENEFICIARY</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>CURRENT BENEFICIARY</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HELEN E CHARLES</t>
+          <t>Helen E Charles</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ORIGINAL TRUSTOR</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>ORIGINAL TRUSTOR</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1294,12 +1294,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>YOLANDA MCKIM AND BILLY MCKIM, WIFE AND HUSBAND AS COMMUNITY PROPERTY</t>
+          <t>Yolanda Mckim And Billy Mckim</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2021066036</t>
+          <t>949-252-8300</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ROBERT FARMER</t>
+          <t>Robert Farmer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>THE FOLLOWING INFORMATION IS PROVIDED PURSUANT TO A.R.S. SECTION 33-808(C)</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>THE FOLLOWING INFORMATION IS PROVIDED PURSUANT TO A.R.S. SECTION 33-808(C)</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NIRA WANNARKA AND WILLIAM DIXON, WIFE AND HUSBAND</t>
+          <t>Nira Wannarka And William Dixon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>105-65-525105-65-525</t>
+          <t>105-65-525</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2022061067</t>
+          <t>949-252-8300</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GOOD NEWS GROUP, LLC</t>
+          <t>Good News Group, Llc</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>’s capacity as a</t>
+          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>’s capacity as a</t>
+          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CAROLINE ANN BRICKELL AND SEAN GENZMER</t>
+          <t>Caroline Ann Brickell And Sean Genzmer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CURRENT BENEFICIARY</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>CURRENT BENEFICIARY</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1917,7 +1917,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gilbert, Arizona 85234</t>
+          <t>sale or if you have an</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1955,11 +1955,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Numbers</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
           <t>$238,500.00</t>
@@ -1967,7 +1963,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Gilbert, Arizona 85234</t>
+          <t>sale or if you have an</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1998,7 +1994,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing</t>
+          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2039,7 +2035,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>OF THE BOBBI SCHULTZ TRUST UNDER TRUST</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2055,7 +2051,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SUN, CITY</t>
+          <t>SUN CITY</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2077,11 +2073,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t>$275,000.00</t>
@@ -2089,12 +2081,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>OF THE BOBBI SCHULTZ TRUST UNDER TRUST</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2022071684</t>
+          <t>(888) 725-4142</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -2120,7 +2112,7 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing</t>
+          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG13" t="n">
@@ -2160,12 +2152,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LUIS ALONSO MIRANDA GOMEZ, A MARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
+          <t>Luis Alonso Miranda Gomez, A Married Man</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>common designation, if any, shown herein.</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2203,11 +2195,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
           <t>$122,042.00</t>
@@ -2215,12 +2203,12 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>common designation, if any, shown herein.</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2018083116</t>
+          <t>(888) 725-4142</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -2246,7 +2234,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG14" t="n">
@@ -2286,12 +2274,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON, HUSBAND AND WIFE AND ANTHONY DE LEON, AN UNMARRIED MAN</t>
+          <t>Yolanda S. De Leon And Domingo De Leon And Anthony De Leon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2341,12 +2329,12 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2022084779</t>
+          <t>949-252-8300</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -2412,12 +2400,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JASON DANIEL MURRAY AND AMBER MURRAY, HUSBAND AND WIFE AS JOINT TENANTS WITH RIGHT OF SURVIVORSHIP</t>
+          <t>Jason Daniel Murray And Amber Murray</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>common designation, if any, shown herein.</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2455,11 +2443,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>$235,653.00</t>
@@ -2467,12 +2451,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>common designation, if any, shown herein.</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2022086524</t>
+          <t>(888) 725-4142</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -2498,7 +2482,7 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG16" t="n">
@@ -2538,12 +2522,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>JORDAN OLIVA, A SINGLE MAN</t>
+          <t>Jordan Oliva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>common designation, if any, shown herein.</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2559,7 +2543,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>QUEEN, CREEK</t>
+          <t>QUEEN CREEK</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2581,11 +2565,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>$427,696.00</t>
@@ -2593,12 +2573,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>common designation, if any, shown herein.</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2021116172</t>
+          <t>(888) 725-4142</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
@@ -2624,7 +2604,7 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG17" t="n">
@@ -2664,12 +2644,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RUSTY ROBERTS AND NICHOLE ROBERTS, HUSBAND AND WIFE</t>
+          <t>Rusty Roberts And Nichole Roberts</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>common designation, if any, shown herein.</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2707,11 +2687,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>$1,138,564.00</t>
@@ -2719,12 +2695,12 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>common designation, if any, shown herein.</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2023015469</t>
+          <t>(888) 725-4142</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -2750,7 +2726,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG18" t="n">
@@ -2790,12 +2766,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RYMAX DEVELOPMENT, L.L.C.</t>
+          <t>Rymax Development, L.L.C.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>602-488-1349 ronaldherb@gmail.com</t>
+          <t>Licensed Real Estate Broker in Arizona.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2845,12 +2821,12 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>602-488-1349 ronaldherb@gmail.com</t>
+          <t>Licensed Real Estate Broker in Arizona.</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2024056527</t>
+          <t>602-488-1349</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -2916,12 +2892,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TITAN FAMILY REALESTATE LLC</t>
+          <t>Titan Family Realestate Llc</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>602-488-1349 ronaldherb@gmail.com</t>
+          <t>Licensed Real Estate Broker in Arizona.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2955,12 +2931,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>602-488-1349 ronaldherb@gmail.com</t>
+          <t>Licensed Real Estate Broker in Arizona.</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026001494</t>
+          <t>602-488-1349</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
@@ -3026,12 +3002,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Graciela Bucio Perez an unmarried woman</t>
+          <t>Graciela Bucio Perez</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>602-488-1349 ronaldherb@gmail.com</t>
+          <t>Licensed Real Estate Broker in Arizona.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3065,12 +3041,12 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>602-488-1349 ronaldherb@gmail.com</t>
+          <t>Licensed Real Estate Broker in Arizona.</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2024014138</t>
+          <t>602-488-1349</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
@@ -3136,12 +3112,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JOSEPH VERDUZCO, A MARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
+          <t>Joseph Verduzco, A Married Man</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3191,12 +3167,12 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2018017439</t>
+          <t>949-252-8300</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -3260,10 +3236,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>(as of the recording of the Notice of</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>to the highest bidder</t>
+          <t>SALE OR IF</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3301,11 +3281,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>IDENTIFIABLE</t>
-        </is>
-      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>$10,000,000.00</t>
@@ -3313,12 +3289,12 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>to the highest bidder</t>
+          <t>SALE OR IF</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2024043257</t>
+          <t>(602) 459-4112</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -3344,11 +3320,11 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -3384,12 +3360,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BRENDA FAE HUBBARD, A MARRIED WOMAN AS HER SOLE AND SEPARATE PROPERTY</t>
+          <t>Brenda Fae Hubbard, A Married Woman</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3439,12 +3415,12 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2022061027</t>
+          <t>(866) 645-7711</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3514,12 +3490,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ZHONG K WANG AND FRANCIS N PRICE, AND UNMARRIED MAN AND FRANCIS PRICE, AN UNMARRIED WOMAN</t>
+          <t>ZHONG K WANG AND FRANCIS N PRICE, and FRANCIS PRICE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>/A gent: QUALITY LOAN SERVICE CORPORATION</t>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3535,7 +3511,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>EL, MIRAGE</t>
+          <t>EL MIRAGE</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3569,12 +3545,12 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>/A gent: QUALITY LOAN SERVICE CORPORATION</t>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2019003016</t>
+          <t>003-0891101</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3649,7 +3625,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3695,14 +3671,10 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>2025032204</t>
-        </is>
-      </c>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
@@ -3726,7 +3698,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG26" t="n">
@@ -3767,7 +3739,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3817,7 +3789,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave</t>
+          <t>MTC FINANCIAL INC</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3888,12 +3860,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Frances Garcia, an unmarried woman</t>
+          <t>Frances Garcia</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3939,14 +3911,10 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>2007055829</t>
-        </is>
-      </c>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
@@ -3970,7 +3938,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG28" t="n">
@@ -4010,12 +3978,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luis Vincente Gurrola Martinez, a single man</t>
+          <t>Luis Vincente Gurrola Martinez</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -4061,12 +4029,12 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2021064449</t>
+          <t>(602) 255-6035</t>
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
@@ -4092,7 +4060,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG29" t="n">
@@ -4132,12 +4100,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Christine Lea Kurtz-Ford, an unmarried woman</t>
+          <t>Christine Lea Kurtz-Ford</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4183,12 +4151,12 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2020092366</t>
+          <t>(602) 255-6035</t>
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
@@ -4214,7 +4182,7 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG30" t="n">
@@ -4254,12 +4222,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Martin V Valadez, a single man and Velazquez David Valadez, a single man</t>
+          <t>Martin V Valadez and Velazquez David Valadez</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4305,12 +4273,12 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2023055878</t>
+          <t>(602) 255-6035</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
@@ -4336,7 +4304,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG31" t="n">
@@ -4376,12 +4344,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Richard L Bristol and Grace A Bristol, husband and wife</t>
+          <t>Richard L Bristol and Grace A Bristol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4427,12 +4395,12 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2016024986</t>
+          <t>(602) 255-6035</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -4458,7 +4426,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG32" t="n">
@@ -4499,7 +4467,7 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Trustee’s Phone</t>
+          <t>. NOTICE! IF YOU BELIEVE THERE IS A DEFENSE TO THE TRUSTEE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4521,11 +4489,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>509-18-83</t>
-        </is>
-      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
           <t>$725,000.00</t>
@@ -4533,7 +4497,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Trustee’s Phone</t>
+          <t>. NOTICE! IF YOU BELIEVE THERE IS A DEFENSE TO THE TRUSTEE</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -4564,7 +4528,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing</t>
+          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG33" t="n">
@@ -4604,12 +4568,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rene Campa, an unmarried woman, and Sebastian Campa, an unmarried man</t>
+          <t>Rene Campa, and Sebastian Campa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4655,14 +4619,10 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>2023023536</t>
-        </is>
-      </c>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
@@ -4686,7 +4646,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG34" t="n">
@@ -4726,12 +4686,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lynda Peretz, an unmarried woman</t>
+          <t>Lynda Peretz</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4777,7 +4737,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>Leonard J. McDonald</t>
+          <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4808,7 +4768,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG35" t="n">
@@ -4848,12 +4808,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RICHARDO MONTES IBARBOL AND ABAGAIL ALEXXIS MENDEZ AND MARIA THERESA IBARBOL CRUZ</t>
+          <t>Richardo Montes Ibarbol And Abagail Alexxis Mendez And Maria Theresa Ibarbol Cruz</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CURRENT BENEFICIARY</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4887,7 +4847,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>CURRENT BENEFICIARY</t>
+          <t>CLEAR RECON CORP</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4958,12 +4918,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>YAVIN JAY CRANSHAW, A SINGLE MAN</t>
+          <t>Yavin Jay Cranshaw</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -5001,11 +4961,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
+      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
           <t>$363,298.00</t>
@@ -5013,12 +4969,12 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2021090453</t>
+          <t>(888) 725-4142</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
@@ -5044,7 +5000,7 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG37" t="n">
@@ -5084,12 +5040,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JUAN CARRANZA, UNMARRIED</t>
+          <t>Juan Carranza, Unmarried</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5127,11 +5083,7 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
           <t>$286,805.00</t>
@@ -5139,12 +5091,12 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>NO LATER THAN 5:00 P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY</t>
+          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2019073407</t>
+          <t>(888) 725-4142</t>
         </is>
       </c>
       <c r="W38" t="inlineStr"/>
@@ -5170,7 +5122,7 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG38" t="n">
@@ -5210,12 +5162,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BLANCA M ARMENTA QUINONEZ, AN UNMARRIED WOMAN AND MICHAEL G ARMENTA, AN UNMARRIED MAN</t>
+          <t>Blanca M Armenta Quinonez And Michael G Armenta</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5265,12 +5217,12 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2024007620</t>
+          <t>(866) 645-7711</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5340,12 +5292,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Andrew S Kulin and Kasie M Lambros, husband and wife as community property with rights of survivorship</t>
+          <t>Andrew S Kulin and Kasie M Lambros with rights of survivorship</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5395,12 +5347,12 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>/Agent: QUALITY LOAN SERVICE CORPORATION</t>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2021094267</t>
+          <t>(866) 645-7711</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -422,7 +422,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="29" customWidth="1" min="10" max="10"/>
@@ -436,7 +436,7 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
@@ -652,7 +652,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sterling M. Grant</t>
+          <t>STERLING M. GRANT</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ronald Hodne, And La Toya Guevara</t>
+          <t>RONALD HODNE AND LA TOYA GUEVARA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W3" t="inlineStr"/>
@@ -904,7 +904,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brian Jamison</t>
+          <t>BRIAN JAMISON</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(844) 477-7869</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Candice Auge And Todd Auge</t>
+          <t>CANDICE AUGE AND TODD AUGE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Helen E Charles</t>
+          <t>HELEN E CHARLES</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yolanda Mckim And Billy Mckim</t>
+          <t>YOLANDA MCKIM AND BILLY MCKIM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Robert Farmer</t>
+          <t>ROBERT FARMER</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nira Wannarka And William Dixon</t>
+          <t>NIRA WANNARKA AND WILLIAM DIXON</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Good News Group, Llc</t>
+          <t>GOOD NEWS GROUP, LLC</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>949-427-2010</t>
+          <t>(949) 427-2010</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Caroline Ann Brickell And Sean Genzmer</t>
+          <t>CAROLINE ANN BRICKELL AND SEAN GENZMER</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(866) 931-0036</t>
+          <t>(800) 280-2832</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1915,11 +1915,7 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>sale or if you have an</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>$238,500.00</t>
@@ -1961,16 +1957,8 @@
           <t>$238,500.00</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>sale or if you have an</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>024-0111013</t>
-        </is>
-      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
@@ -1998,7 +1986,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2033,11 +2021,7 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>$275,000.00</t>
@@ -2079,16 +2063,8 @@
           <t>$275,000.00</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
@@ -2116,7 +2092,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2152,14 +2128,10 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luis Alonso Miranda Gomez, A Married Man</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
+          <t>LUIS ALONSO MIRANDA GOMEZ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>$122,042.00</t>
@@ -2201,16 +2173,8 @@
           <t>$122,042.00</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
@@ -2238,7 +2202,7 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2274,7 +2238,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yolanda S. De Leon And Domingo De Leon And Anthony De Leon</t>
+          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON AND ANTHONY DE LEON</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2334,7 +2298,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -2400,14 +2364,10 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jason Daniel Murray And Amber Murray</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
+          <t>JASON DANIEL MURRAY AND AMBER MURRAY</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>$235,653.00</t>
@@ -2449,16 +2409,8 @@
           <t>$235,653.00</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
@@ -2486,7 +2438,7 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2522,14 +2474,10 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jordan Oliva</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
+          <t>JORDAN OLIVA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>$427,696.00</t>
@@ -2571,16 +2519,8 @@
           <t>$427,696.00</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
@@ -2608,7 +2548,7 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -2644,14 +2584,10 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rusty Roberts And Nichole Roberts</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
+          <t>RUSTY ROBERTS AND NICHOLE ROBERTS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>$1,138,564.00</t>
@@ -2693,16 +2629,8 @@
           <t>$1,138,564.00</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
@@ -2730,7 +2658,7 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -2766,14 +2694,10 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rymax Development, L.L.C.</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Licensed Real Estate Broker in Arizona.</t>
-        </is>
-      </c>
+          <t>RYMAX DEVELOPMENT, L.L.C.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -2819,16 +2743,8 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Licensed Real Estate Broker in Arizona.</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>602-488-1349</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
@@ -2856,7 +2772,7 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -2892,14 +2808,10 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Titan Family Realestate Llc</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Licensed Real Estate Broker in Arizona.</t>
-        </is>
-      </c>
+          <t>TITAN FAMILY REALESTATE LLC</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>$110,000.00</t>
@@ -2929,16 +2841,8 @@
           <t>$110,000.00</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Licensed Real Estate Broker in Arizona.</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>602-488-1349</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
@@ -2966,7 +2870,7 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3005,11 +2909,7 @@
           <t>Graciela Bucio Perez</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Licensed Real Estate Broker in Arizona.</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>$176,000.00</t>
@@ -3039,16 +2939,8 @@
           <t>$176,000.00</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Licensed Real Estate Broker in Arizona.</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>602-488-1349</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
@@ -3076,7 +2968,7 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3112,7 +3004,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Joseph Verduzco, A Married Man</t>
+          <t>JOSEPH VERDUZCO</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3172,7 +3064,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
@@ -3236,16 +3128,8 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>(as of the recording of the Notice of</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>SALE OR IF</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>$10,000,000.00</t>
@@ -3287,16 +3171,8 @@
           <t>$10,000,000.00</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>SALE OR IF</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>(602) 459-4112</t>
-        </is>
-      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
@@ -3320,11 +3196,11 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -3360,7 +3236,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brenda Fae Hubbard, A Married Woman</t>
+          <t>BRENDA FAE HUBBARD</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3420,7 +3296,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(866) 645-7711</t>
+          <t>(202) 602-2751</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3490,7 +3366,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ZHONG K WANG AND FRANCIS N PRICE, and FRANCIS PRICE</t>
+          <t>ZHONG K WANG AND FRANCIS N PRICE AND MAN AND FRANCIS PRICE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3550,7 +3426,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>003-0891101</t>
+          <t>(202) 602-2752</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3620,7 +3496,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wayne Carpenter, a single person</t>
+          <t>Wayne Carpenter</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3674,7 +3550,11 @@
           <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(202) 503-2204</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr">
         <is>
@@ -3794,7 +3674,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>005-1708272</t>
+          <t>(201) 602-8250</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
@@ -3914,7 +3794,11 @@
           <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>(200) 705-5829</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr">
         <is>
@@ -4034,7 +3918,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>(602) 255-6035</t>
+          <t>(202) 106-4449</t>
         </is>
       </c>
       <c r="W29" t="inlineStr"/>
@@ -4156,7 +4040,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>(602) 255-6035</t>
+          <t>(202) 009-2366</t>
         </is>
       </c>
       <c r="W30" t="inlineStr"/>
@@ -4222,7 +4106,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Martin V Valadez and Velazquez David Valadez</t>
+          <t>Martin V Valadez AND Velazquez David Valadez</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4278,7 +4162,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>(602) 255-6035</t>
+          <t>(202) 305-5878</t>
         </is>
       </c>
       <c r="W31" t="inlineStr"/>
@@ -4400,7 +4284,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>(602) 255-6035</t>
+          <t>(201) 602-4986</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -4465,11 +4349,7 @@
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>. NOTICE! IF YOU BELIEVE THERE IS A DEFENSE TO THE TRUSTEE</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>$725,000.00</t>
@@ -4495,16 +4375,8 @@
           <t>$725,000.00</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>. NOTICE! IF YOU BELIEVE THERE IS A DEFENSE TO THE TRUSTEE</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>024-0637955</t>
-        </is>
-      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
@@ -4532,7 +4404,7 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -4568,7 +4440,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rene Campa, and Sebastian Campa</t>
+          <t>Rene Campa AND Sebastian Campa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4622,7 +4494,11 @@
           <t>LEONARD J. MCDONALD</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>(202) 302-3536</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
@@ -4742,7 +4618,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>008-0102507</t>
+          <t>(008) 010-2507</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -4808,7 +4684,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Richardo Montes Ibarbol And Abagail Alexxis Mendez And Maria Theresa Ibarbol Cruz</t>
+          <t>RICHARDO MONTES IBARBOL AND ABAGAIL ALEXXIS MENDEZ AND MARIA THERESA IBARBOL CRUZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4918,14 +4794,10 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Yavin Jay Cranshaw</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
+          <t>YAVIN JAY CRANSHAW</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>$363,298.00</t>
@@ -4967,16 +4839,8 @@
           <t>$363,298.00</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
@@ -5004,7 +4868,7 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -5040,14 +4904,10 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Juan Carranza, Unmarried</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
+          <t>JUAN CARRANZA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>$286,805.00</t>
@@ -5089,16 +4949,8 @@
           <t>$286,805.00</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>herein qualifies as Trustee of the Trust Deed in the Trustee's capacity as a licensed</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr">
         <is>
@@ -5126,7 +4978,7 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -5162,7 +5014,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanca M Armenta Quinonez And Michael G Armenta</t>
+          <t>BLANCA M ARMENTA QUINONEZ AND MICHAEL G ARMENTA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5222,7 +5074,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>(866) 645-7711</t>
+          <t>(202) 602-2849</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5292,7 +5144,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Andrew S Kulin and Kasie M Lambros with rights of survivorship</t>
+          <t>Andrew S Kulin and Kasie M Lambros</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5352,7 +5204,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>(866) 645-7711</t>
+          <t>(202) 602-2851</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>(844) 477-7869</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>(800) 280-2832</t>
+          <t>(866) 931-0036</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>(202) 602-2751</t>
+          <t>(866) 645-7711</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ZHONG K WANG AND FRANCIS N PRICE AND MAN AND FRANCIS PRICE</t>
+          <t>ZHONG K WANG AND FRANCIS N PRICE AND FRANCIS PRICE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>(202) 602-2752</t>
+          <t>(866) 645-7711</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3552,10 +3552,14 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>(202) 503-2204</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>7/30/2026</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr">
         <is>
           <t>20250322044</t>
@@ -3578,7 +3582,7 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG26" t="n">
@@ -3674,7 +3678,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>(201) 602-8250</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
@@ -3796,10 +3800,14 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>(200) 705-5829</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr"/>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>8/6/2026</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr">
         <is>
           <t>20070558292</t>
@@ -3822,7 +3830,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG28" t="n">
@@ -3918,10 +3926,14 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>(202) 106-4449</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr"/>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>8/6/2026</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr">
         <is>
           <t>20210644498</t>
@@ -3944,7 +3956,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG29" t="n">
@@ -4040,10 +4052,14 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>(202) 009-2366</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr"/>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>8/6/2026</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr">
         <is>
           <t>20200923660</t>
@@ -4066,7 +4082,7 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG30" t="n">
@@ -4162,10 +4178,14 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>(202) 305-5878</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr"/>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>8/6/2026</t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr">
         <is>
           <t>20230558787</t>
@@ -4188,7 +4208,7 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG31" t="n">
@@ -4284,10 +4304,14 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>(201) 602-4986</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr"/>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>8/6/2026</t>
+        </is>
+      </c>
       <c r="X32" t="inlineStr">
         <is>
           <t>20160249869</t>
@@ -4310,7 +4334,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG32" t="n">
@@ -4496,10 +4520,14 @@
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>(202) 302-3536</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr"/>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>8/6/2026</t>
+        </is>
+      </c>
       <c r="X34" t="inlineStr">
         <is>
           <t>20230235369</t>
@@ -4522,7 +4550,7 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG34" t="n">
@@ -4618,10 +4646,14 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>(008) 010-2507</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr"/>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>7/30/2026</t>
+        </is>
+      </c>
       <c r="X35" t="inlineStr">
         <is>
           <t>20080235349</t>
@@ -4644,7 +4676,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG35" t="n">
@@ -5074,7 +5106,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>(202) 602-2849</t>
+          <t>(866) 645-7711</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
@@ -5204,7 +5236,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>(202) 602-2851</t>
+          <t>(866) 645-7711</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -421,12 +421,12 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="29" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -435,9 +435,9 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
@@ -446,10 +446,10 @@
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
-    <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="60" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,42 +650,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>STERLING M. GRANT</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>$236,880.00</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>19079 E SEAGULL DR</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>QUEEN CREEK</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>85142</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -695,32 +667,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>314-05-709</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>$236,880.00</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>20180610512</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -731,24 +683,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225916.pdf</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225916.pdf</t>
-        </is>
-      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225916.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -776,42 +720,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>RONALD HODNE AND LA TOYA GUEVARA</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>$690,900.00</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>13910 S 180TH AVE</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>GOODYEAR</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>85338</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -821,32 +737,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>400-82-358</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>$690,900.00</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>20230570155</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -857,24 +753,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226177.pdf</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226177.pdf</t>
-        </is>
-      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226177.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -902,42 +790,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>BRIAN JAMISON</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>$330,000.00</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>8126 W WATKINS ST</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>85043</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -947,36 +807,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>104-33-181</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>$330,000.00</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>7/23/2026</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>20210626779</t>
-        </is>
-      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -987,24 +823,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226185.pdf</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226185.pdf</t>
-        </is>
-      </c>
+      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226185.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1032,42 +860,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CANDICE AUGE AND TODD AUGE</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>$285,000.00</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>4202 E EVERETT DR</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>85032</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -1077,36 +877,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>215-71-184</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>$285,000.00</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>7/23/2026</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>20220200328</t>
-        </is>
-      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -1117,24 +893,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226190.pdf</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226190.pdf</t>
-        </is>
-      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226190.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1162,42 +930,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HELEN E CHARLES</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>$246,500.00</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>9810 N BALBOA DR</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>SUN CITY</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>85351</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1207,36 +947,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>142-84-801</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>$246,500.00</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>7/23/2026</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>20210829918</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -1247,24 +963,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226195.pdf</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226195.pdf</t>
-        </is>
-      </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226195.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1292,42 +1000,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>YOLANDA MCKIM AND BILLY MCKIM</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>$335,805.00</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>3937 W MYRTLE AVE</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>85051</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1337,32 +1017,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>151-26-142</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>$335,805.00</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>20210660360</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
@@ -1373,24 +1033,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226197.pdf</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226197.pdf</t>
-        </is>
-      </c>
+      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226197.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1418,42 +1070,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ROBERT FARMER</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>$205,128.00</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>14300 W BELL RD UNIT 52</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>SURPRISE</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>85374</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1463,36 +1087,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>503-59-212B</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>$205,128.00</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>7/23/2026</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>20230106079</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1503,24 +1103,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226200.pdf</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226200.pdf</t>
-        </is>
-      </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226200.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1548,42 +1140,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NIRA WANNARKA AND WILLIAM DIXON</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>$381,562.00</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2330 W SPENCER RUN</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>85041</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1593,32 +1157,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>105-65-525</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>$381,562.00</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>20220610672</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1629,24 +1173,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226202.pdf</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226202.pdf</t>
-        </is>
-      </c>
+      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226202.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1674,21 +1210,9 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>GOOD NEWS GROUP, LLC</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>$374,000.00</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1703,32 +1227,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>155-53-014</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>$374,000.00</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>(949) 427-2010</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>20230215291</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -1739,24 +1243,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226317.pdf</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226317.pdf</t>
-        </is>
-      </c>
+      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226317.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1784,42 +1280,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CAROLINE ANN BRICKELL AND SEAN GENZMER</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>$252,340.00</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>21003 N 123RD DR</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>SUN CITY WEST</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>85375</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1829,36 +1297,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>232-14-036</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>$252,340.00</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>7/30/2026</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>20211376027</t>
-        </is>
-      </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
@@ -1869,24 +1313,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226412.pdf</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226412.pdf</t>
-        </is>
-      </c>
+      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226412.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1916,32 +1352,12 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>$238,500.00</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>11122 W Montana Ave.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Youngtown</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>85363</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1952,19 +1368,11 @@
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>$238,500.00</t>
-        </is>
-      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>20260226657</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -1975,24 +1383,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226657.pdf</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226657.pdf</t>
-        </is>
-      </c>
+      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226657.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2022,32 +1422,12 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>$275,000.00</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>10437 W CHERYL DR</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>SUN CITY</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>85351</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -2058,19 +1438,11 @@
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>$275,000.00</t>
-        </is>
-      </c>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>20220716841</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -2081,24 +1453,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226771.pdf</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226771.pdf</t>
-        </is>
-      </c>
+      <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226771.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2126,38 +1490,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>LUIS ALONSO MIRANDA GOMEZ</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>$122,042.00</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>520 E HARRISON DR</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>AVONDALE</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>85323</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2168,19 +1508,11 @@
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>$122,042.00</t>
-        </is>
-      </c>
+      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>20180831169</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
@@ -2191,24 +1523,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226956.pdf</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226956.pdf</t>
-        </is>
-      </c>
+      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226956.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2236,42 +1560,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON AND ANTHONY DE LEON</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>$323,000.00</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>30306 WEST PORTLAND STREET</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>BUCKEYE</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>85396</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -2281,32 +1577,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>504-15-159</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>$323,000.00</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>20220847791</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
@@ -2317,24 +1593,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226960.pdf</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226960.pdf</t>
-        </is>
-      </c>
+      <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226960.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2362,38 +1630,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>JASON DANIEL MURRAY AND AMBER MURRAY</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>$235,653.00</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>3307 W ECHO LN</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>85051</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -2404,19 +1648,11 @@
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>$235,653.00</t>
-        </is>
-      </c>
+      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>20220865242</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
@@ -2427,24 +1663,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227028.pdf</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227028.pdf</t>
-        </is>
-      </c>
+      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227028.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2472,38 +1700,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>JORDAN OLIVA</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>$427,696.00</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>22229 E VIA DEL PALO</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>QUEEN CREEK</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>85142</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -2514,19 +1718,11 @@
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>$427,696.00</t>
-        </is>
-      </c>
+      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>20211161722</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
@@ -2537,24 +1733,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227091.pdf</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227091.pdf</t>
-        </is>
-      </c>
+      <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227091.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2582,38 +1770,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>RUSTY ROBERTS AND NICHOLE ROBERTS</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>$1,138,564.00</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>8145 W CAMINO DE ORO</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>PEORIA</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>85383</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -2624,19 +1788,11 @@
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>$1,138,564.00</t>
-        </is>
-      </c>
+      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>20230154699</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
@@ -2647,24 +1803,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227136.pdf</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227136.pdf</t>
-        </is>
-      </c>
+      <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227136.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2692,38 +1840,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>RYMAX DEVELOPMENT, L.L.C.</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>$480,000.00</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>18245 N PIMA ROAD UNIT 1049</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>SCOTTSDALE</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>85040</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -2733,24 +1857,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>113-25-059</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>$480,000.00</t>
-        </is>
-      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>20240565279</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
@@ -2761,24 +1873,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227218.pdf</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227218.pdf</t>
-        </is>
-      </c>
+      <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227218.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2806,17 +1910,9 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>TITAN FAMILY REALESTATE LLC</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>$110,000.00</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -2831,24 +1927,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>102-84-270</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>$110,000.00</t>
-        </is>
-      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>20260014942</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
@@ -2859,24 +1943,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227219.pdf</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227219.pdf</t>
-        </is>
-      </c>
+      <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227219.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2904,17 +1980,9 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Graciela Bucio Perez</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>$176,000.00</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -2929,24 +1997,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>206-20-159</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>$176,000.00</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>20240141383</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
@@ -2957,24 +2013,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227220.pdf</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227220.pdf</t>
-        </is>
-      </c>
+      <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227220.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3002,42 +2050,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>JOSEPH VERDUZCO</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>$294,405.00</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2830 S. CHATSWORTH</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>MESA</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>85212</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -3047,32 +2067,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>309-19-162</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>$294,405.00</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>20180174392</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
@@ -3083,24 +2083,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227284.pdf</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227284.pdf</t>
-        </is>
-      </c>
+      <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227284.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3130,32 +2122,12 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>$10,000,000.00</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>7508 N. 59th Avenue</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>85301</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -3166,19 +2138,11 @@
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>$10,000,000.00</t>
-        </is>
-      </c>
+      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>20240432575</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
@@ -3189,24 +2153,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227302.pdf</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227302.pdf</t>
-        </is>
-      </c>
+      <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227302.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3234,42 +2190,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>BRENDA FAE HUBBARD</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>$192,449.00</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>9113 E BUTTERNUT AVE</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>MESA</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>85208</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -3279,36 +2207,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>218-41-190</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>$192,449.00</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>7/23/2026</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>20220610270</t>
-        </is>
-      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
@@ -3319,24 +2223,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227512.pdf</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227512.pdf</t>
-        </is>
-      </c>
+      <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227512.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3364,42 +2260,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>ZHONG K WANG AND FRANCIS N PRICE AND FRANCIS PRICE</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>$200,000.00</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>12546 W MANDALAY LANE</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>EL MIRAGE</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>85335</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -3409,36 +2277,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>509-13-497</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>$200,000.00</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>7/23/2026</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>20190030161</t>
-        </is>
-      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
@@ -3449,24 +2293,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227521.pdf</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227521.pdf</t>
-        </is>
-      </c>
+      <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227521.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3494,42 +2330,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Wayne Carpenter</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>$50,000.00</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>7486 S Sundown Ct</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Buckeye</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>85326</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -3540,31 +2348,11 @@
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>$50,000.00</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>7/30/2026</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>20250322044</t>
-        </is>
-      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
@@ -3575,24 +2363,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227539.pdf</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227539.pdf</t>
-        </is>
-      </c>
+      <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227539.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3621,37 +2401,13 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>$337,252.80</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>21823 NORTH MAYA COURT</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>SUN CITY WEST</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>85375</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -3661,32 +2417,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>232-31-246</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>$337,252.80</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>20150216695</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
@@ -3697,24 +2433,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227902.pdf</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227902.pdf</t>
-        </is>
-      </c>
+      <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227902.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3742,42 +2470,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Frances Garcia</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>$68,000.00</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2802 West Madison Street</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>85009</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -3788,31 +2488,11 @@
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>$68,000.00</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>8/6/2026</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>20070558292</t>
-        </is>
-      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
@@ -3823,24 +2503,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227926.pdf</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227926.pdf</t>
-        </is>
-      </c>
+      <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227926.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3868,42 +2540,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Luis Vincente Gurrola Martinez</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>$233,100.00</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>4107 W Krall St</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>85019</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
@@ -3914,31 +2558,11 @@
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>$233,100.00</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>8/6/2026</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>20210644498</t>
-        </is>
-      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
@@ -3949,24 +2573,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227939.pdf</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227939.pdf</t>
-        </is>
-      </c>
+      <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227939.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3994,42 +2610,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Christine Lea Kurtz-Ford</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>$121,000.00</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>630 E Jensen St Unit 138</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>85203</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -4040,31 +2628,11 @@
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>$121,000.00</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>8/6/2026</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>20200923660</t>
-        </is>
-      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
@@ -4075,24 +2643,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227955.pdf</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227955.pdf</t>
-        </is>
-      </c>
+      <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227955.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4120,42 +2680,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Martin V Valadez AND Velazquez David Valadez</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>$380,000.00</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>3708 West Berridge Lane</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>85019</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
@@ -4166,31 +2698,11 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>$380,000.00</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>8/6/2026</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>20230558787</t>
-        </is>
-      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
@@ -4201,24 +2713,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227961.pdf</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227961.pdf</t>
-        </is>
-      </c>
+      <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227961.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4246,42 +2750,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Richard L Bristol and Grace A Bristol</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>$149,055.00</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>20803 W Bradley Road</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Wittmann</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>85361</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
@@ -4292,31 +2768,11 @@
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>$149,055.00</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>8/6/2026</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>20160249869</t>
-        </is>
-      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
@@ -4327,24 +2783,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227974.pdf</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227974.pdf</t>
-        </is>
-      </c>
+      <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227974.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4374,11 +2822,7 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>$725,000.00</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -4394,19 +2838,11 @@
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>$725,000.00</t>
-        </is>
-      </c>
+      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>20260228010</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -4417,24 +2853,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228010.pdf</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228010.pdf</t>
-        </is>
-      </c>
+      <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, owner_missing, auction_date_missing, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228010.txt</t>
-        </is>
-      </c>
+      <c r="AH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4462,42 +2890,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Rene Campa AND Sebastian Campa</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>$368,207.00</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>5214 W Cholla St</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>85304</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
@@ -4508,31 +2908,11 @@
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>$368,207.00</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>8/6/2026</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>20230235369</t>
-        </is>
-      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
@@ -4543,24 +2923,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228017.pdf</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228017.pdf</t>
-        </is>
-      </c>
+      <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228017.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4588,42 +2960,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Lynda Peretz</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>$187,000.00</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>325 E. Anderson Ave.</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>85022</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -4634,31 +2978,11 @@
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>$187,000.00</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>7/30/2026</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>20080235349</t>
-        </is>
-      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
@@ -4669,24 +2993,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228048.pdf</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228048.pdf</t>
-        </is>
-      </c>
+      <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228048.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4714,21 +3030,9 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>RICHARDO MONTES IBARBOL AND ABAGAIL ALEXXIS MENDEZ AND MARIA THERESA IBARBOL CRUZ</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>$380,972.00</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -4743,32 +3047,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>152-19-145</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>$380,972.00</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>20230467168</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
@@ -4779,24 +3063,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228059.pdf</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228059.pdf</t>
-        </is>
-      </c>
+      <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228059.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4824,38 +3100,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>YAVIN JAY CRANSHAW</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>$363,298.00</t>
-        </is>
-      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>4454 W PIUTE AVE</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>GLENDALE</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>85308</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -4866,19 +3118,11 @@
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>$363,298.00</t>
-        </is>
-      </c>
+      <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>20210904536</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
@@ -4889,24 +3133,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228370.pdf</t>
         </is>
       </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228370.pdf</t>
-        </is>
-      </c>
+      <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228370.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4934,38 +3170,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>JUAN CARRANZA</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>$286,805.00</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>19559 W LINCOLN STREET</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>BUCKEYE</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>85326</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
@@ -4976,19 +3188,11 @@
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>$286,805.00</t>
-        </is>
-      </c>
+      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>20190734079</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
@@ -4999,24 +3203,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228380.pdf</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228380.pdf</t>
-        </is>
-      </c>
+      <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>50</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228380.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5044,42 +3240,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>BLANCA M ARMENTA QUINONEZ AND MICHAEL G ARMENTA</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>$280,819.00</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2108 W HADLEY ST</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>85009</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
@@ -5089,36 +3257,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>109-64-004</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>$280,819.00</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>7/23/2026</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>20240076207</t>
-        </is>
-      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
@@ -5129,24 +3273,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228499.pdf</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228499.pdf</t>
-        </is>
-      </c>
+      <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228499.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5174,42 +3310,14 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Andrew S Kulin and Kasie M Lambros</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>$372,000.00</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>1923 E PRESIDIO RD</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>85022</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
@@ -5219,36 +3327,12 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>166-41-057</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>$372,000.00</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>7/23/2026</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>20210942675</t>
-        </is>
-      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -5259,24 +3343,16 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228514.pdf</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228514.pdf</t>
-        </is>
-      </c>
+      <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>no_pdf</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>60</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228514.txt</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -421,12 +421,12 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -435,10 +435,10 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
@@ -446,10 +446,10 @@
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="60" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,14 +650,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>STERLING M. GRANT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>$236,880.00</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19079 E SEAGULL DR</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -667,12 +695,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>314-05-709</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>$236,880.00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>20180610512</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -683,16 +731,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225916.pdf</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225916.pdf</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225916.txt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -720,14 +776,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RONALD HODNE, AND LA TOYA GUEVARA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>$690,900.00</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13910 S 180TH AVE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -737,12 +821,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>400-82-358</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>$690,900.00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>20230570155</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -753,16 +857,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226177.pdf</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226177.pdf</t>
+        </is>
+      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226177.txt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -790,14 +902,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BRIAN JAMISON</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>$330,000.00</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8126 W WATKINS ST</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85043</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -807,12 +947,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>104-33-181</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>$330,000.00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>20210626779</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -823,16 +987,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226185.pdf</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226185.pdf</t>
+        </is>
+      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226185.txt</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -860,14 +1032,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CANDICE AUGE AND TODD AUGE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4202 E EVERETT DR</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85032</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -877,12 +1077,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>215-71-184</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>20220200328</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -893,16 +1117,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226190.pdf</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226190.pdf</t>
+        </is>
+      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226190.txt</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -930,14 +1162,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HELEN E CHARLES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>$246,500.00</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>9810 N BALBOA DR</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SUN CITY</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -947,12 +1207,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>142-84-801</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>$246,500.00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>20210829918</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -963,16 +1247,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226195.pdf</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226195.pdf</t>
+        </is>
+      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226195.txt</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1000,14 +1292,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YOLANDA MCKIM AND BILLY MCKIM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>$335,805.00</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3937 W MYRTLE AVE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1017,12 +1337,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>151-26-142</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>$335,805.00</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>20210660360</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
@@ -1033,16 +1373,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226197.pdf</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226197.pdf</t>
+        </is>
+      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226197.txt</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1070,14 +1418,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ROBERT FARMER</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>$205,128.00</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14300 W BELL RD UNIT 52</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SURPRISE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85374</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1087,12 +1463,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>503-59-212B</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>$205,128.00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>20230106079</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1103,16 +1503,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226200.pdf</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226200.pdf</t>
+        </is>
+      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226200.txt</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1140,14 +1548,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NIRA WANNARKA AND WILLIAM DIXON</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$381,562.00</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2330 W SPENCER RUN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1157,12 +1593,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>105-65-525</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>$381,562.00</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>20220610672</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1173,16 +1629,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226202.pdf</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226202.pdf</t>
+        </is>
+      </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226202.txt</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1210,9 +1674,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GOOD NEWS GROUP, LLC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>$374,000.00</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -1227,12 +1703,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>155-53-014</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>$374,000.00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>(949) 427-2010</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>20230215291</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -1243,16 +1739,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226317.pdf</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226317.pdf</t>
+        </is>
+      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226317.txt</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1280,14 +1784,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CAROLINE ANN BRICKELL AND SEAN GENZMER</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>$252,340.00</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>21003 N 123RD DR</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1297,12 +1829,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>232-14-036</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>$252,340.00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>7/30/2026</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>20211376027</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
@@ -1313,16 +1869,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226412.pdf</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226412.pdf</t>
+        </is>
+      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226412.txt</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1352,12 +1916,32 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>$238,500.00</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11122 W Montana Ave.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Youngtown</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85363</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1368,11 +1952,19 @@
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>$238,500.00</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>20260226657</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -1383,16 +1975,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226657.pdf</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226657.pdf</t>
+        </is>
+      </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, owner_suspect, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226657.txt</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1420,14 +2020,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BOBBI SCHULTZ AS</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$275,000.00</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10437 W CHERYL DR</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SUN CITY</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1438,11 +2062,19 @@
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>$275,000.00</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>20220716841</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -1453,16 +2085,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226771.pdf</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226771.pdf</t>
+        </is>
+      </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226771.txt</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1490,14 +2130,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>LUIS ALONSO MIRANDA GOMEZ</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>$122,042.00</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>520 E HARRISON DR</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>AVONDALE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -1508,11 +2172,19 @@
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>$122,042.00</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>20180831169</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
@@ -1523,16 +2195,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226956.pdf</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226956.pdf</t>
+        </is>
+      </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226956.txt</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1560,14 +2240,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON, AND ANTHONY DE LEON</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>$323,000.00</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30306 WEST PORTLAND STREET</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>BUCKEYE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85396</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1577,12 +2285,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>504-15-159</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>$323,000.00</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>20220847791</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
@@ -1593,16 +2321,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226960.pdf</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226960.pdf</t>
+        </is>
+      </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226960.txt</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1630,14 +2366,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JASON DANIEL MURRAY AND AMBER MURRAY</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>$235,653.00</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3307 W ECHO LN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1648,11 +2408,19 @@
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>$235,653.00</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>20220865242</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
@@ -1663,16 +2431,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227028.pdf</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227028.pdf</t>
+        </is>
+      </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227028.txt</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1700,14 +2476,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>JORDAN OLIVA</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$427,696.00</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22229 E VIA DEL PALO</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -1718,11 +2518,19 @@
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>$427,696.00</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>20211161722</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
@@ -1733,16 +2541,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227091.pdf</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227091.pdf</t>
+        </is>
+      </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227091.txt</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1770,14 +2586,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RUSTY ROBERTS AND NICHOLE ROBERTS</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>$1,138,564.00</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8145 W CAMINO DE ORO</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PEORIA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85383</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -1788,11 +2628,19 @@
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>$1,138,564.00</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>20230154699</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
@@ -1803,16 +2651,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227136.pdf</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227136.pdf</t>
+        </is>
+      </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227136.txt</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1840,14 +2696,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>RYMAX DEVELOPMENT, L.L.C.</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>$480,000.00</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18245 N PIMA ROAD UNIT 1049</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>SCOTTSDALE</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -1857,12 +2737,24 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>113-25-059</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>$480,000.00</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>20240565279</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
@@ -1873,16 +2765,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227218.pdf</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227218.pdf</t>
+        </is>
+      </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227218.txt</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1910,9 +2810,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TITAN FAMILY REALESTATE LLC</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>$110,000.00</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1927,12 +2835,24 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>102-84-270</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>$110,000.00</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>20260014942</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
@@ -1943,16 +2863,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227219.pdf</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227219.pdf</t>
+        </is>
+      </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227219.txt</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1980,9 +2908,17 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Graciela Bucio Perez</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>$176,000.00</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1997,12 +2933,24 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>206-20-159</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>$176,000.00</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>20240141383</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
@@ -2013,16 +2961,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227220.pdf</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227220.pdf</t>
+        </is>
+      </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227220.txt</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2050,14 +3006,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JOSEPH VERDUZCO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>$294,405.00</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2830 S. CHATSWORTH</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85212</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -2067,12 +3051,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>309-19-162</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>$294,405.00</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>20180174392</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
@@ -2083,16 +3087,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227284.pdf</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227284.pdf</t>
+        </is>
+      </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227284.txt</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2122,12 +3134,32 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>$10,000,000.00</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7508 N. 59th Avenue</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -2138,11 +3170,19 @@
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>$10,000,000.00</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>20240432575</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
@@ -2153,16 +3193,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227302.pdf</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227302.pdf</t>
+        </is>
+      </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, owner_suspect, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227302.txt</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2190,14 +3238,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BRENDA FAE HUBBARD</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>$192,449.00</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>9113 E BUTTERNUT AVE</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>85208</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -2207,12 +3283,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>218-41-190</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>$192,449.00</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>20220610270</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
@@ -2223,16 +3323,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227512.pdf</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227512.pdf</t>
+        </is>
+      </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227512.txt</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2260,14 +3368,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ZHONG K WANG AND FRANCIS N PRICE, AND MAN AND FRANCIS PRICE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>$200,000.00</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>12546 W MANDALAY LANE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>EL MIRAGE</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -2277,12 +3413,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>509-13-497</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>$200,000.00</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>20190030161</t>
+        </is>
+      </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
@@ -2293,16 +3453,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227521.pdf</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227521.pdf</t>
+        </is>
+      </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227521.txt</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2330,14 +3498,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Wayne Carpenter</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>$50,000.00</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>7486 S Sundown Ct</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -2348,11 +3544,31 @@
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>$50,000.00</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>July 30, 2026</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>20250322044</t>
+        </is>
+      </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
@@ -2363,16 +3579,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227539.pdf</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227539.pdf</t>
+        </is>
+      </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227539.txt</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2401,13 +3625,37 @@
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>$337,252.80</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>21823 NORTH MAYA COURT</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -2417,12 +3665,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>232-31-246</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>$337,252.80</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>20150216695</t>
+        </is>
+      </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
@@ -2433,16 +3701,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227902.pdf</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227902.pdf</t>
+        </is>
+      </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, owner_suspect, auction_date_missing</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227902.txt</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2470,14 +3746,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Frances Garcia</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>$68,000.00</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2802 West Madison Street</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -2488,11 +3792,31 @@
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>$68,000.00</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>August 6, 2026</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>20070558292</t>
+        </is>
+      </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
@@ -2503,16 +3827,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227926.pdf</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227926.pdf</t>
+        </is>
+      </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227926.txt</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2540,14 +3872,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Luis Vincente Gurrola Martinez</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>$233,100.00</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4107 W Krall St</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
@@ -2558,11 +3918,31 @@
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>$233,100.00</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>August 6, 2026</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>20210644498</t>
+        </is>
+      </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
@@ -2573,16 +3953,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227939.pdf</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227939.pdf</t>
+        </is>
+      </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227939.txt</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2610,14 +3998,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Christine Lea Kurtz-Ford</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>$121,000.00</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>630 E Jensen St Unit 138</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85203</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -2628,11 +4044,31 @@
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>$121,000.00</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>August 6, 2026</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>20200923660</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
@@ -2643,16 +4079,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227955.pdf</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227955.pdf</t>
+        </is>
+      </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227955.txt</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2680,14 +4124,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Martin V Valadez, and Velazquez David Valadez</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>$380,000.00</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3708 West Berridge Lane</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
@@ -2698,11 +4170,31 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>$380,000.00</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>August 6, 2026</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>20230558787</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
@@ -2713,16 +4205,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227961.pdf</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227961.pdf</t>
+        </is>
+      </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227961.txt</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2750,14 +4250,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Richard L Bristol and Grace A Bristol</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>$149,055.00</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>20803 W Bradley Road</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Wittmann</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>85361</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
@@ -2768,11 +4296,31 @@
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>$149,055.00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>August 6, 2026</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>20160249869</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
@@ -2783,16 +4331,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227974.pdf</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227974.pdf</t>
+        </is>
+      </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227974.txt</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2822,7 +4378,11 @@
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>$725,000.00</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -2838,11 +4398,19 @@
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>$725,000.00</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>20260228010</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -2853,16 +4421,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228010.pdf</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228010.pdf</t>
+        </is>
+      </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, owner_suspect, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
-      <c r="AH33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228010.txt</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2890,14 +4466,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rene Campa, and Sebastian Campa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>$368,207.00</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>5214 W Cholla St</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85304</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
@@ -2908,11 +4512,31 @@
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>$368,207.00</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>August 6, 2026</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>20230235369</t>
+        </is>
+      </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
@@ -2923,16 +4547,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228017.pdf</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228017.pdf</t>
+        </is>
+      </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228017.txt</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2960,14 +4592,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lynda Peretz</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>$187,000.00</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>325 E. Anderson Ave.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -2978,11 +4638,31 @@
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>$187,000.00</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>July 30, 2026</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>20080235349</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
@@ -2993,16 +4673,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228048.pdf</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228048.pdf</t>
+        </is>
+      </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228048.txt</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3030,9 +4718,21 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>RICHARDO MONTES IBARBOL AND ABAGAIL ALEXXIS MENDEZ AND MARIA THERESA IBARBOL CRUZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>$380,972.00</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -3047,12 +4747,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>152-19-145</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>$380,972.00</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>20230467168</t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
@@ -3063,16 +4783,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228059.pdf</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228059.pdf</t>
+        </is>
+      </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228059.txt</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3100,14 +4828,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>YAVIN JAY CRANSHAW</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>$363,298.00</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4454 W PIUTE AVE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -3118,11 +4870,19 @@
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>$363,298.00</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>20210904536</t>
+        </is>
+      </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
@@ -3133,16 +4893,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228370.pdf</t>
         </is>
       </c>
-      <c r="AE37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228370.pdf</t>
+        </is>
+      </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228370.txt</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3170,14 +4938,38 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JUAN CARRANZA</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>$286,805.00</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>19559 W LINCOLN STREET</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>BUCKEYE</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
@@ -3188,11 +4980,19 @@
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>$286,805.00</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>20190734079</t>
+        </is>
+      </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
@@ -3203,16 +5003,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228380.pdf</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228380.pdf</t>
+        </is>
+      </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228380.txt</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3240,14 +5048,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BLANCA M ARMENTA QUINONEZ, AND MICHAEL G ARMENTA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>$280,819.00</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2108 W HADLEY ST</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
@@ -3257,12 +5093,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>109-64-004</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>$280,819.00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>20240076207</t>
+        </is>
+      </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
@@ -3273,16 +5133,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228499.pdf</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228499.pdf</t>
+        </is>
+      </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228499.txt</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3310,14 +5178,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Andrew S Kulin and Kasie M Lambros</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>$372,000.00</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1923 E PRESIDIO RD</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
@@ -3327,12 +5223,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>166-41-057</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>$372,000.00</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>7/23/2026</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>20210942675</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -3343,16 +5263,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228514.pdf</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228514.pdf</t>
+        </is>
+      </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228514.txt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -715,7 +715,11 @@
           <t>(866) 931-0036</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>4/13/2026</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>20180610512</t>
@@ -738,7 +742,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -778,7 +782,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>RONALD HODNE, AND LA TOYA GUEVARA</t>
+          <t>RONALD HODNE AND LA TOYA GUEVARA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -841,7 +845,11 @@
           <t>(949) 252-8300</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>July 23, 2026</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>20230570155</t>
@@ -864,7 +872,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -1357,7 +1365,11 @@
           <t>(949) 252-8300</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>July 23, 2026</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>20210660360</t>
@@ -1380,7 +1392,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG7" t="n">
@@ -1613,7 +1625,11 @@
           <t>(949) 252-8300</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>July 23, 2026</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>20220610672</t>
@@ -1636,7 +1652,7 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG9" t="n">
@@ -1723,7 +1739,11 @@
           <t>(949) 427-2010</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>7/28/2026</t>
+        </is>
+      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>20230215291</t>
@@ -1746,7 +1766,7 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG10" t="n">
@@ -1959,7 +1979,11 @@
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>July 22, 2026</t>
+        </is>
+      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>20260226657</t>
@@ -1982,7 +2006,7 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, owner_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2022,10 +2046,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BOBBI SCHULTZ AS</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>BOBBI SCHULTZ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>$275,000.00</t>
@@ -2067,9 +2095,21 @@
           <t>$275,000.00</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>07/22/2026</t>
+        </is>
+      </c>
       <c r="X13" t="inlineStr">
         <is>
           <t>20220716841</t>
@@ -2092,11 +2132,11 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2135,7 +2175,11 @@
           <t>LUIS ALONSO MIRANDA GOMEZ</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>$122,042.00</t>
@@ -2177,9 +2221,21 @@
           <t>$122,042.00</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr">
         <is>
           <t>20180831169</t>
@@ -2202,11 +2258,11 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2242,7 +2298,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON, AND ANTHONY DE LEON</t>
+          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON AND ANTHONY DE LEON</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2305,7 +2361,11 @@
           <t>(949) 252-8300</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>July 21, 2026</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr">
         <is>
           <t>20220847791</t>
@@ -2328,7 +2388,7 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG15" t="n">
@@ -2371,7 +2431,11 @@
           <t>JASON DANIEL MURRAY AND AMBER MURRAY</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>$235,653.00</t>
@@ -2413,9 +2477,21 @@
           <t>$235,653.00</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr">
         <is>
           <t>20220865242</t>
@@ -2438,11 +2514,11 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2481,7 +2557,11 @@
           <t>JORDAN OLIVA</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>$427,696.00</t>
@@ -2523,9 +2603,21 @@
           <t>$427,696.00</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr">
         <is>
           <t>20211161722</t>
@@ -2548,11 +2640,11 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -2591,7 +2683,11 @@
           <t>RUSTY ROBERTS AND NICHOLE ROBERTS</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>$1,138,564.00</t>
@@ -2633,9 +2729,21 @@
           <t>$1,138,564.00</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>07/23/2026</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>20230154699</t>
@@ -2658,11 +2766,11 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -2701,7 +2809,11 @@
           <t>RYMAX DEVELOPMENT, L.L.C.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -2747,8 +2859,16 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>(602) 488-1349</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
@@ -2776,7 +2896,7 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -2815,7 +2935,11 @@
           <t>TITAN FAMILY REALESTATE LLC</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>$110,000.00</t>
@@ -2845,9 +2969,21 @@
           <t>$110,000.00</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>(602) 488-1349</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1/09/2026</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr">
         <is>
           <t>20260014942</t>
@@ -2870,11 +3006,11 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -2913,7 +3049,11 @@
           <t>Graciela Bucio Perez</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>$176,000.00</t>
@@ -2943,9 +3083,21 @@
           <t>$176,000.00</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>(602) 488-1349</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>JULY 20, 2026</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
           <t>20240141383</t>
@@ -2968,11 +3120,11 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3071,7 +3223,11 @@
           <t>(949) 252-8300</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>July 23, 2026</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr">
         <is>
           <t>20180174392</t>
@@ -3094,7 +3250,7 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG22" t="n">
@@ -3370,7 +3526,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ZHONG K WANG AND FRANCIS N PRICE, AND MAN AND FRANCIS PRICE</t>
+          <t>ZHONG K WANG AND FRANCIS N PRICE AND MAN AND FRANCIS PRICE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3685,7 +3841,11 @@
           <t>(949) 252-8300</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>June 2, 2026</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr">
         <is>
           <t>20150216695</t>
@@ -3708,7 +3868,7 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, auction_date_missing</t>
+          <t>ocr_fallback, owner_suspect</t>
         </is>
       </c>
       <c r="AG27" t="n">
@@ -4126,7 +4286,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Martin V Valadez, and Velazquez David Valadez</t>
+          <t>Martin V Valadez AND Velazquez David Valadez</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4405,7 +4565,11 @@
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>July 16, 2026</t>
+        </is>
+      </c>
       <c r="X33" t="inlineStr">
         <is>
           <t>20260228010</t>
@@ -4428,7 +4592,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, owner_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG33" t="n">
@@ -4468,7 +4632,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rene Campa, and Sebastian Campa</t>
+          <t>Rene Campa AND Sebastian Campa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4767,7 +4931,11 @@
           <t>(866) 931-0036</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>4/14/2026</t>
+        </is>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
           <t>20230467168</t>
@@ -4790,7 +4958,7 @@
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG36" t="n">
@@ -4833,7 +5001,11 @@
           <t>YAVIN JAY CRANSHAW</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>$363,298.00</t>
@@ -4875,9 +5047,21 @@
           <t>$363,298.00</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>07/30/2026</t>
+        </is>
+      </c>
       <c r="X37" t="inlineStr">
         <is>
           <t>20210904536</t>
@@ -4900,11 +5084,11 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -4943,7 +5127,11 @@
           <t>JUAN CARRANZA</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>$286,805.00</t>
@@ -4985,9 +5173,21 @@
           <t>$286,805.00</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>07/30/2026</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr">
         <is>
           <t>20190734079</t>
@@ -5010,11 +5210,11 @@
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -5050,7 +5250,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BLANCA M ARMENTA QUINONEZ, AND MICHAEL G ARMENTA</t>
+          <t>BLANCA M ARMENTA QUINONEZ AND MICHAEL G ARMENTA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -438,7 +438,7 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="34" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>4/13/2026</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>20180610512</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -847,12 +847,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>July 23, 2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>20230570155</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -977,12 +977,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>7/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>20210626779</t>
+          <t>2021-06-07</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>7/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>20220200328</t>
+          <t>2022-03-03</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>7/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>20210829918</t>
+          <t>2021-07-29</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>July 23, 2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>20210660360</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>7/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>20230106079</t>
+          <t>2023-03-02</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>July 23, 2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>20220610672</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1741,12 +1741,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>7/28/2026</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>20230215291</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>7/30/2026</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>20211376027</t>
+          <t>2021-12-23</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1981,12 +1981,12 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>July 22, 2026</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>20260226657</t>
+          <t>2024-02-29</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>07/22/2026</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>20220716841</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>07/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>20180831169</t>
+          <t>2018-11-07</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>July 21, 2026</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>20220847791</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>07/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>20220865242</t>
+          <t>2022-11-30</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2615,12 +2615,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>07/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>20211161722</t>
+          <t>2021-10-28</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2741,12 +2741,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>07/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>20230154699</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2872,7 +2872,7 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
-          <t>20240565279</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1/09/2026</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>20260014942</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3095,12 +3095,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>JULY 20, 2026</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>20240141383</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3225,12 +3225,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>July 23, 2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>20180174392</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3336,7 +3336,7 @@
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>20240432575</t>
+          <t>2024-08-10</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>7/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>20220610270</t>
+          <t>2022-07-28</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3591,12 +3591,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>7/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>20190030161</t>
+          <t>2019-01-15</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3717,14 +3717,10 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>July 30, 2026</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>20250322044</t>
-        </is>
-      </c>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
@@ -3843,12 +3839,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>June 2, 2026</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>20150216695</t>
+          <t>2015-03-31</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -3969,14 +3965,10 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>August 6, 2026</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>20070558292</t>
-        </is>
-      </c>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
@@ -4095,14 +4087,10 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>August 6, 2026</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>20210644498</t>
-        </is>
-      </c>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
@@ -4221,14 +4209,10 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>August 6, 2026</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>20200923660</t>
-        </is>
-      </c>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
@@ -4347,14 +4331,10 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>August 6, 2026</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>20230558787</t>
-        </is>
-      </c>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
@@ -4473,14 +4453,10 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>August 6, 2026</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>20160249869</t>
-        </is>
-      </c>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
@@ -4567,12 +4543,12 @@
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
-          <t>July 16, 2026</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>20260228010</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4693,14 +4669,10 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>August 6, 2026</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>20230235369</t>
-        </is>
-      </c>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
@@ -4819,12 +4791,12 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>July 30, 2026</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>20080235349</t>
+          <t>2008-02-05</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -4933,12 +4905,12 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>4/14/2026</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>20230467168</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5059,12 +5031,12 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>07/30/2026</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>20210904536</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5185,12 +5157,12 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>07/30/2026</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>20190734079</t>
+          <t>2019-09-18</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5315,12 +5287,12 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>7/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>20240076207</t>
+          <t>2024-02-14</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5445,12 +5417,12 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>7/23/2026</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>20210942675</t>
+          <t>2021-08-30</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -425,8 +425,8 @@
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="29" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -1706,7 +1706,11 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1802 WEST PIERSON STREET</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1770,7 +1774,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -1944,7 +1948,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11122 W Montana Ave.</t>
+          <t>11122 W Montana Ave</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2822,12 +2826,12 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18245 N PIMA ROAD UNIT 1049</t>
+          <t>4037 S. 12th Street</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SCOTTSDALE</t>
+          <t>th Street Phoenix</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2946,7 +2950,11 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5420 W. Onyx Ave</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -3010,7 +3018,7 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3060,7 +3068,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5420 W. Onyx Ave</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -3124,7 +3136,7 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3298,24 +3310,12 @@
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>7508 N. 59th Avenue</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Glendale</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>85301</t>
-        </is>
-      </c>
+          <t>1429 N. Scottsdale Road</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ZHONG K WANG AND FRANCIS N PRICE AND MAN AND FRANCIS PRICE</t>
+          <t>ZHONG K WANG AND FRANCIS N PRICE AND FRANCIS PRICE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4520,7 +4520,11 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>7537 E. McDonald Drive</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -4572,7 +4576,7 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -4870,10 +4874,26 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>3939 W CAVALIER DR</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
@@ -4934,7 +4954,7 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -422,7 +422,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
@@ -436,7 +436,7 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="34" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
@@ -447,7 +447,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="60" customWidth="1" min="32" max="32"/>
+    <col width="52" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -1939,7 +1939,11 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Unofficial Document</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>$238,500.00</t>
@@ -1981,7 +1985,11 @@
           <t>$238,500.00</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Unofficial Document</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
@@ -2014,7 +2022,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -3300,8 +3308,16 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mani Hotels, LLC State Bank of Texas</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MOUNTAIN STANDARD TIME OF THE LAST BUSINESS DAY BEFORE THE</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>$10,000,000.00</t>
@@ -3331,7 +3347,11 @@
           <t>$10,000,000.00</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>MOUNTAIN STANDARD TIME OF THE LAST BUSINESS DAY BEFORE THE</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
@@ -3356,11 +3376,11 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -3776,7 +3796,11 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>WHEREAS, the Deed of Trust was insured by the United States Secretary of Housing and Urban</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>MTC FINANCIAL INC</t>
@@ -3864,11 +3888,11 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4512,8 +4536,16 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Strong Base, LLC</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>on November 27, 2024, as instrument number 2024-0637955, executed by Strong Base, LLC</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>$725,000.00</t>
@@ -4543,8 +4575,16 @@
           <t>$725,000.00</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>on November 27, 2024, as instrument number 2024-0637955, executed by Strong Base, LLC</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>024-0637955</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -4572,11 +4612,11 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -421,12 +421,12 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -435,9 +435,9 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
@@ -446,10 +446,10 @@
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="52" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,14 +650,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>STERLING M. GRANT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>$236,880.00</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19079 E SEAGULL DR</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -667,12 +695,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>314-05-709</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>$236,880.00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2018-08-08</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -683,16 +735,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225916.pdf</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225916.pdf</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225916.txt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -720,14 +780,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RONALD HODNE AND LA TOYA GUEVARA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>$690,900.00</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13910 S 180TH AVE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -737,12 +825,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>400-82-358</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>$690,900.00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -753,16 +865,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226177.pdf</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226177.pdf</t>
+        </is>
+      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226177.txt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -790,14 +910,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BRIAN JAMISON</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>$330,000.00</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8126 W WATKINS ST</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85043</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -807,12 +955,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>104-33-181</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>$330,000.00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -823,16 +995,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226185.pdf</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226185.pdf</t>
+        </is>
+      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226185.txt</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -860,14 +1040,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CANDICE AUGE AND TODD AUGE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4202 E EVERETT DR</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85032</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -877,12 +1085,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>215-71-184</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -893,16 +1125,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226190.pdf</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226190.pdf</t>
+        </is>
+      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226190.txt</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -930,14 +1170,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HELEN E CHARLES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>$246,500.00</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>9810 N BALBOA DR</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SUN CITY</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -947,12 +1215,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>142-84-801</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>$246,500.00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2021-07-29</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -963,16 +1255,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226195.pdf</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226195.pdf</t>
+        </is>
+      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226195.txt</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1000,14 +1300,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YOLANDA MCKIM AND BILLY MCKIM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>$335,805.00</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3937 W MYRTLE AVE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1017,12 +1345,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>151-26-142</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>$335,805.00</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
@@ -1033,16 +1385,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226197.pdf</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226197.pdf</t>
+        </is>
+      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226197.txt</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1070,14 +1430,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ROBERT FARMER</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>$205,128.00</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14300 W BELL RD UNIT 52</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SURPRISE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85374</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1087,12 +1475,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>503-59-212B</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>$205,128.00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1103,16 +1515,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226200.pdf</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226200.pdf</t>
+        </is>
+      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226200.txt</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1140,14 +1560,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NIRA WANNARKA AND WILLIAM DIXON</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$381,562.00</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2330 W SPENCER RUN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1157,12 +1605,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>105-65-525</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>$381,562.00</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1173,16 +1645,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226202.pdf</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226202.pdf</t>
+        </is>
+      </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226202.txt</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1210,11 +1690,27 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GOOD NEWS GROUP, LLC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>$374,000.00</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1802 WEST PIERSON STREET</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1227,12 +1723,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>155-53-014</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>$374,000.00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>(949) 427-2010</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -1243,16 +1763,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226317.pdf</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226317.pdf</t>
+        </is>
+      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226317.txt</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1280,14 +1808,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CAROLINE ANN BRICKELL AND SEAN GENZMER</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>$252,340.00</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>21003 N 123RD DR</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1297,12 +1853,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>232-14-036</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>$252,340.00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2021-12-23</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
@@ -1313,16 +1893,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226412.pdf</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226412.pdf</t>
+        </is>
+      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226412.txt</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1351,13 +1939,37 @@
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Unofficial Document</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>$238,500.00</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11122 W Montana Ave</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Youngtown</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85363</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -1368,11 +1980,27 @@
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>$238,500.00</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Unofficial Document</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -1383,16 +2011,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226657.pdf</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226657.pdf</t>
+        </is>
+      </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, owner_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226657.txt</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1420,14 +2056,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BOBBI SCHULTZ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$275,000.00</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10437 W CHERYL DR</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SUN CITY</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1438,11 +2102,31 @@
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>$275,000.00</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -1453,16 +2137,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226771.pdf</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226771.pdf</t>
+        </is>
+      </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226771.txt</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1490,14 +2182,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>LUIS ALONSO MIRANDA GOMEZ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>$122,042.00</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>520 E HARRISON DR</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>AVONDALE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -1508,11 +2228,31 @@
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>$122,042.00</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2018-11-07</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
@@ -1523,16 +2263,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226956.pdf</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226956.pdf</t>
+        </is>
+      </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226956.txt</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1560,14 +2308,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON AND ANTHONY DE LEON</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>$323,000.00</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30306 WEST PORTLAND STREET</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>BUCKEYE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85396</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1577,12 +2353,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>504-15-159</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>$323,000.00</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
@@ -1593,16 +2393,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226960.pdf</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226960.pdf</t>
+        </is>
+      </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226960.txt</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1630,14 +2438,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JASON DANIEL MURRAY AND AMBER MURRAY</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>$235,653.00</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3307 W ECHO LN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1648,11 +2484,31 @@
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>$235,653.00</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2022-11-30</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
@@ -1663,16 +2519,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227028.pdf</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227028.pdf</t>
+        </is>
+      </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227028.txt</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1700,14 +2564,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>JORDAN OLIVA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$427,696.00</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22229 E VIA DEL PALO</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -1718,11 +2610,31 @@
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>$427,696.00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
@@ -1733,16 +2645,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227091.pdf</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227091.pdf</t>
+        </is>
+      </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227091.txt</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1770,14 +2690,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RUSTY ROBERTS AND NICHOLE ROBERTS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>$1,138,564.00</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8145 W CAMINO DE ORO</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PEORIA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85383</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -1788,11 +2736,31 @@
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>$1,138,564.00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2023-03-28</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
@@ -1803,16 +2771,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227136.pdf</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227136.pdf</t>
+        </is>
+      </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227136.txt</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1840,14 +2816,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>RYMAX DEVELOPMENT, L.L.C.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>$480,000.00</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4037 S. 12th Street</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>th Street Phoenix</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -1857,12 +2861,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>113-25-059</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>$480,000.00</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>(602) 488-1349</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
@@ -1873,16 +2897,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227218.pdf</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227218.pdf</t>
+        </is>
+      </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227218.txt</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1910,11 +2942,27 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TITAN FAMILY REALESTATE LLC</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>$110,000.00</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5420 W. Onyx Ave</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -1927,12 +2975,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>102-84-270</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>$110,000.00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>(602) 488-1349</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
@@ -1943,16 +3015,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227219.pdf</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227219.pdf</t>
+        </is>
+      </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227219.txt</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1980,11 +3060,27 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Graciela Bucio Perez</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>$176,000.00</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5420 W. Onyx Ave</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -1997,12 +3093,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>206-20-159</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>$176,000.00</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>(602) 488-1349</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
@@ -2013,16 +3133,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227220.pdf</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227220.pdf</t>
+        </is>
+      </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227220.txt</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2050,14 +3178,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JOSEPH VERDUZCO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>$294,405.00</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2830 S. CHATSWORTH</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85212</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -2067,12 +3223,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>309-19-162</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>$294,405.00</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
@@ -2083,16 +3263,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227284.pdf</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227284.pdf</t>
+        </is>
+      </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227284.txt</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2120,11 +3308,27 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mani Hotels, LLC State Bank of Texas</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MOUNTAIN STANDARD TIME OF THE LAST BUSINESS DAY BEFORE THE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>$10,000,000.00</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1429 N. Scottsdale Road</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -2138,11 +3342,23 @@
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>$10,000,000.00</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>MOUNTAIN STANDARD TIME OF THE LAST BUSINESS DAY BEFORE THE</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
@@ -2153,16 +3369,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227302.pdf</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227302.pdf</t>
+        </is>
+      </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227302.txt</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2190,14 +3414,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BRENDA FAE HUBBARD</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>$192,449.00</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>9113 E BUTTERNUT AVE</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>85208</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -2207,12 +3459,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>218-41-190</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>$192,449.00</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
@@ -2223,16 +3499,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227512.pdf</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227512.pdf</t>
+        </is>
+      </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227512.txt</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2260,14 +3544,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ZHONG K WANG AND FRANCIS N PRICE AND FRANCIS PRICE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>$200,000.00</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>12546 W MANDALAY LANE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>EL MIRAGE</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -2277,12 +3589,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>509-13-497</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>$200,000.00</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2019-01-15</t>
+        </is>
+      </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
@@ -2293,16 +3629,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227521.pdf</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227521.pdf</t>
+        </is>
+      </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227521.txt</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2330,14 +3674,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Wayne Carpenter</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>$50,000.00</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>7486 S Sundown Ct</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -2348,10 +3720,26 @@
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>$50,000.00</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
@@ -2363,16 +3751,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227539.pdf</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227539.pdf</t>
+        </is>
+      </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227539.txt</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2400,14 +3796,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>WHEREAS, the Deed of Trust was insured by the United States Secretary of Housing and Urban</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>$337,252.80</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>21823 NORTH MAYA COURT</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -2417,12 +3841,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>232-31-246</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>$337,252.80</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2015-03-31</t>
+        </is>
+      </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
@@ -2433,16 +3881,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227902.pdf</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227902.pdf</t>
+        </is>
+      </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227902.txt</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2470,14 +3926,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Frances Garcia</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>$68,000.00</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2802 West Madison Street</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -2488,10 +3972,26 @@
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>$68,000.00</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
@@ -2503,16 +4003,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227926.pdf</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227926.pdf</t>
+        </is>
+      </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227926.txt</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2540,14 +4048,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Luis Vincente Gurrola Martinez</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>$233,100.00</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4107 W Krall St</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
@@ -2558,10 +4094,26 @@
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>$233,100.00</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
@@ -2573,16 +4125,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227939.pdf</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227939.pdf</t>
+        </is>
+      </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227939.txt</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2610,14 +4170,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Christine Lea Kurtz-Ford</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>$121,000.00</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>630 E Jensen St Unit 138</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85203</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -2628,10 +4216,26 @@
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>$121,000.00</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
@@ -2643,16 +4247,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227955.pdf</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227955.pdf</t>
+        </is>
+      </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227955.txt</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2680,14 +4292,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Martin V Valadez AND Velazquez David Valadez</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>$380,000.00</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3708 West Berridge Lane</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
@@ -2698,10 +4338,26 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>$380,000.00</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
@@ -2713,16 +4369,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227961.pdf</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227961.pdf</t>
+        </is>
+      </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227961.txt</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2750,14 +4414,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Richard L Bristol and Grace A Bristol</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>$149,055.00</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>20803 W Bradley Road</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Wittmann</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>85361</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
@@ -2768,10 +4460,26 @@
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>$149,055.00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
@@ -2783,16 +4491,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227974.pdf</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227974.pdf</t>
+        </is>
+      </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227974.txt</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2820,11 +4536,27 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Strong Base, LLC</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>on November 27, 2024, as instrument number 2024-0637955, executed by Strong Base, LLC</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>$725,000.00</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>7537 E. McDonald Drive</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2838,11 +4570,31 @@
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>$725,000.00</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>on November 27, 2024, as instrument number 2024-0637955, executed by Strong Base, LLC</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>024-0637955</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -2853,16 +4605,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228010.pdf</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228010.pdf</t>
+        </is>
+      </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228010.txt</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2890,14 +4650,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rene Campa AND Sebastian Campa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>$368,207.00</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>5214 W Cholla St</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85304</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
@@ -2908,10 +4696,26 @@
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>$368,207.00</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
@@ -2923,16 +4727,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228017.pdf</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228017.pdf</t>
+        </is>
+      </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228017.txt</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2960,14 +4772,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lynda Peretz</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>$187,000.00</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>325 E. Anderson Ave.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -2978,11 +4818,31 @@
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>$187,000.00</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>2008-02-05</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
@@ -2993,16 +4853,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228048.pdf</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228048.pdf</t>
+        </is>
+      </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228048.txt</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3030,14 +4898,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>RICHARDO MONTES IBARBOL AND ABAGAIL ALEXXIS MENDEZ AND MARIA THERESA IBARBOL CRUZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>$380,972.00</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>3939 W CAVALIER DR</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
@@ -3047,12 +4943,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>152-19-145</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>$380,972.00</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
@@ -3063,16 +4983,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228059.pdf</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228059.pdf</t>
+        </is>
+      </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228059.txt</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3100,14 +5028,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>YAVIN JAY CRANSHAW</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>$363,298.00</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4454 W PIUTE AVE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -3118,11 +5074,31 @@
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>$363,298.00</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
@@ -3133,16 +5109,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228370.pdf</t>
         </is>
       </c>
-      <c r="AE37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228370.pdf</t>
+        </is>
+      </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228370.txt</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3170,14 +5154,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JUAN CARRANZA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>$286,805.00</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>19559 W LINCOLN STREET</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>BUCKEYE</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
@@ -3188,11 +5200,31 @@
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>$286,805.00</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
@@ -3203,16 +5235,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228380.pdf</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228380.pdf</t>
+        </is>
+      </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228380.txt</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3240,14 +5280,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BLANCA M ARMENTA QUINONEZ AND MICHAEL G ARMENTA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>$280,819.00</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2108 W HADLEY ST</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
@@ -3257,12 +5325,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>109-64-004</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>$280,819.00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
@@ -3273,16 +5365,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228499.pdf</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228499.pdf</t>
+        </is>
+      </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228499.txt</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3310,14 +5410,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Andrew S Kulin and Kasie M Lambros</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>$372,000.00</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1923 E PRESIDIO RD</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
@@ -3327,12 +5455,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>166-41-057</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>$372,000.00</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -3343,16 +5495,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228514.pdf</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228514.pdf</t>
+        </is>
+      </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228514.txt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -421,12 +421,12 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -435,9 +435,9 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
@@ -447,7 +447,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="45" customWidth="1" min="32" max="32"/>
+    <col width="52" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -650,14 +650,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>STERLING M. GRANT</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>$236,880.00</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19079 E SEAGULL DR</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -667,12 +695,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>314-05-709</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>$236,880.00</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2018-08-08</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -683,16 +735,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260225916.pdf</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260225916.pdf</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260225916.txt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -720,14 +780,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RONALD HODNE AND LA TOYA GUEVARA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>$690,900.00</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13910 S 180TH AVE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -737,12 +825,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>400-82-358</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>$690,900.00</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
@@ -753,16 +865,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226177.pdf</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226177.pdf</t>
+        </is>
+      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226177.txt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -790,14 +910,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>BRIAN JAMISON</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>$330,000.00</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8126 W WATKINS ST</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>85043</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -807,12 +955,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>104-33-181</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>$330,000.00</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2021-06-07</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
@@ -823,16 +995,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226185.pdf</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226185.pdf</t>
+        </is>
+      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226185.txt</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -860,14 +1040,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CANDICE AUGE AND TODD AUGE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>4202 E EVERETT DR</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85032</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -877,12 +1085,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>215-71-184</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>$285,000.00</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2022-03-03</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
@@ -893,16 +1125,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226190.pdf</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226190.pdf</t>
+        </is>
+      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226190.txt</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -930,14 +1170,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>HELEN E CHARLES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>$246,500.00</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>9810 N BALBOA DR</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SUN CITY</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -947,12 +1215,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>142-84-801</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>$246,500.00</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>2021-07-29</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
@@ -963,16 +1255,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226195.pdf</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226195.pdf</t>
+        </is>
+      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226195.txt</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1000,14 +1300,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YOLANDA MCKIM AND BILLY MCKIM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>$335,805.00</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>3937 W MYRTLE AVE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1017,12 +1345,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>151-26-142</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>$335,805.00</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
@@ -1033,16 +1385,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226197.pdf</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226197.pdf</t>
+        </is>
+      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226197.txt</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1070,14 +1430,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ROBERT FARMER</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>$205,128.00</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>14300 W BELL RD UNIT 52</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SURPRISE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85374</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -1087,12 +1475,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>503-59-212B</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>$205,128.00</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2023-03-02</t>
+        </is>
+      </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1103,16 +1515,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226200.pdf</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226200.pdf</t>
+        </is>
+      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226200.txt</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1140,14 +1560,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>NIRA WANNARKA AND WILLIAM DIXON</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>$381,562.00</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2330 W SPENCER RUN</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -1157,12 +1605,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>105-65-525</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>$381,562.00</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1173,16 +1645,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226202.pdf</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226202.pdf</t>
+        </is>
+      </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226202.txt</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1210,11 +1690,27 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GOOD NEWS GROUP, LLC</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>$374,000.00</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1802 WEST PIERSON STREET</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1227,12 +1723,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>155-53-014</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>$374,000.00</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>(949) 427-2010</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -1243,16 +1763,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226317.pdf</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226317.pdf</t>
+        </is>
+      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226317.txt</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1280,14 +1808,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CAROLINE ANN BRICKELL AND SEAN GENZMER</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>$252,340.00</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>21003 N 123RD DR</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -1297,12 +1853,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>232-14-036</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>$252,340.00</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2021-12-23</t>
+        </is>
+      </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
@@ -1313,16 +1893,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226412.pdf</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226412.pdf</t>
+        </is>
+      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226412.txt</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1468,14 +2056,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BOBBI SCHULTZ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>$275,000.00</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10437 W CHERYL DR</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SUN CITY</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -1486,11 +2102,31 @@
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>$275,000.00</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -1501,16 +2137,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226771.pdf</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226771.pdf</t>
+        </is>
+      </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226771.txt</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1538,14 +2182,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>LUIS ALONSO MIRANDA GOMEZ</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>$122,042.00</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>520 E HARRISON DR</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>AVONDALE</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -1556,11 +2228,31 @@
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>$122,042.00</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2018-11-07</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
@@ -1571,16 +2263,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226956.pdf</t>
         </is>
       </c>
-      <c r="AE14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226956.pdf</t>
+        </is>
+      </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226956.txt</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1608,14 +2308,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>YOLANDA S. DE LEON AND DOMINGO DE LEON AND ANTHONY DE LEON</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>$323,000.00</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>30306 WEST PORTLAND STREET</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>BUCKEYE</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85396</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -1625,12 +2353,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>504-15-159</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>$323,000.00</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
@@ -1641,16 +2393,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260226960.pdf</t>
         </is>
       </c>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260226960.pdf</t>
+        </is>
+      </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260226960.txt</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1678,14 +2438,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>JASON DANIEL MURRAY AND AMBER MURRAY</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>$235,653.00</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3307 W ECHO LN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -1696,11 +2484,31 @@
         </is>
       </c>
       <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>$235,653.00</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2022-11-30</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
@@ -1711,16 +2519,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227028.pdf</t>
         </is>
       </c>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227028.pdf</t>
+        </is>
+      </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227028.txt</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1748,14 +2564,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>JORDAN OLIVA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>$427,696.00</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22229 E VIA DEL PALO</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -1766,11 +2610,31 @@
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>$427,696.00</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2021-10-28</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
@@ -1781,16 +2645,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227091.pdf</t>
         </is>
       </c>
-      <c r="AE17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227091.pdf</t>
+        </is>
+      </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227091.txt</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1818,14 +2690,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RUSTY ROBERTS AND NICHOLE ROBERTS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>$1,138,564.00</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8145 W CAMINO DE ORO</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>PEORIA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85383</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -1836,11 +2736,31 @@
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>$1,138,564.00</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2023-03-28</t>
+        </is>
+      </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
@@ -1851,16 +2771,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227136.pdf</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227136.pdf</t>
+        </is>
+      </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227136.txt</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1888,14 +2816,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>RYMAX DEVELOPMENT, L.L.C.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>$480,000.00</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4037 S. 12th Street</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>th Street Phoenix</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -1905,12 +2861,32 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>113-25-059</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>$480,000.00</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>(602) 488-1349</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
@@ -1921,16 +2897,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227218.pdf</t>
         </is>
       </c>
-      <c r="AE19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227218.pdf</t>
+        </is>
+      </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227218.txt</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1958,11 +2942,27 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TITAN FAMILY REALESTATE LLC</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>$110,000.00</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5420 W. Onyx Ave</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -1975,12 +2975,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>102-84-270</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>$110,000.00</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>(602) 488-1349</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
@@ -1991,16 +3015,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227219.pdf</t>
         </is>
       </c>
-      <c r="AE20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227219.pdf</t>
+        </is>
+      </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227219.txt</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2028,11 +3060,27 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Graciela Bucio Perez</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>$176,000.00</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5420 W. Onyx Ave</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -2045,12 +3093,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>206-20-159</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>$176,000.00</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>RONALD B. HERB</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>(602) 488-1349</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
@@ -2061,16 +3133,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227220.pdf</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227220.pdf</t>
+        </is>
+      </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227220.txt</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2098,14 +3178,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JOSEPH VERDUZCO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>$294,405.00</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2830 S. CHATSWORTH</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>85212</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -2115,12 +3223,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>309-19-162</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>$294,405.00</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
@@ -2131,16 +3263,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227284.pdf</t>
         </is>
       </c>
-      <c r="AE22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227284.pdf</t>
+        </is>
+      </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227284.txt</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2168,11 +3308,27 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mani Hotels, LLC State Bank of Texas</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>MOUNTAIN STANDARD TIME OF THE LAST BUSINESS DAY BEFORE THE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>$10,000,000.00</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1429 N. Scottsdale Road</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -2186,11 +3342,23 @@
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>$10,000,000.00</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>MOUNTAIN STANDARD TIME OF THE LAST BUSINESS DAY BEFORE THE</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2024-08-10</t>
+        </is>
+      </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
@@ -2201,16 +3369,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227302.pdf</t>
         </is>
       </c>
-      <c r="AE23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227302.pdf</t>
+        </is>
+      </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227302.txt</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2238,14 +3414,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>BRENDA FAE HUBBARD</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>$192,449.00</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>9113 E BUTTERNUT AVE</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>85208</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
@@ -2255,12 +3459,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>218-41-190</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>$192,449.00</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2022-07-28</t>
+        </is>
+      </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
@@ -2271,16 +3499,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227512.pdf</t>
         </is>
       </c>
-      <c r="AE24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227512.pdf</t>
+        </is>
+      </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227512.txt</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2308,14 +3544,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ZHONG K WANG AND FRANCIS N PRICE AND FRANCIS PRICE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>$200,000.00</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>12546 W MANDALAY LANE</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>EL MIRAGE</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -2325,12 +3589,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>509-13-497</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>$200,000.00</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2019-01-15</t>
+        </is>
+      </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
@@ -2341,16 +3629,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227521.pdf</t>
         </is>
       </c>
-      <c r="AE25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227521.pdf</t>
+        </is>
+      </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227521.txt</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2378,14 +3674,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Wayne Carpenter</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>$50,000.00</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>7486 S Sundown Ct</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Buckeye</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -2396,10 +3720,26 @@
         </is>
       </c>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>$50,000.00</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
@@ -2411,16 +3751,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227539.pdf</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227539.pdf</t>
+        </is>
+      </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227539.txt</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2448,14 +3796,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>WHEREAS, the Deed of Trust was insured by the United States Secretary of Housing and Urban</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>$337,252.80</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>21823 NORTH MAYA COURT</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
@@ -2465,12 +3841,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>232-31-246</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>$337,252.80</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>MTC FINANCIAL INC</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>(949) 252-8300</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2015-03-31</t>
+        </is>
+      </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
@@ -2481,16 +3881,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227902.pdf</t>
         </is>
       </c>
-      <c r="AE27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227902.pdf</t>
+        </is>
+      </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227902.txt</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2518,14 +3926,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Frances Garcia</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>$68,000.00</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2802 West Madison Street</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -2536,10 +3972,26 @@
         </is>
       </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>$68,000.00</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
@@ -2551,16 +4003,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227926.pdf</t>
         </is>
       </c>
-      <c r="AE28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227926.pdf</t>
+        </is>
+      </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227926.txt</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2588,14 +4048,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Luis Vincente Gurrola Martinez</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>$233,100.00</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>4107 W Krall St</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
@@ -2606,10 +4094,26 @@
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>$233,100.00</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
@@ -2621,16 +4125,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227939.pdf</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227939.pdf</t>
+        </is>
+      </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227939.txt</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2658,14 +4170,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Christine Lea Kurtz-Ford</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>$121,000.00</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>630 E Jensen St Unit 138</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>85203</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -2676,10 +4216,26 @@
         </is>
       </c>
       <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>$121,000.00</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
@@ -2691,16 +4247,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227955.pdf</t>
         </is>
       </c>
-      <c r="AE30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227955.pdf</t>
+        </is>
+      </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227955.txt</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2728,14 +4292,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Martin V Valadez AND Velazquez David Valadez</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>$380,000.00</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>3708 West Berridge Lane</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
@@ -2746,10 +4338,26 @@
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>$380,000.00</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
@@ -2761,16 +4369,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227961.pdf</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227961.pdf</t>
+        </is>
+      </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227961.txt</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2798,14 +4414,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Richard L Bristol and Grace A Bristol</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>$149,055.00</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>20803 W Bradley Road</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Wittmann</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>85361</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
@@ -2816,10 +4460,26 @@
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>$149,055.00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
@@ -2831,16 +4491,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260227974.pdf</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260227974.pdf</t>
+        </is>
+      </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260227974.txt</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2868,11 +4536,27 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Strong Base, LLC</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>on November 27, 2024, as instrument number 2024-0637955, executed by Strong Base, LLC</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>$725,000.00</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>7537 E. McDonald Drive</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2886,11 +4570,31 @@
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>$725,000.00</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>on November 27, 2024, as instrument number 2024-0637955, executed by Strong Base, LLC</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>024-0637955</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
@@ -2901,16 +4605,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228010.pdf</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228010.pdf</t>
+        </is>
+      </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228010.txt</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2938,14 +4650,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rene Campa AND Sebastian Campa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>$368,207.00</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>5214 W Cholla St</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>85304</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
@@ -2956,10 +4696,26 @@
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>$368,207.00</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
@@ -2971,16 +4727,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228017.pdf</t>
         </is>
       </c>
-      <c r="AE34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228017.pdf</t>
+        </is>
+      </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228017.txt</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3008,14 +4772,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lynda Peretz</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>$187,000.00</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>325 E. Anderson Ave.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -3026,11 +4818,31 @@
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>$187,000.00</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>LEONARD J. MCDONALD</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>(602) 255-6035</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>2008-02-05</t>
+        </is>
+      </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
@@ -3041,16 +4853,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228048.pdf</t>
         </is>
       </c>
-      <c r="AE35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228048.pdf</t>
+        </is>
+      </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228048.txt</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3078,14 +4898,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>RICHARDO MONTES IBARBOL AND ABAGAIL ALEXXIS MENDEZ AND MARIA THERESA IBARBOL CRUZ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>$380,972.00</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>3939 W CAVALIER DR</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>85019</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
@@ -3095,12 +4943,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>152-19-145</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>$380,972.00</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>CLEAR RECON CORP</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
@@ -3111,16 +4983,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228059.pdf</t>
         </is>
       </c>
-      <c r="AE36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228059.pdf</t>
+        </is>
+      </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228059.txt</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3148,14 +5028,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>YAVIN JAY CRANSHAW</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>$363,298.00</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4454 W PIUTE AVE</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
@@ -3166,11 +5074,31 @@
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>$363,298.00</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2021-08-20</t>
+        </is>
+      </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
@@ -3181,16 +5109,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228370.pdf</t>
         </is>
       </c>
-      <c r="AE37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228370.pdf</t>
+        </is>
+      </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228370.txt</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3218,14 +5154,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JUAN CARRANZA</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>$286,805.00</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>19559 W LINCOLN STREET</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>BUCKEYE</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>85326</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
@@ -3236,11 +5200,31 @@
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>$286,805.00</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>PRIME RECON LLC</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>(888) 725-4142</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2019-09-18</t>
+        </is>
+      </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
@@ -3251,16 +5235,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228380.pdf</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228380.pdf</t>
+        </is>
+      </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228380.txt</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3288,14 +5280,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>BLANCA M ARMENTA QUINONEZ AND MICHAEL G ARMENTA</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>$280,819.00</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2108 W HADLEY ST</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
@@ -3305,12 +5325,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>109-64-004</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>$280,819.00</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2024-02-14</t>
+        </is>
+      </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
@@ -3321,16 +5365,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228499.pdf</t>
         </is>
       </c>
-      <c r="AE39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228499.pdf</t>
+        </is>
+      </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228499.txt</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3358,14 +5410,42 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Andrew S Kulin and Kasie M Lambros</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>$372,000.00</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1923 E PRESIDIO RD</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>85022</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
@@ -3375,12 +5455,36 @@
           <t>Maricopa</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>166-41-057</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>$372,000.00</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>QUALITY LOAN SERVICE CORPORATION</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>(866) 645-7711</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>2021-08-30</t>
+        </is>
+      </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -3391,16 +5495,24 @@
           <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260228514.pdf</t>
         </is>
       </c>
-      <c r="AE40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260228514.pdf</t>
+        </is>
+      </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>no_pdf</t>
+          <t>ocr_fallback</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260228514.txt</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -422,11 +422,11 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -436,8 +436,8 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="60" customWidth="1" min="21" max="21"/>
-    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
@@ -447,7 +447,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="60" customWidth="1" min="30" max="30"/>
     <col width="60" customWidth="1" min="31" max="31"/>
-    <col width="52" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
     <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
@@ -655,11 +655,7 @@
           <t>WILLIAM GUNTY AND JENNIFER GUNTY</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>$548,250.00</t>
@@ -705,16 +701,8 @@
           <t>$548,250.00</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -742,11 +730,11 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -782,14 +770,10 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>{} Sarah Rendon AND Patricia Cross, .</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Entra Default Solutions, LLC</t>
-        </is>
-      </c>
+          <t>Sarah Rendon AND Patricia Cross, .</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>$276,822.00</t>
@@ -835,11 +819,7 @@
           <t>$276,822.00</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Entra Default Solutions, LLC</t>
-        </is>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
@@ -868,11 +848,11 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -911,11 +891,7 @@
           <t>RONALD EDWARD DOERLER</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>$874,250.00</t>
@@ -949,16 +925,8 @@
           <t>$874,250.00</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>(949) 427-2010</t>
-        </is>
-      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
           <t>2026-07-21</t>
@@ -986,11 +954,11 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1029,11 +997,7 @@
           <t>WENDY ORTIZ AND JOSEPH ORTIZ</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>$525,000.00</t>
@@ -1079,16 +1043,8 @@
           <t>$525,000.00</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -1116,11 +1072,11 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1159,11 +1115,7 @@
           <t>ALEX M MONTOYAAND CYNTHIA U MONTOYA</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>$285,729.00</t>
@@ -1209,16 +1161,8 @@
           <t>$285,729.00</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -1246,11 +1190,11 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1289,11 +1233,7 @@
           <t>Paul M Power</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>$264,000.00</t>
@@ -1339,16 +1279,8 @@
           <t>$264,000.00</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -1376,11 +1308,11 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1419,11 +1351,7 @@
           <t>DAWN L MARTHINI</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>$396,000.00</t>
@@ -1465,16 +1393,8 @@
           <t>$396,000.00</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -1502,11 +1422,11 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1545,11 +1465,7 @@
           <t>LUCY AKPAN</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>$43,780.00</t>
@@ -1595,16 +1511,8 @@
           <t>$43,780.00</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -1632,11 +1540,11 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1671,11 +1579,7 @@
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>$516,000.00</t>
@@ -1721,16 +1625,8 @@
           <t>$516,000.00</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -1758,11 +1654,11 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect</t>
+          <t>ocr_fallback, owner_suspect, trustee_suspect</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -1801,11 +1697,7 @@
           <t>Agency, AZ</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>WHEREAS, the Deed of Trust was insured by the United States Secretary of</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>$318,773.40</t>
@@ -1851,11 +1743,7 @@
           <t>$318,773.40</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>WHEREAS, the Deed of Trust was insured by the United States Secretary of</t>
-        </is>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
@@ -1884,11 +1772,11 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -1927,11 +1815,7 @@
           <t>Beata L Knowles, A Widow</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>$340,500.00</t>
@@ -1977,16 +1861,8 @@
           <t>$340,500.00</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>(949) 427-2010</t>
-        </is>
-      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -2014,11 +1890,11 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2057,11 +1933,7 @@
           <t>Francisco Javier Guzman Orozco</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>PIONEER TITLE</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>$300,000.00</t>
@@ -2107,11 +1979,7 @@
           <t>$300,000.00</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>PIONEER TITLE</t>
-        </is>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
@@ -2140,11 +2008,11 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2183,11 +2051,7 @@
           <t>RYMAX DEVELOPMENT, L.L.C.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -2201,7 +2065,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>th Street Phoenix</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2233,16 +2097,8 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
@@ -2266,11 +2122,11 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, trustee_suspect, auction_date_missing</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2309,11 +2165,7 @@
           <t>RYMAX DEVELOPMENT, L.L.C.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -2327,7 +2179,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>th Street Phoenix</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2359,16 +2211,8 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
@@ -2392,11 +2236,11 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, trustee_suspect, auction_date_missing</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2435,11 +2279,7 @@
           <t>RYMAX DEVELOPMENT, L.L.C.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -2453,7 +2293,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>th Street Phoenix</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2481,16 +2321,8 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
@@ -2514,11 +2346,11 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2557,11 +2389,7 @@
           <t>RYMAX DEVELOPMENT, L.L.C.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -2575,7 +2403,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>th Street Phoenix</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2607,16 +2435,8 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
@@ -2640,11 +2460,11 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, trustee_suspect, auction_date_missing</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -2683,11 +2503,7 @@
           <t>RYMAX DEVELOPMENT, L.L.C.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -2701,7 +2517,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>th Street Phoenix</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2733,16 +2549,8 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2770,11 +2578,11 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -2813,11 +2621,7 @@
           <t>RYMAX DEVELOPMENT, L.L.C.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -2831,7 +2635,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>th Street Phoenix</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2863,16 +2667,8 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -2900,11 +2696,11 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -2943,11 +2739,7 @@
           <t>RYMAX DEVELOPMENT, L.L.C.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -2961,7 +2753,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>th Street Phoenix</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2993,16 +2785,8 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3030,11 +2814,11 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3073,11 +2857,7 @@
           <t>RYMAX DEVELOPMENT, L.L.C.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -3091,7 +2871,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>th Street Phoenix</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3119,16 +2899,8 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -3156,11 +2928,11 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3199,11 +2971,7 @@
           <t>Rymax Development, L.L.C.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>OR YOU MAY HAVE WAIVED ANY DEFENSES OR OBJECTIONS TO THE</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -3249,11 +3017,7 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>OR YOU MAY HAVE WAIVED ANY DEFENSES OR OBJECTIONS TO THE</t>
-        </is>
-      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
@@ -3282,11 +3046,11 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3325,11 +3089,7 @@
           <t>Rymax Development, L.L.C.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>OR YOU MAY HAVE WAIVED ANY DEFENSES OR OBJECTIONS TO THE</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -3375,11 +3135,7 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>OR YOU MAY HAVE WAIVED ANY DEFENSES OR OBJECTIONS TO THE</t>
-        </is>
-      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
@@ -3408,11 +3164,11 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -3451,11 +3207,7 @@
           <t>Rymax Development, L.L.C.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>OR YOU MAY HAVE WAIVED ANY DEFENSES OR OBJECTIONS TO THE</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -3501,11 +3253,7 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>OR YOU MAY HAVE WAIVED ANY DEFENSES OR OBJECTIONS TO THE</t>
-        </is>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
@@ -3534,11 +3282,11 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -3577,11 +3325,7 @@
           <t>Rymax Development, L.L.C.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>OR YOU MAY HAVE WAIVED ANY DEFENSES OR OBJECTIONS TO THE</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -3627,11 +3371,7 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>OR YOU MAY HAVE WAIVED ANY DEFENSES OR OBJECTIONS TO THE</t>
-        </is>
-      </c>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
@@ -3660,11 +3400,11 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -3703,11 +3443,7 @@
           <t>VICTOR M. CASILLAS</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>$146,610.00</t>
@@ -3737,16 +3473,8 @@
           <t>$146,610.00</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -3774,11 +3502,11 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -3817,11 +3545,7 @@
           <t>David Bitterman and Melissa Coles-Bitterman, 70 West Roadrunner Drive, Chandler, AZ</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY BEFORE THE</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>$389,695.44</t>
@@ -3867,11 +3591,7 @@
           <t>$389,695.44</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY BEFORE THE</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
@@ -3900,11 +3620,11 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -3943,11 +3663,7 @@
           <t>Aaron Anaya</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY BEFORE THE</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>$450,000.00</t>
@@ -3989,11 +3705,7 @@
           <t>$450,000.00</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY BEFORE THE</t>
-        </is>
-      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
@@ -4022,11 +3734,11 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4065,11 +3777,7 @@
           <t>CALVIN HUGGAR AND KARMA JOY HUGGAR</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>$517,997.00</t>
@@ -4115,11 +3823,7 @@
           <t>$517,997.00</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
@@ -4148,11 +3852,11 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -4191,11 +3895,7 @@
           <t>BOBBY DEAN SWIM AND TERRY ANN SWIM</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Planet Home Lending LLC</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>$364,000.00</t>
@@ -4241,11 +3941,7 @@
           <t>$364,000.00</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Planet Home Lending LLC</t>
-        </is>
-      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
@@ -4274,11 +3970,11 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -4317,11 +4013,7 @@
           <t>JESSE G SERNA AND VALERIE ANN LLANEZ</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>$289,656.00</t>
@@ -4367,16 +4059,8 @@
           <t>$289,656.00</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -4404,11 +4088,11 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5287,11 +4971,7 @@
           <t>DANAE LOREAN FLORES</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>America West Lender Services, LLC</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
@@ -5325,11 +5005,7 @@
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>America West Lender Services, LLC</t>
-        </is>
-      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
@@ -5358,11 +5034,11 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -5401,11 +5077,7 @@
           <t>ANA ESTRADA AND JOHN ESTRADA</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>$314,204.00</t>
@@ -5451,11 +5123,7 @@
           <t>$314,204.00</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
@@ -5484,11 +5152,11 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -5527,11 +5195,7 @@
           <t>MARIA G ESTRADA AND BRANDON AMAYA</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Nestor Solutions, LLC</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>$537,240.00</t>
@@ -5573,11 +5237,7 @@
           <t>$537,240.00</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Nestor Solutions, LLC</t>
-        </is>
-      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
@@ -5606,11 +5266,11 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -5649,11 +5309,7 @@
           <t>ERIC D FLORE</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>$166,920.00</t>
@@ -5699,11 +5355,7 @@
           <t>$166,920.00</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
@@ -5732,11 +5384,11 @@
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -5775,11 +5427,7 @@
           <t>Luis Ernesto Olmos Jr</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>$242,526.00</t>
@@ -5825,11 +5473,7 @@
           <t>$242,526.00</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
@@ -5858,11 +5502,11 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -5901,11 +5545,7 @@
           <t>Alberto Vasquez</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>$219,000.00</t>
@@ -5947,16 +5587,8 @@
           <t>$219,000.00</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
           <t>2026-07-21</t>
@@ -5980,11 +5612,11 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -6020,14 +5652,10 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Jorge Valles, Jr. and Melissa Vivar Y. Balderrama, AND not as tenants in common or as joint tenants</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+          <t>Jorge Valles, Jr. and Melissa Vivar Y. Balderrama, AND</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>$369,780.00</t>
@@ -6069,16 +5697,8 @@
           <t>$369,780.00</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -6102,11 +5722,11 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -6145,11 +5765,7 @@
           <t>JOSEPH WYLEZIK AND TAYLOR WYLEZIK</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>$531,226.00</t>
@@ -6195,16 +5811,8 @@
           <t>$531,226.00</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>2026-07-21</t>
@@ -6232,11 +5840,11 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -6275,11 +5883,7 @@
           <t>JESUS ZAMORA AND OLIVA ZAMORA</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>$461,295.00</t>
@@ -6325,16 +5929,8 @@
           <t>$461,295.00</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
           <t>2026-07-21</t>
@@ -6362,11 +5958,11 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -6405,11 +6001,7 @@
           <t>KENNY B SEAVER</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>$733,400.00</t>
@@ -6455,16 +6047,8 @@
           <t>$733,400.00</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -6492,11 +6076,11 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -6535,11 +6119,7 @@
           <t>Roy C.Burnett and Marie O. Burnett, as joint tenants</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>$319,500.00</t>
@@ -6581,16 +6161,8 @@
           <t>$319,500.00</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -6614,11 +6186,11 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -6732,7 +6304,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG55" t="n">
@@ -6775,11 +6347,7 @@
           <t>Donna Mae Wilcox</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>$164,000.00</t>
@@ -6821,16 +6389,8 @@
           <t>$164,000.00</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -6854,11 +6414,11 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -6897,11 +6457,7 @@
           <t>Gregory L Ehmann</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>$190,328.00</t>
@@ -6943,16 +6499,8 @@
           <t>$190,328.00</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -6976,11 +6524,11 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -7016,14 +6564,10 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GEORGE T. NORTON JR. AND NANCY NORTON, NOT AS TENANTS IN COMMON, NOT ESTATE, BUT</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+          <t>GEORGE T. NORTON JR. AND NANCY NORTON</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>$141,004.00</t>
@@ -7069,11 +6613,7 @@
           <t>$141,004.00</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr">
         <is>
@@ -7102,11 +6642,11 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -7142,14 +6682,10 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>’s Name and Address: Seth Dixon Jessica Dixon</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>warranty, express or implied, regarding title, condition, possession or encumbrances, to pay the</t>
-        </is>
-      </c>
+          <t>Seth Dixon Jessica Dixon</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>$972,000.00</t>
@@ -7191,11 +6727,7 @@
           <t>$972,000.00</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>warranty, express or implied, regarding title, condition, possession or encumbrances, to pay the</t>
-        </is>
-      </c>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr">
         <is>
@@ -7224,11 +6756,11 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -7267,11 +6799,7 @@
           <t>DOKUZ, LLC</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>$420,750.00</t>
@@ -7313,16 +6841,8 @@
           <t>$420,750.00</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>2026-08-18</t>
@@ -7350,11 +6870,11 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -7393,11 +6913,7 @@
           <t>LORI YATES</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>$398,860.00</t>
@@ -7443,11 +6959,7 @@
           <t>$398,860.00</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="inlineStr"/>
       <c r="W61" t="inlineStr">
         <is>
@@ -7476,11 +6988,11 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -7519,11 +7031,7 @@
           <t>RAUL BERMUDEZ</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>$220,924.00</t>
@@ -7569,11 +7077,7 @@
           <t>$220,924.00</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr">
         <is>
@@ -7602,11 +7106,11 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -7645,11 +7149,7 @@
           <t>JEREMY JAMES MOLLENHAUER</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>$601,663.00</t>
@@ -7695,11 +7195,7 @@
           <t>$601,663.00</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr">
         <is>
@@ -7728,11 +7224,11 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -7771,11 +7267,7 @@
           <t>JNRL Enterprises, LLC</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Janel M. Glynn, Esq.</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>$1,932,500.00</t>
@@ -7821,11 +7313,7 @@
           <t>$1,932,500.00</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>Janel M. Glynn, Esq.</t>
-        </is>
-      </c>
+      <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr">
         <is>
@@ -7854,11 +7342,11 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -7897,11 +7385,7 @@
           <t>SPS PLATINUM PROPERTIES, LLC</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>$250,000.00</t>
@@ -7947,16 +7431,8 @@
           <t>$250,000.00</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
       <c r="W65" t="inlineStr">
         <is>
           <t>2026-07-21</t>
@@ -7984,11 +7460,11 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -8027,11 +7503,7 @@
           <t>PEGGY LEE KNIGHT</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>WESTERN PROGRESSIVE</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>$ 630,000.00</t>
@@ -8077,11 +7549,7 @@
           <t>$ 630,000.00</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>WESTERN PROGRESSIVE</t>
-        </is>
-      </c>
+      <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr">
         <is>
@@ -8110,11 +7578,11 @@
       </c>
       <c r="AF66" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -8153,11 +7621,7 @@
           <t>DONALD J. ECHOLS AND COLLEEN A. ECHOLS</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>$285,000.00</t>
@@ -8203,16 +7667,8 @@
           <t>$285,000.00</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr">
         <is>
           <t>2026-07-22</t>
@@ -8240,11 +7696,11 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG67" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -8283,11 +7739,7 @@
           <t>MASON BODROG</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>$444,795.00</t>
@@ -8333,16 +7785,8 @@
           <t>$444,795.00</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -8370,11 +7814,11 @@
       </c>
       <c r="AF68" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -8410,14 +7854,10 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>’s Stated Name and Address: Salt River Point TT, LLC</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>(MESA REPOSITION PARTNERS, LLC/SALT RIVER POINT TT, LLC)</t>
-        </is>
-      </c>
+          <t>Salt River Point TT, LLC</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>$55,250,000</t>
@@ -8451,11 +7891,7 @@
           <t>$55,250,000</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>(MESA REPOSITION PARTNERS, LLC/SALT RIVER POINT TT, LLC)</t>
-        </is>
-      </c>
+      <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr">
         <is>
@@ -8484,11 +7920,11 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -8527,11 +7963,7 @@
           <t>Rommel Eugenio Cordova</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>$304,385</t>
@@ -8561,16 +7993,8 @@
           <t>$304,385</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
           <t>2026-07-15</t>
@@ -8594,11 +8018,11 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -8637,11 +8061,7 @@
           <t>ALEXIS M JAUREGU! RODRIGUEZ AND IYOANA G CHAVEZ</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>$294,566.00</t>
@@ -8687,16 +8107,8 @@
           <t>$294,566.00</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr">
         <is>
           <t>2026-07-21</t>
@@ -8724,11 +8136,11 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -8767,11 +8179,7 @@
           <t>Margie C. Yates</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>My commission expires</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>$100,000.00</t>
@@ -8817,11 +8225,7 @@
           <t>$100,000.00</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>My commission expires</t>
-        </is>
-      </c>
+      <c r="U72" t="inlineStr"/>
       <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr">
         <is>
@@ -8850,11 +8254,11 @@
       </c>
       <c r="AF72" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -8893,11 +8297,7 @@
           <t>LOGAN HAINLEN AND APRILYN STREETY</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>$322,200.00</t>
@@ -8943,16 +8343,8 @@
           <t>$322,200.00</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -8980,11 +8372,11 @@
       </c>
       <c r="AF73" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -9023,11 +8415,7 @@
           <t>JOSEPH PARKINSON AND ALEXIS PARKINSON</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>$766,550.00</t>
@@ -9073,16 +8461,8 @@
           <t>$766,550.00</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -9110,11 +8490,11 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -9153,11 +8533,7 @@
           <t>ROBERTO GAMINO</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>$82,500.00</t>
@@ -9203,16 +8579,8 @@
           <t>$82,500.00</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -9240,11 +8608,11 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -9283,11 +8651,7 @@
           <t>Mary Watola</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>$250,000.00</t>
@@ -9329,16 +8693,8 @@
           <t>$250,000.00</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr">
         <is>
           <t>2026-07-15</t>
@@ -9362,11 +8718,11 @@
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -9405,11 +8761,7 @@
           <t>MICHELLE INEZ MIRABELLA AND CRAIG STEVEN NETH</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Carrington Mortgage Services, LLC</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>$381,954.00</t>
@@ -9455,11 +8807,7 @@
           <t>$381,954.00</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Carrington Mortgage Services, LLC</t>
-        </is>
-      </c>
+      <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
@@ -9488,11 +8836,11 @@
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -9531,11 +8879,7 @@
           <t>Jerry Beck</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>$302,421.00</t>
@@ -9577,16 +8921,8 @@
           <t>$302,421.00</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -9610,11 +8946,11 @@
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -9653,11 +8989,7 @@
           <t>Cynthia L Walsh</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>$104,000.00</t>
@@ -9699,16 +9031,8 @@
           <t>$104,000.00</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
       <c r="W79" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -9732,11 +9056,11 @@
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG79" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -9775,11 +9099,7 @@
           <t>Jorge Guzman</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY BEFORE THE</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>$465,000.00</t>
@@ -9825,11 +9145,7 @@
           <t>$465,000.00</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>P.M. MOUNTAIN STANDARD TIME ON THE LAST BUSINESS DAY BEFORE THE</t>
-        </is>
-      </c>
+      <c r="U80" t="inlineStr"/>
       <c r="V80" t="inlineStr"/>
       <c r="W80" t="inlineStr">
         <is>
@@ -9858,11 +9174,11 @@
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG80" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -9901,11 +9217,7 @@
           <t>Thomas A. Dehne, single</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>$1,295,280.00</t>
@@ -9947,16 +9259,8 @@
           <t>$1,295,280.00</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
       <c r="W81" t="inlineStr">
         <is>
           <t>2026-07-15</t>
@@ -9980,11 +9284,11 @@
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -10023,11 +9327,7 @@
           <t>Travis Partridge</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>$117,930.00</t>
@@ -10069,16 +9369,8 @@
           <t>$117,930.00</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
       <c r="W82" t="inlineStr">
         <is>
           <t>2026-07-15</t>
@@ -10102,11 +9394,11 @@
       </c>
       <c r="AF82" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -10145,11 +9437,7 @@
           <t>Antonio A. Rodriguez, Jr.</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
           <t>$167,200.00</t>
@@ -10191,16 +9479,8 @@
           <t>$167,200.00</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
       <c r="W83" t="inlineStr">
         <is>
           <t>2026-07-22</t>
@@ -10224,11 +9504,11 @@
       </c>
       <c r="AF83" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG83" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -10267,11 +9547,7 @@
           <t>Jaime G Lopez</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
           <t>$285,000.00</t>
@@ -10313,16 +9589,8 @@
           <t>$285,000.00</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
       <c r="W84" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -10346,11 +9614,11 @@
       </c>
       <c r="AF84" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG84" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -10389,11 +9657,7 @@
           <t>Domanick O Lucious</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
           <t>$262,350.00</t>
@@ -10435,16 +9699,8 @@
           <t>$262,350.00</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
       <c r="W85" t="inlineStr">
         <is>
           <t>2026-07-22</t>
@@ -10468,11 +9724,11 @@
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG85" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -10511,11 +9767,7 @@
           <t>Jorge A Cornejo</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>$206,196.00</t>
@@ -10545,16 +9797,8 @@
           <t>$206,196.00</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr">
         <is>
           <t>2026-08-06</t>
@@ -10578,11 +9822,11 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -10621,11 +9865,7 @@
           <t>CLAYTON M. WOODRUFF AND DOROTHY J. WOODRUFF</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
           <t>$147,000.00</t>
@@ -10671,16 +9911,8 @@
           <t>$147,000.00</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>(949) 427-2010</t>
-        </is>
-      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
       <c r="W87" t="inlineStr">
         <is>
           <t>2026-08-04</t>
@@ -10708,11 +9940,11 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG87" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -10751,11 +9983,7 @@
           <t>TYRONE DANIEL WEST II AND ANDRIA ELANIA WEST, AS 20260225192 COMMUNITY PROPERTY</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>$353,100.00</t>
@@ -10801,16 +10029,8 @@
           <t>$353,100.00</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">
         <is>
           <t>2026-07-22</t>
@@ -10838,11 +10058,11 @@
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG88" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -10881,11 +10101,7 @@
           <t>Ariel Carlos, 20260225194</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
           <t>$455,000.00</t>
@@ -10931,16 +10147,8 @@
           <t>$455,000.00</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
       <c r="W89" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -10968,11 +10176,11 @@
       </c>
       <c r="AF89" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG89" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -11011,11 +10219,7 @@
           <t>Paul A. Brent and Teresa D. Hernandez-Brent</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
           <t>$185,739.00</t>
@@ -11061,16 +10265,8 @@
           <t>$185,739.00</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
       <c r="W90" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -11098,11 +10294,11 @@
       </c>
       <c r="AF90" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG90" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -11141,11 +10337,7 @@
           <t>SERGIO VILLAGOMEZ PADILLA AND MARIA VILLAGOMEZ</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
           <t>$373,117.00</t>
@@ -11191,16 +10383,8 @@
           <t>$373,117.00</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>(949) 427-2010</t>
-        </is>
-      </c>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
       <c r="W91" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -11228,11 +10412,11 @@
       </c>
       <c r="AF91" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -11271,11 +10455,7 @@
           <t>SERENA SHAO AND SAMUEL TANG</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>$596,000.00</t>
@@ -11321,16 +10501,8 @@
           <t>$596,000.00</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr">
         <is>
           <t>2026-01-14</t>
@@ -11358,11 +10530,11 @@
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -11401,11 +10573,7 @@
           <t>CORNELIUS E TANY! AND COLETTE T EBAIL, in the office of the County 20260225528 7110S CHAMPAGNE WAY, xxx, GILBERT, AZ</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>$550,800.00</t>
@@ -11439,16 +10607,8 @@
           <t>$550,800.00</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr">
         <is>
           <t>2026-07-22</t>
@@ -11476,11 +10636,11 @@
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -11519,11 +10679,7 @@
           <t>ROBERT L HENDERSON JR, SINGLE MAN</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>$392,950.00</t>
@@ -11557,16 +10713,8 @@
           <t>$392,950.00</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr">
         <is>
           <t>2026-08-06</t>
@@ -11594,11 +10742,11 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG94" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -11637,11 +10785,7 @@
           <t>STERLING M. GRANT</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>$236,880.00</t>
@@ -11687,16 +10831,8 @@
           <t>$236,880.00</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr">
         <is>
           <t>2026-04-13</t>
@@ -11724,11 +10860,11 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG95" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -11767,11 +10903,7 @@
           <t>RONALD HODNE AND LA TOYA GUEVARA</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>$690,900.00</t>
@@ -11817,16 +10949,8 @@
           <t>$690,900.00</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -11854,11 +10978,11 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -11897,11 +11021,7 @@
           <t>BRIAN JAMISON</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
           <t>$330,000.00</t>
@@ -11947,16 +11067,8 @@
           <t>$330,000.00</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
       <c r="W97" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -11984,11 +11096,11 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG97" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -12027,11 +11139,7 @@
           <t>CANDICE AUGE AND TODD AUGE</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
           <t>$285,000.00</t>
@@ -12077,16 +11185,8 @@
           <t>$285,000.00</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -12114,11 +11214,11 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG98" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -12157,11 +11257,7 @@
           <t>HELEN E CHARLES</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
           <t>$246,500.00</t>
@@ -12207,16 +11303,8 @@
           <t>$246,500.00</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
       <c r="W99" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -12244,11 +11332,11 @@
       </c>
       <c r="AF99" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG99" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -12287,11 +11375,7 @@
           <t>YOLANDA MCKIM AND BILLY MCKIM</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
           <t>$335,805.00</t>
@@ -12337,16 +11421,8 @@
           <t>$335,805.00</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
       <c r="W100" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -12374,11 +11450,11 @@
       </c>
       <c r="AF100" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG100" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -12417,11 +11493,7 @@
           <t>ROBERT FARMER</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
           <t>$205,128.00</t>
@@ -12467,16 +11539,8 @@
           <t>$205,128.00</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V101" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
       <c r="W101" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -12504,11 +11568,11 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG101" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -12547,11 +11611,7 @@
           <t>NIRA WANNARKA AND WILLIAM DIXON</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
           <t>$381,562.00</t>
@@ -12597,16 +11657,8 @@
           <t>$381,562.00</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V102" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
       <c r="W102" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -12634,11 +11686,11 @@
       </c>
       <c r="AF102" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG102" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -12677,11 +11729,7 @@
           <t>GOOD NEWS GROUP, LLC</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr">
         <is>
           <t>$374,000.00</t>
@@ -12715,16 +11763,8 @@
           <t>$374,000.00</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>PRESTIGE DEFAULT SERVICES, LLC</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>(949) 427-2010</t>
-        </is>
-      </c>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
       <c r="W103" t="inlineStr">
         <is>
           <t>2026-07-28</t>
@@ -12752,11 +11792,11 @@
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG103" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -12795,11 +11835,7 @@
           <t>CAROLINE ANN BRICKELL AND SEAN GENZMER</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>$252,340.00</t>
@@ -12845,16 +11881,8 @@
           <t>$252,340.00</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -12882,11 +11910,11 @@
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG104" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -12921,11 +11949,7 @@
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Unofficial Document</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
           <t>$238,500.00</t>
@@ -12967,11 +11991,7 @@
           <t>$238,500.00</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
-        <is>
-          <t>Unofficial Document</t>
-        </is>
-      </c>
+      <c r="U105" t="inlineStr"/>
       <c r="V105" t="inlineStr"/>
       <c r="W105" t="inlineStr">
         <is>
@@ -13000,11 +12020,11 @@
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, parcel_missing</t>
+          <t>ocr_fallback, owner_suspect, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG105" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -13043,11 +12063,7 @@
           <t>BOBBI SCHULTZ</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
           <t>$275,000.00</t>
@@ -13089,16 +12105,8 @@
           <t>$275,000.00</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
-      <c r="V106" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
       <c r="W106" t="inlineStr">
         <is>
           <t>2026-07-22</t>
@@ -13126,11 +12134,11 @@
       </c>
       <c r="AF106" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG106" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -13169,11 +12177,7 @@
           <t>LUIS ALONSO MIRANDA GOMEZ</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
           <t>$122,042.00</t>
@@ -13215,16 +12219,8 @@
           <t>$122,042.00</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
       <c r="W107" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -13252,11 +12248,11 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG107" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -13295,11 +12291,7 @@
           <t>YOLANDA S. DE LEON AND DOMINGO DE LEON AND ANTHONY DE LEON</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
           <t>$323,000.00</t>
@@ -13345,16 +12337,8 @@
           <t>$323,000.00</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
       <c r="W108" t="inlineStr">
         <is>
           <t>2026-07-21</t>
@@ -13382,11 +12366,11 @@
       </c>
       <c r="AF108" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG108" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -13425,11 +12409,7 @@
           <t>JASON DANIEL MURRAY AND AMBER MURRAY</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
           <t>$235,653.00</t>
@@ -13471,16 +12451,8 @@
           <t>$235,653.00</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
       <c r="W109" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -13508,11 +12480,11 @@
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG109" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -13551,11 +12523,7 @@
           <t>JORDAN OLIVA</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
           <t>$427,696.00</t>
@@ -13597,16 +12565,8 @@
           <t>$427,696.00</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
       <c r="W110" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -13634,11 +12594,11 @@
       </c>
       <c r="AF110" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG110" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -13677,11 +12637,7 @@
           <t>RUSTY ROBERTS AND NICHOLE ROBERTS</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
           <t>$1,138,564.00</t>
@@ -13723,16 +12679,8 @@
           <t>$1,138,564.00</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
-      <c r="V111" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
       <c r="W111" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -13760,11 +12708,11 @@
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG111" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -13803,11 +12751,7 @@
           <t>RYMAX DEVELOPMENT, L.L.C.</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
           <t>$480,000.00</t>
@@ -13821,7 +12765,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>th Street Phoenix</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -13853,16 +12797,8 @@
           <t>$480,000.00</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr">
         <is>
@@ -13886,11 +12822,11 @@
       </c>
       <c r="AF112" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing</t>
+          <t>ocr_fallback, trustee_suspect, auction_date_missing</t>
         </is>
       </c>
       <c r="AG112" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -13929,11 +12865,7 @@
           <t>TITAN FAMILY REALESTATE LLC</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
           <t>$110,000.00</t>
@@ -13967,16 +12899,8 @@
           <t>$110,000.00</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
       <c r="W113" t="inlineStr">
         <is>
           <t>2026-01-09</t>
@@ -14004,11 +12928,11 @@
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG113" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -14047,11 +12971,7 @@
           <t>Graciela Bucio Perez</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>$176,000.00</t>
@@ -14085,16 +13005,8 @@
           <t>$176,000.00</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
-        <is>
-          <t>RONALD B. HERB</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>(602) 488-1349</t>
-        </is>
-      </c>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
       <c r="W114" t="inlineStr">
         <is>
           <t>2026-07-20</t>
@@ -14122,11 +13034,11 @@
       </c>
       <c r="AF114" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG114" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -14165,11 +13077,7 @@
           <t>JOSEPH VERDUZCO</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
           <t>$294,405.00</t>
@@ -14215,16 +13123,8 @@
           <t>$294,405.00</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V115" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
       <c r="W115" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -14252,11 +13152,11 @@
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG115" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -14295,11 +13195,7 @@
           <t>Mani Hotels, LLC State Bank of Texas</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>MOUNTAIN STANDARD TIME OF THE LAST BUSINESS DAY BEFORE THE</t>
-        </is>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
           <t>$10,000,000.00</t>
@@ -14329,11 +13225,7 @@
           <t>$10,000,000.00</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
-        <is>
-          <t>MOUNTAIN STANDARD TIME OF THE LAST BUSINESS DAY BEFORE THE</t>
-        </is>
-      </c>
+      <c r="U116" t="inlineStr"/>
       <c r="V116" t="inlineStr"/>
       <c r="W116" t="inlineStr"/>
       <c r="X116" t="inlineStr">
@@ -14358,11 +13250,11 @@
       </c>
       <c r="AF116" t="inlineStr">
         <is>
-          <t>ocr_fallback, auction_date_missing, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, auction_date_missing, parcel_missing</t>
         </is>
       </c>
       <c r="AG116" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -14401,11 +13293,7 @@
           <t>BRENDA FAE HUBBARD</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
           <t>$192,449.00</t>
@@ -14451,16 +13339,8 @@
           <t>$192,449.00</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V117" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
       <c r="W117" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -14488,11 +13368,11 @@
       </c>
       <c r="AF117" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG117" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -14531,11 +13411,7 @@
           <t>ZHONG K WANG AND FRANCIS N PRICE AND FRANCIS PRICE</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
           <t>$200,000.00</t>
@@ -14581,16 +13457,8 @@
           <t>$200,000.00</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
       <c r="W118" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -14618,11 +13486,11 @@
       </c>
       <c r="AF118" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG118" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -14661,11 +13529,7 @@
           <t>Wayne Carpenter</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
           <t>$50,000.00</t>
@@ -14707,16 +13571,8 @@
           <t>$50,000.00</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
       <c r="W119" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -14740,11 +13596,11 @@
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG119" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH119" t="inlineStr">
         <is>
@@ -14783,11 +13639,7 @@
           <t>WHEREAS, the Deed of Trust was insured by the United States Secretary of Housing and Urban</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
           <t>$337,252.80</t>
@@ -14833,16 +13685,8 @@
           <t>$337,252.80</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>(949) 252-8300</t>
-        </is>
-      </c>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
       <c r="W120" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -14870,11 +13714,11 @@
       </c>
       <c r="AF120" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG120" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -14913,11 +13757,7 @@
           <t>Frances Garcia</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
           <t>$68,000.00</t>
@@ -14959,16 +13799,8 @@
           <t>$68,000.00</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
       <c r="W121" t="inlineStr">
         <is>
           <t>2026-08-06</t>
@@ -14992,11 +13824,11 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG121" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH121" t="inlineStr">
         <is>
@@ -15035,11 +13867,7 @@
           <t>Luis Vincente Gurrola Martinez</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
           <t>$233,100.00</t>
@@ -15081,16 +13909,8 @@
           <t>$233,100.00</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
       <c r="W122" t="inlineStr">
         <is>
           <t>2026-08-06</t>
@@ -15114,11 +13934,11 @@
       </c>
       <c r="AF122" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG122" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -15157,11 +13977,7 @@
           <t>Christine Lea Kurtz-Ford</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
           <t>$121,000.00</t>
@@ -15203,16 +14019,8 @@
           <t>$121,000.00</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
       <c r="W123" t="inlineStr">
         <is>
           <t>2026-08-06</t>
@@ -15236,11 +14044,11 @@
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG123" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH123" t="inlineStr">
         <is>
@@ -15279,11 +14087,7 @@
           <t>Martin V Valadez AND Velazquez David Valadez</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
           <t>$380,000.00</t>
@@ -15325,16 +14129,8 @@
           <t>$380,000.00</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V124" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
       <c r="W124" t="inlineStr">
         <is>
           <t>2026-08-06</t>
@@ -15358,11 +14154,11 @@
       </c>
       <c r="AF124" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG124" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH124" t="inlineStr">
         <is>
@@ -15401,11 +14197,7 @@
           <t>Richard L Bristol and Grace A Bristol</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
           <t>$149,055.00</t>
@@ -15447,16 +14239,8 @@
           <t>$149,055.00</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
       <c r="W125" t="inlineStr">
         <is>
           <t>2026-08-06</t>
@@ -15480,11 +14264,11 @@
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG125" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH125" t="inlineStr">
         <is>
@@ -15523,11 +14307,7 @@
           <t>Strong Base, LLC</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>on November 27, 2024, as instrument number 2024-0637955, executed by Strong Base, LLC</t>
-        </is>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
           <t>$725,000.00</t>
@@ -15557,16 +14337,8 @@
           <t>$725,000.00</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
-        <is>
-          <t>on November 27, 2024, as instrument number 2024-0637955, executed by Strong Base, LLC</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>024-0637955</t>
-        </is>
-      </c>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
       <c r="W126" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -15594,11 +14366,11 @@
       </c>
       <c r="AF126" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG126" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH126" t="inlineStr">
         <is>
@@ -15637,11 +14409,7 @@
           <t>Rene Campa AND Sebastian Campa</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>$368,207.00</t>
@@ -15683,16 +14451,8 @@
           <t>$368,207.00</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V127" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
       <c r="W127" t="inlineStr">
         <is>
           <t>2026-08-06</t>
@@ -15716,11 +14476,11 @@
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG127" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH127" t="inlineStr">
         <is>
@@ -15759,11 +14519,7 @@
           <t>Lynda Peretz</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
           <t>$187,000.00</t>
@@ -15805,16 +14561,8 @@
           <t>$187,000.00</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>LEONARD J. MCDONALD</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
       <c r="W128" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -15842,11 +14590,11 @@
       </c>
       <c r="AF128" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG128" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH128" t="inlineStr">
         <is>
@@ -15885,11 +14633,7 @@
           <t>RICHARDO MONTES IBARBOL AND ABAGAIL ALEXXIS MENDEZ AND MARIA THERESA IBARBOL CRUZ</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
           <t>$380,972.00</t>
@@ -15935,16 +14679,8 @@
           <t>$380,972.00</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
-        <is>
-          <t>CLEAR RECON CORP</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>(866) 931-0036</t>
-        </is>
-      </c>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
       <c r="W129" t="inlineStr">
         <is>
           <t>2026-04-14</t>
@@ -15972,11 +14708,11 @@
       </c>
       <c r="AF129" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG129" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH129" t="inlineStr">
         <is>
@@ -16015,11 +14751,7 @@
           <t>YAVIN JAY CRANSHAW</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
           <t>$363,298.00</t>
@@ -16061,16 +14793,8 @@
           <t>$363,298.00</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
-      <c r="V130" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
       <c r="W130" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -16098,11 +14822,11 @@
       </c>
       <c r="AF130" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG130" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH130" t="inlineStr">
         <is>
@@ -16141,11 +14865,7 @@
           <t>JUAN CARRANZA</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
           <t>$286,805.00</t>
@@ -16187,16 +14907,8 @@
           <t>$286,805.00</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>PRIME RECON LLC</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>(888) 725-4142</t>
-        </is>
-      </c>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
       <c r="W131" t="inlineStr">
         <is>
           <t>2026-07-30</t>
@@ -16224,11 +14936,11 @@
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, trustee_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG131" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH131" t="inlineStr">
         <is>
@@ -16267,11 +14979,7 @@
           <t>BLANCA M ARMENTA QUINONEZ AND MICHAEL G ARMENTA</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
           <t>$280,819.00</t>
@@ -16317,16 +15025,8 @@
           <t>$280,819.00</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V132" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
       <c r="W132" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -16354,11 +15054,11 @@
       </c>
       <c r="AF132" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG132" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH132" t="inlineStr">
         <is>
@@ -16397,11 +15097,7 @@
           <t>Andrew S Kulin and Kasie M Lambros</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
           <t>$372,000.00</t>
@@ -16447,16 +15143,8 @@
           <t>$372,000.00</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>QUALITY LOAN SERVICE CORPORATION</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr"/>
       <c r="W133" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -16484,11 +15172,11 @@
       </c>
       <c r="AF133" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG133" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AH133" t="inlineStr">
         <is>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH23"/>
+  <dimension ref="A1:AH106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -421,7 +421,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -436,7 +436,7 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="37" customWidth="1" min="21" max="21"/>
+    <col width="57" customWidth="1" min="21" max="21"/>
     <col width="15" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
@@ -627,7 +627,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260228838</t>
+          <t>20260189838</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -637,20 +637,24 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DANIEL MEADOR, AN UNMARRIED MAN</t>
+          <t>(as shown on the Deed of Trust)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>PEORIA, AZ 85345,</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -661,11 +665,15 @@
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -685,7 +693,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260229113</t>
+          <t>20260189851</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -695,20 +703,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MARYLIN IRISH, A SINGLE WOMAN</t>
+          <t>(as shown on the Deed of Trust)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PEORIA, AZ 85345,</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -719,11 +731,15 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -743,7 +759,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260229590</t>
+          <t>20260190248</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -753,16 +769,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>PHOENIX, AZ 85044,</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -773,11 +797,15 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2027-04-25</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -797,7 +825,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260229593</t>
+          <t>20260190396</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -807,20 +835,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1017 W. Myrtle Ave.</t>
+          <t>(as shown on the Deed of Trust)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>SURPRISE, AZ 85387,</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -831,9 +863,17 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
@@ -851,7 +891,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260229598</t>
+          <t>20260190991</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -861,18 +901,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>MESA, AZ 85215,</t>
+          <t>QUEEN CREEK, AZ 85142,</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -885,11 +929,15 @@
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale) Unofficial Document</t>
+        </is>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -909,7 +957,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260230052</t>
+          <t>20260191611</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -919,16 +967,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>PHOENIX, AZ 85023,</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -939,9 +995,17 @@
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
@@ -959,7 +1023,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260230053</t>
+          <t>20260191625</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -969,16 +1033,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>A.P.N.: 175-11-160, Original Principal Balance: $1,500,000.00</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -989,9 +1061,17 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
@@ -1009,7 +1089,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260230054</t>
+          <t>20260191626</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1019,16 +1099,24 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>A.P.N.: 173-59-126, Original Principal Balance: $1,724,250.00</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -1039,9 +1127,17 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
@@ -1059,7 +1155,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260230133</t>
+          <t>20260191627</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1069,7 +1165,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1078,7 +1174,11 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>A.P.N.: 301-02-415, Original Principal Balance: $1,724,250.00</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1089,11 +1189,15 @@
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
@@ -1113,7 +1217,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260230140</t>
+          <t>20260191631</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1123,16 +1227,24 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>A.P.N.: 131-43-007, Original Principal Balance: $1,724,250.00</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1143,9 +1255,17 @@
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
@@ -1163,7 +1283,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260230151</t>
+          <t>20260191651</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1173,16 +1293,24 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>{as shown on the Deed of Trust)</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>A.P.N.: 131-52-039,</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1193,11 +1321,15 @@
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1217,7 +1349,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260230571</t>
+          <t>20260191655</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1227,16 +1359,24 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>A.P.N.: 131-28-208, Original Principal Balance: $1,724,250.00</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1247,11 +1387,15 @@
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1271,7 +1415,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260230587</t>
+          <t>20260191662</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,7 +1425,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1290,7 +1434,11 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>PEORIA, AZ 85383-1442,</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -1305,7 +1453,7 @@
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1325,7 +1473,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260230626</t>
+          <t>20260191740</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1335,7 +1483,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1344,7 +1492,11 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST. AZ 85375,</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -1355,11 +1507,15 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1379,7 +1535,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260230632</t>
+          <t>20260191897</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1389,7 +1545,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1398,11 +1554,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>SCOTTSDALE, AZ 85260,</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -1417,7 +1569,7 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1437,7 +1589,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260230955</t>
+          <t>20260192403</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1447,16 +1599,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>PHOENIX, Arizona 85086,</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -1467,11 +1627,15 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1491,7 +1655,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260230972</t>
+          <t>20260192558</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1501,7 +1665,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1523,7 +1687,11 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
@@ -1541,7 +1709,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260231008</t>
+          <t>20260192629</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1551,24 +1719,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>(as shown on the Deed of Trust)</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>A.P.N.: 214-32-038, Original Principal Balance: $55,000.00</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -1579,15 +1739,11 @@
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>(as of recording of Notice of Sale)</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -1607,7 +1763,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260231075</t>
+          <t>20260192666</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1617,7 +1773,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1639,11 +1795,7 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>2026-11-03</t>
-        </is>
-      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
@@ -1661,7 +1813,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260231092</t>
+          <t>20260192668</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1671,7 +1823,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1680,7 +1832,11 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>PHOENIX, AZ 85042-7851,</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -1691,11 +1847,15 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -1715,7 +1875,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260231096</t>
+          <t>20260192700</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1725,12 +1885,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>JESUS REYES, AN UNMARRIED MAN,</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1749,7 +1913,7 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -1769,7 +1933,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260231127</t>
+          <t>20260192707</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1779,7 +1943,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1788,7 +1952,11 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PHOENIX AZ 85009,</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -1799,11 +1967,15 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -1820,6 +1992,4580 @@
       </c>
       <c r="AH23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260192766</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>JUAN MANUEL MIRELES JR AND SANDRA MIRELES HUSBAND AND WIFE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260192883</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>MESA, AZ 85208,</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260192896</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260192940</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260192943</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>GOODYEAR, AZ 85395,</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260192978</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ 85257, A.P.N.: 129-22-080</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260192984</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260192994</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ 85257, A.P.N.: 129-07-039</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260193030</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260193112</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20260193202</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20260193241</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>MESA AZ 85213,</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20260193873</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20260194588</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20260194891</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20260195052</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>GILBERT, AZ 85234,</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20260195145</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260195158</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260195172</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260195201</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260195224</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260195896</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260195937</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260195960</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260196009</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260196023</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260196029</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260196134</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260196140</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260196332</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>A.P.N.: 219-25-300, Original Principal Balance: $969,000.00</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260196404</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260196494</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260196990</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260196995</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260198192</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ROCHELLE JOHNS, A SINGLE WOMAN, AND REGINALD HOLDEN, A SINGLE MAN, AS</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260198434</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>SUN CITY WEST, AZ 85375,</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260198528</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260198560</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>GLENDALE, AZ 85301,</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260198786</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260198797</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr"/>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260198817</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr"/>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260198819</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="inlineStr"/>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260198938</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>TIMOTHY NEPPER, AN UNMARRIED MAN</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260198994</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="inlineStr"/>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260199010</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="inlineStr"/>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260199011</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="inlineStr"/>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260199025</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="inlineStr"/>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260200681</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>SURPRISE AZ 85379,</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="inlineStr"/>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260200826</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>10621 N. 43'¢ Avenue</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="inlineStr"/>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260200835</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260201371</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260201418</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>MESA, AZ 85205-7355,</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260201442</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>SURPRISE, AZ 85379,</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>20260201682</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>17441 W FAIR OAKS, LLC, a Wyoming limited liability company, Steeve Raymond</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>20260201709</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Liability; Company, 3340 W. Southern Ave., Phoenix, AZ 85041</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>20260201730</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>SCOTTSDALE AZ 85257,</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>20260201897</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>20260201906</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>20260201933</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>20260201940</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>2026-11-09</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
+      <c r="AC83" t="inlineStr"/>
+      <c r="AD83" t="inlineStr"/>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>20260202046</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="inlineStr"/>
+      <c r="AD84" t="inlineStr"/>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>20260202182</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>FLORINE Z JONES, A SINGLE WOMAN</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
+      <c r="AC85" t="inlineStr"/>
+      <c r="AD85" t="inlineStr"/>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>20260202185</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
+      <c r="AC86" t="inlineStr"/>
+      <c r="AD86" t="inlineStr"/>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>20260202502</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
+      <c r="AC87" t="inlineStr"/>
+      <c r="AD87" t="inlineStr"/>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>20260203024</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>(as shown on the Deed of Trust)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>(as of recording of Notice of Sale)</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
+      <c r="AC88" t="inlineStr"/>
+      <c r="AD88" t="inlineStr"/>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20260203655</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>261 S. Chippewa PI., Chandler, AZ 85224</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
+      <c r="AC89" t="inlineStr"/>
+      <c r="AD89" t="inlineStr"/>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>20260203683</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Glendale, AZ 85301</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="inlineStr"/>
+      <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>20260203883</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ROBYN A ARTHUR, AN UNMARRIED WOMAN</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
+      <c r="AC91" t="inlineStr"/>
+      <c r="AD91" t="inlineStr"/>
+      <c r="AE91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>20260203946</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
+      <c r="AC92" t="inlineStr"/>
+      <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20260203989</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
+      <c r="AC93" t="inlineStr"/>
+      <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>20260204001</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
+      <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="inlineStr"/>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>20260204029</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
+      <c r="AB95" t="inlineStr"/>
+      <c r="AC95" t="inlineStr"/>
+      <c r="AD95" t="inlineStr"/>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>20260204357</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr"/>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
+      <c r="AC96" t="inlineStr"/>
+      <c r="AD96" t="inlineStr"/>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>20260204443</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
+      <c r="AC97" t="inlineStr"/>
+      <c r="AD97" t="inlineStr"/>
+      <c r="AE97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>20260204779</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Jean F, Diop</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
+      <c r="AC98" t="inlineStr"/>
+      <c r="AD98" t="inlineStr"/>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>20260204838</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr"/>
+      <c r="AC99" t="inlineStr"/>
+      <c r="AD99" t="inlineStr"/>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>20260204845</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
+      <c r="AC100" t="inlineStr"/>
+      <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>20260204967</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
+      <c r="AC101" t="inlineStr"/>
+      <c r="AD101" t="inlineStr"/>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>20260205429</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr"/>
+      <c r="AC102" t="inlineStr"/>
+      <c r="AD102" t="inlineStr"/>
+      <c r="AE102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>20260205432</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>CARL ANTHONY DANCKAERT, HUSBAND AND SARA MARIE DANCKAERT, WIFE</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr"/>
+      <c r="AC103" t="inlineStr"/>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>20260205473</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr"/>
+      <c r="AC104" t="inlineStr"/>
+      <c r="AD104" t="inlineStr"/>
+      <c r="AE104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>20260205520</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>PHOENIX, AZ 85041,</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr"/>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr"/>
+      <c r="AC105" t="inlineStr"/>
+      <c r="AD105" t="inlineStr"/>
+      <c r="AE105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr"/>
+      <c r="AG105" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>20260205551</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr"/>
+      <c r="AC106" t="inlineStr"/>
+      <c r="AD106" t="inlineStr"/>
+      <c r="AE106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="n">
+        <v>90</v>
+      </c>
+      <c r="AH106" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -437,7 +437,7 @@
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
     <col width="60" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
@@ -652,7 +652,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HIRAM OSVALDO RAMIREZ AND</t>
+          <t>HIRAM OSVALDO RAMIREZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -666,26 +666,10 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -734,11 +718,11 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -774,7 +758,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BRANDON S. MAXWELL AND CANDACE C. MAXWELL, COMMUNITY</t>
+          <t>BRANDON S. MAXWELL AND CANDACE C. MAXWELL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -788,26 +772,10 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -856,11 +824,11 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -910,26 +878,10 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -978,11 +930,11 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1018,7 +970,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SHANE DOUGLAS TREMBLY, MAN</t>
+          <t>SHANE DOUGLAS TREMBLY</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1032,26 +984,10 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -1100,11 +1036,11 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1140,7 +1076,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CHRISTOPHER NGUYEN-VU LE AND ROSIE HONG MANIVONG LE, NOT</t>
+          <t>CHRISTOPHER NGUYEN-VU LE AND ROSIE HONG MANIVONG LE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1154,26 +1090,10 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -1222,11 +1142,11 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1276,26 +1196,10 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -1326,11 +1230,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
@@ -1348,11 +1248,11 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1452,11 +1352,7 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
@@ -1578,11 +1474,7 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
@@ -1704,11 +1596,7 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
@@ -1830,11 +1718,7 @@
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
@@ -1956,11 +1840,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
@@ -2082,11 +1962,7 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
@@ -2158,26 +2034,10 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>201 W. JEFFERSON STREET</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -2230,11 +2090,11 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2270,7 +2130,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WILLIAM SETTEN, AN PERSON</t>
+          <t>WILLIAM SETTEN, AN INDIVIDUAL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -2310,11 +2170,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
@@ -2372,7 +2228,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>JASON NUTT AND KRISTA NUTT, MARRIED, NOT AS TENANTS IN COMMON AND NOT</t>
+          <t>JASON NUTT AND KRISTA NUTT, MARRIED</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2386,26 +2242,10 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -2428,7 +2268,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1 2026019189</t>
+          <t>(202) 601-9189</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2454,11 +2294,11 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>address_missing, ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2508,26 +2348,10 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -2562,11 +2386,7 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
@@ -2584,11 +2404,11 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -2802,7 +2622,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1 (602) 255-6035</t>
+          <t>(602) 255-6035</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3000,26 +2820,10 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -3046,11 +2850,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
@@ -3068,11 +2868,11 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>ocr_fallback, trustee_suspect</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3122,26 +2922,10 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
@@ -3164,7 +2948,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1 2026019270</t>
+          <t>(202) 601-9270</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3190,11 +2974,11 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>address_missing, ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3240,26 +3024,10 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
@@ -3286,11 +3054,7 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
@@ -3308,11 +3072,11 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>ocr_fallback, trustee_suspect</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -3396,7 +3160,7 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -3404,11 +3168,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
@@ -3469,37 +3229,17 @@
           <t>LUISE A. LUCAS</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Please be advised that the highest bidder (“purchaser”) at this trustee’s sale may be required</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>$129,609.00</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
@@ -3519,11 +3259,7 @@
           <t>$129,609.00</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Please be advised that the highest bidder (“purchaser”) at this trustee’s sale may be required</t>
-        </is>
-      </c>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
@@ -3548,11 +3284,11 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -3602,26 +3338,10 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>201 WEST JEFFERSON</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>PHOENIX.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
@@ -3656,11 +3376,7 @@
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
@@ -3678,11 +3394,11 @@
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -3721,11 +3437,7 @@
           <t>Kevin M Kurtz</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>$89,841.00</t>
@@ -3767,16 +3479,8 @@
           <t>$89,841.00</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -3800,11 +3504,11 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -3854,26 +3558,10 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
@@ -3922,11 +3610,11 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -3972,26 +3660,10 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
@@ -4018,7 +3690,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1 215-855-9521</t>
+          <t>(215) 855-9521</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4044,11 +3716,11 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect</t>
+          <t>address_missing, ocr_fallback, owner_suspect</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -4084,40 +3756,20 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
+          <t>Sales Line: 800-280-2832</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>$598,000.00</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
@@ -4133,16 +3785,8 @@
           <t>$598,000.00</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>108 2026019</t>
-        </is>
-      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
           <t>2026-07-09</t>
@@ -4166,11 +3810,11 @@
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>address_missing, ocr_fallback, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -4216,26 +3860,10 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
@@ -4262,7 +3890,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1 215-855-9521</t>
+          <t>(215) 855-9521</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4288,11 +3916,11 @@
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect</t>
+          <t>address_missing, ocr_fallback, owner_suspect</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -4571,37 +4199,17 @@
           <t>ELIZABETH GALVEZ GARCIA, AS HIS SOLE</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>$161,400.00</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
@@ -4621,16 +4229,8 @@
           <t>$161,400.00</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
           <t>2026-07-08</t>
@@ -4654,11 +4254,11 @@
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -4708,26 +4308,10 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
@@ -4758,11 +4342,7 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
@@ -4780,11 +4360,11 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -4864,7 +4444,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -4872,11 +4452,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
@@ -4937,11 +4513,7 @@
           <t>Cynthia Kokesh</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Attorney at Law, Trustee, is regulated by, and qualified under</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>$6,000.00</t>
@@ -4983,16 +4555,8 @@
           <t>$6,000.00</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Attorney at Law, Trustee, is regulated by, and qualified under</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>480-660-6250</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
           <t>2026-07-10</t>
@@ -5020,11 +4584,11 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -5116,7 +4680,7 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>1 (602) 255-6035</t>
+          <t>(602) 255-6035</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
@@ -5182,7 +4746,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>RUSSELL WADE WATSON AKA RUSSELL WATSON, AS HIS SOLE AND</t>
+          <t>RUSSELL WADE WATSON AKA RUSSELL WATSON, AS HIS SOLE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -5192,26 +4756,10 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
@@ -5238,11 +4786,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
@@ -5260,11 +4804,11 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>ocr_fallback, trustee_suspect</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -5356,7 +4900,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>1 (602) 255-6035</t>
+          <t>(602) 255-6035</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
@@ -5425,11 +4969,7 @@
           <t>Kristen Ana De Sousa</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>$196,278.00</t>
@@ -5471,16 +5011,8 @@
           <t>$196,278.00</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>1 (602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -5504,11 +5036,11 @@
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -5547,11 +5079,7 @@
           <t>Jonathan Ortiz and Veronica Ortiz</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>$561,494.00</t>
@@ -5593,16 +5121,8 @@
           <t>$561,494.00</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>1 (602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -5626,11 +5146,11 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -5669,11 +5189,7 @@
           <t>Alexia Valenzuela</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>$235,653.00</t>
@@ -5715,16 +5231,8 @@
           <t>$235,653.00</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>1 (602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -5748,11 +5256,11 @@
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -5791,11 +5299,7 @@
           <t>Emilio M Murillo, an person</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Indenture Trustee Twenty Fourth Floor</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>$50,000.00</t>
@@ -5837,16 +5341,8 @@
           <t>$50,000.00</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Indenture Trustee Twenty Fourth Floor</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -5870,11 +5366,11 @@
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -5908,11 +5404,7 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>trust created by said Deed of Trust.</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>Sheri L. Morris, Trustee Sale Officer</t>
@@ -5988,11 +5480,11 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, owner_suspect</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -6027,11 +5519,7 @@
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>$800,000.00</t>
@@ -6073,16 +5561,8 @@
           <t>$800,000.00</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>(602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -6106,11 +5586,11 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect, parcel_missing</t>
+          <t>ocr_fallback, owner_suspect, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -6202,7 +5682,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>1 (602) 255-6035</t>
+          <t>(602) 255-6035</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6393,11 +5873,7 @@
           <t>Deanna Nord and Donald Nord</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>On this “tL day of April, 2026 before me, Stephen Daniel Clem, a Notary Public for said State, personally</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>$274,329.00</t>
@@ -6439,11 +5915,7 @@
           <t>$274,329.00</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>On this “tL day of April, 2026 before me, Stephen Daniel Clem, a Notary Public for said State, personally</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
@@ -6468,11 +5940,11 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -6522,26 +5994,10 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
@@ -6590,11 +6046,11 @@
       </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>address_missing, ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -6630,40 +6086,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
+          <t>Sales Line: 800-280-2832</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>$205,600.00</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
@@ -6683,16 +6119,8 @@
           <t>$205,600.00</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>2026019613</t>
-        </is>
-      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
           <t>2026-07-09</t>
@@ -6716,11 +6144,11 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -6756,14 +6184,10 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
+          <t>Sales Line: 800-280-2832</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>$51,403.00</t>
@@ -6797,16 +6221,8 @@
           <t>$51,403.00</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -6826,11 +6242,11 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>auction_date_missing, ocr_fallback</t>
+          <t>auction_date_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -6930,11 +6346,7 @@
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
@@ -6992,40 +6404,20 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
+          <t>Sales Line: 800-280-2832</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>$363,298.00</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
@@ -7045,16 +6437,8 @@
           <t>$363,298.00</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
           <t>2026-07-09</t>
@@ -7078,11 +6462,11 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -7121,11 +6505,7 @@
           <t>Micole Denae Neely</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>to the Deed of Trust. The Trustee shall not express an opinion as to the condition of title.</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>$305,000.00</t>
@@ -7155,22 +6535,14 @@
           <t>$305,000.00</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>to the Deed of Trust. The Trustee shall not express an opinion as to the condition of title.</t>
-        </is>
-      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr"/>
@@ -7188,11 +6560,11 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>address_missing, ocr_fallback</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -7242,26 +6614,10 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>201 WEST JEFFERSON</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
@@ -7314,11 +6670,11 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -7354,7 +6710,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ANTONIO P. RODRIGUEZ AND EUSEVIA RODRIGUEZ, AS JOINT</t>
+          <t>ANTONIO P. RODRIGUEZ AND EUSEVIA RODRIGUEZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -7700,14 +7056,10 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dana A Carbaja! Quintana</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
+          <t>Dana A Carbajal Quintana</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>$365,585.00</t>
@@ -7749,16 +7101,8 @@
           <t>$365,585.00</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>Care of/Servicer Twenty Fourth Floor</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>1 (602) 255-6035</t>
-        </is>
-      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr">
         <is>
           <t>2026-07-23</t>
@@ -7782,11 +7126,11 @@
       </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG60" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -7836,26 +7180,10 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>201 W. JEFFERSON STREET</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
@@ -7908,11 +7236,11 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG61" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -7946,11 +7274,7 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>“Notice to Potential bidders: If you are the successful bidder on the subject property, you may be subject to filing</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>Sheri L. Morris, Trustee Sale Officer</t>
@@ -8022,11 +7346,11 @@
       </c>
       <c r="AF62" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, owner_suspect</t>
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -8060,11 +7384,7 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>"Notice to Potential bidders: If you are the successful bidder on the subject property, you may be subject to filing</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>Sheri L. Morris, Trustee Sale Officer</t>
@@ -8132,11 +7452,11 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, owner_suspect, parcel_missing</t>
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -8170,11 +7490,7 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>"Notice to Potential bidders: If you are the successful bidder on the subject property, you may be subject to filing</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>Sheri L. Morris, Trustee Sale Officer</t>
@@ -8246,11 +7562,11 @@
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, owner_suspect</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -8284,11 +7600,7 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>"Notice to Potential bidders: If you are the successful bidder on the subject property, you may be subject to filing</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>Sheri L. Morris, Trustee Sale Officer</t>
@@ -8360,11 +7672,11 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, owner_suspect</t>
         </is>
       </c>
       <c r="AG65" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -8448,7 +7760,7 @@
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
@@ -8456,11 +7768,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
+      <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr"/>
@@ -8518,7 +7826,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kip M. Micuda and Ann E Haugen-Micuda, with right</t>
+          <t>Kip M. Micuda and Ann E Haugen-Micuda</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -8887,11 +8195,7 @@
           <t>Jimmie David Manning, Jr.</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>On this 34) day of April, 2026 before me, Stephen Daniel Clem, a Notary Public for said State, personally</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>$280,000.00</t>
@@ -8933,11 +8237,7 @@
           <t>$280,000.00</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>On this 34) day of April, 2026 before me, Stephen Daniel Clem, a Notary Public for said State, personally</t>
-        </is>
-      </c>
+      <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr">
         <is>
@@ -8962,11 +8262,11 @@
       </c>
       <c r="AF70" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>ocr_fallback, parcel_missing, trustee_suspect</t>
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -9016,26 +8316,10 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
@@ -9062,11 +8346,7 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
+      <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr"/>
@@ -9084,11 +8364,11 @@
       </c>
       <c r="AF71" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>address_missing, ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -9266,7 +8546,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026020083</t>
+          <t>(202) 602-0083</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -9472,26 +8752,10 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>201 W. JEFFERSON STREET</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
@@ -9544,11 +8808,11 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -9598,26 +8862,10 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>201 W. JEFFERSON STREET</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
@@ -9670,11 +8918,11 @@
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback</t>
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -9709,37 +8957,17 @@
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Default Services Department</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>$ 315,000.00</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
@@ -9759,26 +8987,14 @@
           <t>$ 315,000.00</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Default Services Department</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>480-214-4537</t>
-        </is>
-      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+      <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
@@ -9796,11 +9012,11 @@
       </c>
       <c r="AF77" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect</t>
+          <t>address_missing, ocr_fallback, owner_suspect, trustee_suspect</t>
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -9972,26 +9188,10 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
@@ -10026,11 +9226,7 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
+      <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr"/>
@@ -10048,11 +9244,11 @@
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>ocr_fallback, owner_suspect</t>
+          <t>address_missing, ocr_fallback, owner_suspect</t>
         </is>
       </c>
       <c r="AG79" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -10198,7 +9394,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Naomi M. Johnson AND Clifford Duwan Johnson, as joint tenants</t>
+          <t>Naomi M. Johnson AND Clifford Duwan Johnson</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -10564,7 +9760,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>COUNTY OF Maricopa ): 8s.</t>
+          <t>This instrument was acknowledged to me by Howard A. Chorost, a member of the State</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -10608,7 +9804,7 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026020204</t>
+          <t>(202) 602-0204</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
@@ -10616,11 +9812,7 @@
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
+      <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr"/>
@@ -10726,7 +9918,7 @@
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W85" t="inlineStr">
@@ -10734,11 +9926,7 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
+      <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
@@ -10796,14 +9984,10 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
+          <t>Sales Line: 800-758-8052</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
           <t>$384,899.00</t>
@@ -10837,16 +10021,8 @@
           <t>$384,899.00</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>2026020218</t>
-        </is>
-      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
       <c r="W86" t="inlineStr">
         <is>
           <t>2026-07-13</t>
@@ -10870,11 +10046,11 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -11007,11 +10183,7 @@
           <t>Peter Joseph Kennedy</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Please be advised that the trustee may require entity or trust bidders at this trustee's sale to provide</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>$75,000.00</t>
@@ -11041,26 +10213,14 @@
           <t>$75,000.00</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Please be advised that the trustee may require entity or trust bidders at this trustee's sale to provide</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>623-581-3262</t>
-        </is>
-      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
+      <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr"/>
@@ -11078,11 +10238,11 @@
       </c>
       <c r="AF88" t="inlineStr">
         <is>
-          <t>address_missing, ocr_fallback</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG88" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -11484,40 +10644,20 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
+          <t>Sales Line: 916-939-0772</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
           <t>$346,320.00</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
@@ -11537,16 +10677,8 @@
           <t>$346,320.00</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
       <c r="W92" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -11570,11 +10702,11 @@
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -11610,14 +10742,10 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
+          <t>Sales Line: 800-280-2832</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
           <t>$168,000.00</t>
@@ -11651,16 +10779,8 @@
           <t>$168,000.00</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>108 2026020</t>
-        </is>
-      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
       <c r="W93" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -11684,11 +10804,11 @@
       </c>
       <c r="AF93" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -11724,40 +10844,20 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
+          <t>Sales Line: 800-280-2832</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>$520,000.00</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
@@ -11777,16 +10877,8 @@
           <t>$520,000.00</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
       <c r="W94" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -11810,11 +10902,11 @@
       </c>
       <c r="AF94" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG94" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -11850,40 +10942,20 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
+          <t>Sales Line: 916-939-0772</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
           <t>$446,205.00</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
@@ -11903,16 +10975,8 @@
           <t>$446,205.00</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>http://www.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>(866) 645-7711</t>
-        </is>
-      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
       <c r="W95" t="inlineStr">
         <is>
           <t>2026-07-14</t>
@@ -11936,11 +11000,11 @@
       </c>
       <c r="AF95" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG95" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -11976,40 +11040,20 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>http://Awww.qualityloan.com</t>
-        </is>
-      </c>
+          <t>Sales Line: 800-280-2832</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>$154,646.00</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
@@ -12029,16 +11073,8 @@
           <t>$154,646.00</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>http://Awww.qualityloan.com</t>
-        </is>
-      </c>
-      <c r="V96" t="inlineStr">
-        <is>
-          <t>108 2026020</t>
-        </is>
-      </c>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
       <c r="W96" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -12062,11 +11098,11 @@
       </c>
       <c r="AF96" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -12116,26 +11152,10 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
@@ -12158,7 +11178,7 @@
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>1 2026020444</t>
+          <t>(202) 602-0444</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
@@ -12184,11 +11204,11 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>ocr_fallback, parcel_missing</t>
+          <t>address_missing, ocr_fallback, parcel_missing</t>
         </is>
       </c>
       <c r="AG97" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -12234,26 +11254,10 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
@@ -12274,21 +11278,13 @@
         </is>
       </c>
       <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>2026020477</t>
-        </is>
-      </c>
+      <c r="V98" t="inlineStr"/>
       <c r="W98" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
+      <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
       <c r="AA98" t="inlineStr"/>
@@ -12306,11 +11302,11 @@
       </c>
       <c r="AF98" t="inlineStr">
         <is>
-          <t>ocr_fallback, trustee_suspect</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG98" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -12588,11 +11584,7 @@
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>"Notice to Potential bidders: If you are the successful bidder on the subject property, you may be subject to filing</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>Sheri L. Morris, Trustee Sale Officer</t>
@@ -12664,11 +11656,11 @@
       </c>
       <c r="AF101" t="inlineStr">
         <is>
-          <t>ocr_fallback</t>
+          <t>ocr_fallback, owner_suspect</t>
         </is>
       </c>
       <c r="AG101" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -12704,7 +11696,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>DAVIDA K. KELLER AND MICHAEL KELLER, AS COMMUNITY</t>
+          <t>DAVIDA K. KELLER AND MICHAEL KELLER</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -12818,7 +11810,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CARL ANTHONY DANCKAERT, HUSBAND AND SARA MARIE DANCKAERT, WIFE</t>
+          <t>CARL ANTHONY DANCKAERT</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -12866,7 +11858,7 @@
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
@@ -12936,40 +11928,20 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>If the sale is set aside for any reason, including if the Trustee is unable to convey title, the Purchaser at the sale shall</t>
-        </is>
-      </c>
+          <t>Sales Line: 855-882-1314</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
           <t>$290,000.00</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
@@ -12989,11 +11961,7 @@
           <t>$290,000.00</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
-        <is>
-          <t>If the sale is set aside for any reason, including if the Trustee is unable to convey title, the Purchaser at the sale shall</t>
-        </is>
-      </c>
+      <c r="U104" t="inlineStr"/>
       <c r="V104" t="inlineStr"/>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
@@ -13014,11 +11982,11 @@
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>auction_date_missing, ocr_fallback</t>
+          <t>address_missing, auction_date_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG104" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="AH104" t="inlineStr">
         <is>
@@ -13064,26 +12032,10 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>201 W. Jefferson Street</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>85003</t>
-        </is>
-      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
@@ -13110,11 +12062,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
+      <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr"/>
       <c r="AA105" t="inlineStr"/>
@@ -13132,11 +12080,11 @@
       </c>
       <c r="AF105" t="inlineStr">
         <is>
-          <t>ocr_fallback, trustee_suspect</t>
+          <t>address_missing, ocr_fallback, trustee_suspect</t>
         </is>
       </c>
       <c r="AG105" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -13172,7 +12120,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>DAVID L. CASCIATO AND ROSEMARY L. CASCIATO, AS COMMUNITY</t>
+          <t>DAVID L. CASCIATO AND ROSEMARY L. CASCIATO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -13220,7 +12168,7 @@
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>949-252-8300</t>
+          <t>(949) 252-8300</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
@@ -13228,11 +12176,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
+      <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
       <c r="AA106" t="inlineStr"/>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,15 +413,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH106"/>
+  <dimension ref="A1:AH88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -436,7 +436,7 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
     <col width="15" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
@@ -445,7 +445,7 @@
     <col width="14" customWidth="1" min="27" max="27"/>
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="60" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="12" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
@@ -627,22 +627,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260189838</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>20260170977</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 9602 WECHO LN, PEORIA, AZ 85345</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -650,7 +662,11 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -662,31 +678,53 @@
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260170977.pdf</t>
+        </is>
+      </c>
       <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
       <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260189851</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>20260171315</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 7745 W JENAN DR, PEORIA, AZ 85345</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -694,7 +732,11 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -706,31 +748,53 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260171315.pdf</t>
+        </is>
+      </c>
       <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
       <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260190248</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>20260171369</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 3726 E SALINAS ST, PHOENIX, AZ 85044</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -738,7 +802,11 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -750,31 +818,53 @@
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260171369.pdf</t>
+        </is>
+      </c>
       <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
       <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260190396</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>20260171624</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 15562 W HACKAMORE DR, SURPRISE, AZ 85387</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -782,7 +872,11 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -794,31 +888,53 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260171624.pdf</t>
+        </is>
+      </c>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
       <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260190991</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>20260171680</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 23403 S 228TH STREET, QUEEN CREEK, AZ 85142</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -826,7 +942,11 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -838,31 +958,53 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260171680.pdf</t>
+        </is>
+      </c>
       <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
       <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260191611</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>20260172186</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 113 W LIBBY ST, PHOENIX, AZ 85023</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -870,7 +1012,11 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -882,31 +1028,53 @@
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260172186.pdf</t>
+        </is>
+      </c>
       <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
       <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260191625</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>20260172339</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>8329 East Charter Oak Road, Scottsdale, AZ 85260</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -914,7 +1082,11 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -926,31 +1098,53 @@
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260172339.pdf</t>
+        </is>
+      </c>
       <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
       <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260191626</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>20260172604</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>7575 E Redfield #219, Scottsdale, AZ 85260</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -958,7 +1152,11 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -970,31 +1168,53 @@
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260172604.pdf</t>
+        </is>
+      </c>
       <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
       <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260191627</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>20260172605</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>7575 E Redfield #219, Scottsdale, AZ 85260</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -1002,7 +1222,11 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -1014,31 +1238,53 @@
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260172605.pdf</t>
+        </is>
+      </c>
       <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
       <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260191631</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>20260172672</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>7575 E Redfield #219, Scottsdale, AZ 85260</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1046,7 +1292,11 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -1058,31 +1308,53 @@
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260172672.pdf</t>
+        </is>
+      </c>
       <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
       <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260191651</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>20260172690</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>7575 E Redfield #219, Scottsdale, AZ 85260</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1090,7 +1362,11 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1102,31 +1378,53 @@
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260172690.pdf</t>
+        </is>
+      </c>
       <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
       <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260191655</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+          <t>20260172705</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>11001 N Rockwell, Oklahoma City, OK 73162</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -1134,7 +1432,11 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -1146,31 +1448,53 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260172705.pdf</t>
+        </is>
+      </c>
       <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
       <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260191662</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+          <t>20260173080</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>3707 East Southern Avenue, Mesa, AZ 85206</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -1178,7 +1502,11 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -1190,22 +1518,48 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260173080.pdf</t>
+        </is>
+      </c>
       <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
       <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260191740</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>20260173090</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -1218,7 +1572,11 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -1230,31 +1588,53 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260173090.pdf</t>
+        </is>
+      </c>
       <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
       <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260191897</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+          <t>20260173122</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>8950 Cypress Waters Blyd, Coppell, TX 75019</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -1262,7 +1642,11 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -1274,22 +1658,48 @@
       <c r="AA16" t="inlineStr"/>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260173122.pdf</t>
+        </is>
+      </c>
       <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
       <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260192403</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+          <t>20260173239</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -1302,7 +1712,11 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -1314,31 +1728,53 @@
       <c r="AA17" t="inlineStr"/>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260173239.pdf</t>
+        </is>
+      </c>
       <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
       <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260192558</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+          <t>20260173254</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -1346,7 +1782,11 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -1358,31 +1798,53 @@
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260173254.pdf</t>
+        </is>
+      </c>
       <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
       <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260192629</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+          <t>20260173263</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 16, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -1390,7 +1852,11 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -1402,31 +1868,53 @@
       <c r="AA19" t="inlineStr"/>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260173263.pdf</t>
+        </is>
+      </c>
       <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
       <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260192666</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>20260173265</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -1434,7 +1922,11 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -1446,31 +1938,53 @@
       <c r="AA20" t="inlineStr"/>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260173265.pdf</t>
+        </is>
+      </c>
       <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
       <c r="AH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260192668</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+          <t>20260173416</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 8617 S 9TH ST, PHOENIX, AZ 85042-7851</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -1478,7 +1992,11 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -1490,31 +2008,53 @@
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260173416.pdf</t>
+        </is>
+      </c>
       <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
       <c r="AH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20260192700</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+          <t>20260173626</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>8950 Cypress Waters Blvd, Coppell, TX 75019</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
@@ -1522,7 +2062,11 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -1534,22 +2078,48 @@
       <c r="AA22" t="inlineStr"/>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260173626.pdf</t>
+        </is>
+      </c>
       <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
       <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20260192707</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+          <t>20260173646</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1562,7 +2132,11 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -1574,31 +2148,53 @@
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260173646.pdf</t>
+        </is>
+      </c>
       <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
       <c r="AH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>20260192766</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+          <t>20260174122</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave, Irvine, CA 92614</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -1606,7 +2202,11 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
@@ -1618,31 +2218,53 @@
       <c r="AA24" t="inlineStr"/>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260174122.pdf</t>
+        </is>
+      </c>
       <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
       <c r="AH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20260192883</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+          <t>20260174417</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 246 SOUTH 90TH PLACE, MESA, AZ 85208</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -1650,7 +2272,11 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
@@ -1662,31 +2288,53 @@
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260174417.pdf</t>
+        </is>
+      </c>
       <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
       <c r="AH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20260192896</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>20260174422</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>1355 Willow Way Ste 250, Concord, CA 94520</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -1694,7 +2342,11 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -1706,31 +2358,53 @@
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260174422.pdf</t>
+        </is>
+      </c>
       <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
       <c r="AH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>20260192940</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+          <t>20260174586</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -1738,7 +2412,11 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -1750,31 +2428,53 @@
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260174586.pdf</t>
+        </is>
+      </c>
       <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
       <c r="AH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>20260192943</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+          <t>20260174643</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 15800 W ALVARADO DR, GOODYEAR, AZ 85395</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -1782,7 +2482,11 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
@@ -1794,31 +2498,53 @@
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260174643.pdf</t>
+        </is>
+      </c>
       <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
       <c r="AH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20260192978</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+          <t>20260174814</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>4300 N. Miller Rd., Ste. 110-02, Scottsdale, AZ 85251</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -1826,7 +2552,11 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -1838,31 +2568,53 @@
       <c r="AA29" t="inlineStr"/>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260174814.pdf</t>
+        </is>
+      </c>
       <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
       <c r="AH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>20260192984</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+          <t>20260175047</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -1870,7 +2622,11 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -1882,31 +2638,53 @@
       <c r="AA30" t="inlineStr"/>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260175047.pdf</t>
+        </is>
+      </c>
       <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
       <c r="AH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20260192994</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+          <t>20260175171</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>4300 N. Miller Rd., Ste. 110-02, Scottsdale, AZ 85251</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -1914,7 +2692,11 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
@@ -1926,31 +2708,53 @@
       <c r="AA31" t="inlineStr"/>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260175171.pdf</t>
+        </is>
+      </c>
       <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
       <c r="AH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>20260193030</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+          <t>20260175467</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave, Irvine, CA 92614</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -1958,7 +2762,11 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -1970,31 +2778,53 @@
       <c r="AA32" t="inlineStr"/>
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260175467.pdf</t>
+        </is>
+      </c>
       <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
       <c r="AH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20260193112</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+          <t>20260175543</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2999 N. 44" Street, Ste. 625, Phoenix, AZ 85018</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2002,7 +2832,11 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
@@ -2014,31 +2848,53 @@
       <c r="AA33" t="inlineStr"/>
       <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260175543.pdf</t>
+        </is>
+      </c>
       <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
       <c r="AH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20260193202</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+          <t>20260175742</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -2046,7 +2902,11 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
@@ -2058,31 +2918,53 @@
       <c r="AA34" t="inlineStr"/>
       <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260175742.pdf</t>
+        </is>
+      </c>
       <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
       <c r="AH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20260193241</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+          <t>20260176121</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2254 University Drive Unit 5, Mesa, AZ 85213</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2090,7 +2972,11 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
@@ -2102,31 +2988,53 @@
       <c r="AA35" t="inlineStr"/>
       <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260176121.pdf</t>
+        </is>
+      </c>
       <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
       <c r="AH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20260193873</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+          <t>20260176154</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave, irvine, CA 92614</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2134,7 +3042,11 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
@@ -2146,31 +3058,53 @@
       <c r="AA36" t="inlineStr"/>
       <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260176154.pdf</t>
+        </is>
+      </c>
       <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
       <c r="AH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20260194588</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+          <t>20260176194</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>8656 W. Mountain View Rd, Peoria, AZ 85345</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -2178,7 +3112,11 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
@@ -2190,31 +3128,53 @@
       <c r="AA37" t="inlineStr"/>
       <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260176194.pdf</t>
+        </is>
+      </c>
       <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
       <c r="AH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>20260194891</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+          <t>20260176391</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -2222,7 +3182,11 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
@@ -2234,31 +3198,53 @@
       <c r="AA38" t="inlineStr"/>
       <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260176391.pdf</t>
+        </is>
+      </c>
       <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
       <c r="AH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>20260195052</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+          <t>20260176423</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 808 N BLUE MARLIN DRIVE, GILBERT, AZ 85234</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -2266,7 +3252,11 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
@@ -2278,31 +3268,53 @@
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260176423.pdf</t>
+        </is>
+      </c>
       <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
       <c r="AH39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>20260195145</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+          <t>20260176763</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -2310,7 +3322,11 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
@@ -2322,31 +3338,53 @@
       <c r="AA40" t="inlineStr"/>
       <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260176763.pdf</t>
+        </is>
+      </c>
       <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
       <c r="AH40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>20260195158</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+          <t>20260176765</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 16, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -2354,7 +3392,11 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
@@ -2366,31 +3408,53 @@
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260176765.pdf</t>
+        </is>
+      </c>
       <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
       <c r="AH41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20260195172</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+          <t>20260176766</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 16, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -2398,7 +3462,11 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
@@ -2410,31 +3478,53 @@
       <c r="AA42" t="inlineStr"/>
       <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260176766.pdf</t>
+        </is>
+      </c>
       <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
       <c r="AH42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20260195201</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+          <t>20260176863</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -2442,7 +3532,11 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
@@ -2454,31 +3548,53 @@
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260176863.pdf</t>
+        </is>
+      </c>
       <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
       <c r="AH43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>20260195224</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+          <t>20260176872</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>6332 W Ocotillo Rd, Glendale, AZ 85301-3026</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -2486,7 +3602,11 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
@@ -2498,22 +3618,48 @@
       <c r="AA44" t="inlineStr"/>
       <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260176872.pdf</t>
+        </is>
+      </c>
       <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
       <c r="AH44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>20260195896</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+          <t>20260177416</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -2526,7 +3672,11 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
@@ -2538,31 +3688,53 @@
       <c r="AA45" t="inlineStr"/>
       <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260177416.pdf</t>
+        </is>
+      </c>
       <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
       <c r="AH45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>20260195937</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+          <t>20260177428</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>20824-20418 N. 47th Avenue, Glendale, AZ 85308</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
@@ -2570,7 +3742,11 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
@@ -2582,31 +3758,53 @@
       <c r="AA46" t="inlineStr"/>
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260177428.pdf</t>
+        </is>
+      </c>
       <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
       <c r="AH46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>20260195960</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+          <t>20260177454</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -2614,7 +3812,11 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
@@ -2626,31 +3828,53 @@
       <c r="AA47" t="inlineStr"/>
       <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260177454.pdf</t>
+        </is>
+      </c>
       <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
       <c r="AH47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20260196009</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+          <t>20260177461</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>10802 W Canterbury Dr, Sun City, AZ 85351</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -2658,7 +3882,11 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
@@ -2670,31 +3898,53 @@
       <c r="AA48" t="inlineStr"/>
       <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260177461.pdf</t>
+        </is>
+      </c>
       <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
       <c r="AH48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>20260196023</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+          <t>20260177987</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 14, 2026 at 10:00 AM in the Courtyard, by the main entrance of the, Superior Court Building, 201 West Jefferson, Phoenix, AZ 85003 and the property will be sold by the Trustee to</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
@@ -2702,7 +3952,11 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
@@ -2714,31 +3968,53 @@
       <c r="AA49" t="inlineStr"/>
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260177987.pdf</t>
+        </is>
+      </c>
       <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
       <c r="AH49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20260196029</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+          <t>20260178572</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -2746,7 +4022,11 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
@@ -2758,31 +4038,53 @@
       <c r="AA50" t="inlineStr"/>
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260178572.pdf</t>
+        </is>
+      </c>
       <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
       <c r="AH50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20260196134</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+          <t>20260178574</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -2790,7 +4092,11 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
@@ -2802,31 +4108,53 @@
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260178574.pdf</t>
+        </is>
+      </c>
       <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
       <c r="AH51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20260196140</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+          <t>20260178778</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -2834,7 +4162,11 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
@@ -2846,31 +4178,53 @@
       <c r="AA52" t="inlineStr"/>
       <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260178778.pdf</t>
+        </is>
+      </c>
       <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
       <c r="AH52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20260196332</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+          <t>20260178857</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2315 N Avoca, Mesa, AZ 85207</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -2878,7 +4232,11 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
@@ -2890,31 +4248,53 @@
       <c r="AA53" t="inlineStr"/>
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260178857.pdf</t>
+        </is>
+      </c>
       <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
       <c r="AH53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20260196404</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+          <t>20260179571</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -2922,7 +4302,11 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
@@ -2934,22 +4318,48 @@
       <c r="AA54" t="inlineStr"/>
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260179571.pdf</t>
+        </is>
+      </c>
       <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
       <c r="AH54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20260196494</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+          <t>20260180029</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
@@ -2962,7 +4372,11 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
@@ -2974,31 +4388,53 @@
       <c r="AA55" t="inlineStr"/>
       <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260180029.pdf</t>
+        </is>
+      </c>
       <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
       <c r="AH55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20260196990</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+          <t>20260180034</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>3707 East Southern Avenue Ga, Mesa, AZ 85206</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -3006,7 +4442,11 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
@@ -3018,31 +4458,53 @@
       <c r="AA56" t="inlineStr"/>
       <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260180034.pdf</t>
+        </is>
+      </c>
       <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
       <c r="AH56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20260196995</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+          <t>20260180047</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2999 N. 44" Street, Ste. 625, Phoenix, AZ 85018</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
@@ -3050,7 +4512,11 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -3062,31 +4528,53 @@
       <c r="AA57" t="inlineStr"/>
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260180047.pdf</t>
+        </is>
+      </c>
       <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
       <c r="AH57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20260198192</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+          <t>20260180059</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2999 N. 44" Street, Ste. 625, Phoenix, AZ 85018</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
@@ -3094,7 +4582,11 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -3106,31 +4598,53 @@
       <c r="AA58" t="inlineStr"/>
       <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr"/>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260180059.pdf</t>
+        </is>
+      </c>
       <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
       <c r="AH58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20260198434</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+          <t>20260180084</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>3707 East Southern Avenue Ho:, Mesa, AZ 85206</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
@@ -3138,7 +4652,11 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -3150,31 +4668,53 @@
       <c r="AA59" t="inlineStr"/>
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr"/>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260180084.pdf</t>
+        </is>
+      </c>
       <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
       <c r="AH59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20260198528</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+          <t>20260180223</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
@@ -3182,7 +4722,11 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -3194,31 +4738,53 @@
       <c r="AA60" t="inlineStr"/>
       <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr"/>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260180223.pdf</t>
+        </is>
+      </c>
       <c r="AE60" t="inlineStr"/>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>0</v>
+      </c>
       <c r="AH60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>20260198560</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+          <t>20260180562</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>3707 East Southern Avenue To, Mesa, AZ 85206</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -3226,7 +4792,11 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -3238,31 +4808,53 @@
       <c r="AA61" t="inlineStr"/>
       <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr"/>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260180562.pdf</t>
+        </is>
+      </c>
       <c r="AE61" t="inlineStr"/>
-      <c r="AF61" t="inlineStr"/>
-      <c r="AG61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
+        <v>0</v>
+      </c>
       <c r="AH61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20260198786</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+          <t>20260180692</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>of Maricopa County, Arizona, in Book 39 of Maps, Page 32., PURPORTED PROPERTY ADDRESS: 2437 W. Yavapai St., Phoenix, AZ 85009</t>
-        </is>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -3270,7 +4862,11 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -3282,27 +4878,45 @@
       <c r="AA62" t="inlineStr"/>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
-      <c r="AD62" t="inlineStr"/>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260180692.pdf</t>
+        </is>
+      </c>
       <c r="AE62" t="inlineStr"/>
-      <c r="AF62" t="inlineStr"/>
-      <c r="AG62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>no_pdf</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>0</v>
+      </c>
       <c r="AH62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>20260198797</t>
+          <t>20260181745</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Paula McAllister and Chad McAllister, a married couple as Community Property with Rights of Survivorship.</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>18, 2021 AS INSTRUMENT NO. 20210891037 OF OFFICIAL RECORDS., 13740 W BANFF LN, SURPRISE, AZ 85379</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -3313,9 +4927,17 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of sale under that certain Deed</t>
+        </is>
+      </c>
       <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
@@ -3331,18 +4953,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20260198817</t>
+          <t>20260181935</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Black Rock 16 L.P., an Arizona limited partnership</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>7575 E Redfield #219, Scottsdale, AZ 85260</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
@@ -3353,9 +4983,17 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain</t>
+        </is>
+      </c>
       <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
@@ -3371,18 +5009,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20260198819</t>
+          <t>20260181937</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Black Rock 16 L.P., an Arizona limited partnership</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>7875 E Redfield #219, Scottsdale, AZ 85260</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -3393,9 +5039,17 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain</t>
+        </is>
+      </c>
       <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
@@ -3411,20 +5065,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20260198938</t>
+          <t>20260181939</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Black Rock 16 L.P., an Arizona limited partnership</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave, Irvine, CA 92614</t>
+          <t>7575 E Redfield #219, Scottsdale, AZ 85260</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -3437,9 +5095,17 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain</t>
+        </is>
+      </c>
       <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
@@ -3455,20 +5121,24 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20260198994</t>
+          <t>20260181961</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Alexis Omar Alvarez, an unmarried woman</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>16509 E Lone Mountain Rd, Scottsdale, AZ 85262</t>
+          <t>10529 W Loma Lane, Peoria, AZ 85345</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -3481,9 +5151,17 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain</t>
+        </is>
+      </c>
       <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
@@ -3499,20 +5177,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20260199010</t>
+          <t>20260181963</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Wesley Bohmler, an unmarried man</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
-          <t>8546 E Meseto Ave, Mesa, AZ 85209</t>
+          <t>6726 S 37TH LANE, PHOENIX, AZ 85041</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -3525,9 +5207,17 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain</t>
+        </is>
+      </c>
       <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
@@ -3543,20 +5233,24 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20260199011</t>
+          <t>20260181965</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Wesley Bohmler, an unmarried man</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>135 N Fraser Dr, Mesa, AZ 85203</t>
+          <t>6726 S 37TH LANE, PHOENIX, AZ 85041</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -3569,9 +5263,17 @@
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain</t>
+        </is>
+      </c>
       <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
@@ -3587,20 +5289,24 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20260199025</t>
+          <t>20260182010</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JUAN M CABADA, A MARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
+          <t>highest bidder at the Main Entrance to the Superior Court Building, Maricopa County Courthouse, 201 W., Jefferson Street, Phoenix, AZ 85003, in Maricopa County, on 07/09/2026 at 10:00 AM of said day:</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -3613,9 +5319,17 @@
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of sale under that certain Deed</t>
+        </is>
+      </c>
       <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
@@ -3631,20 +5345,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20260200681</t>
+          <t>20260182127</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JESUS M. AGUILAR</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>15826 MERCER LN, Surprise, AZ 85379</t>
+          <t>3707 East Southern Avenue, Mesa, AZ 85206</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -3657,9 +5375,17 @@
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain Deed of</t>
+        </is>
+      </c>
       <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
@@ -3675,20 +5401,24 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20260200826</t>
+          <t>20260182418</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ANITA NUNES</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2032 E. Harvard Street, Phoenix, AZ 85258</t>
+          <t>3707 East Southern Avenue Ho:, Mesa, AZ 85206</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -3701,9 +5431,17 @@
       <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain Deed of</t>
+        </is>
+      </c>
       <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
@@ -3719,20 +5457,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20260200835</t>
+          <t>20260183240</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>community property, nor as joint tenants with right of survivorship, but as community property with right of</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2538 E. Maddock Road, Cave Creek, AZ 85331</t>
+          <t>4524 West Judson Drive, New River, AZ 85087</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -3745,7 +5487,11 @@
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>File ID. #26-01018-MC-AZ Croteau</t>
+        </is>
+      </c>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
@@ -3763,20 +5509,24 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>20260201371</t>
+          <t>20260183254</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>of survivorship</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>BE FINAL AND WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the, Superior Courts Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the</t>
+          <t>221 N 107th Dr, Avondale, AZ 85323</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -3789,7 +5539,11 @@
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>File ID. #26-05274-US-AZ Badilla</t>
+        </is>
+      </c>
       <c r="V74" t="inlineStr"/>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
@@ -3807,20 +5561,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>20260201418</t>
+          <t>20260183277</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>6120 W Townley Ave, Glendale, AZ 85302</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>3707 East Southern Avenue To, Mesa, AZ 85206</t>
+          <t>6120 W Townley Ave, Glendale, AZ 85302</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -3833,7 +5591,11 @@
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>File ID. #26-05093-US-AZ Beth</t>
+        </is>
+      </c>
       <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
@@ -3851,20 +5613,24 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>20260201442</t>
+          <t>20260183481</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>LADEAN MELBY</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>3707 East Southern Avenue mo, Mesa, AZ 85206</t>
+          <t>3707 East Southern Avenue Ho:, Mesa, AZ 85206</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -3877,9 +5643,17 @@
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain Deed of</t>
+        </is>
+      </c>
       <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
@@ -3895,20 +5669,24 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20260201682</t>
+          <t>20260183653</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ASHLEY DOHI AND URIAH DOHI, WIFE AND HUSBAND,</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>50331 N 23RD DR, NEW RIVER, AZ 85087</t>
+          <t>9726 Old Bailes Rd Ste 200, Fort Mill, SC 29707</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -3921,9 +5699,17 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>NOTICE! IF YOU BELIEVE THERE IS A DEFENSE TO THE TRUSTEE SALE OR IF YOU HAVE AN</t>
+        </is>
+      </c>
       <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
@@ -3939,20 +5725,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20260201709</t>
+          <t>20260183900</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Christine Brockman, A Single Woman</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2150 E. Brown Road, Ste 2 60, Mesa, AZ 85213 mo</t>
+          <t>915 S 96TH PL, MESA, AZ 85208</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -3965,9 +5755,17 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain</t>
+        </is>
+      </c>
       <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
@@ -3983,18 +5781,26 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20260201730</t>
+          <t>20260183907</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Casandra Cronk, an unmarried woman</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>6611 W ALTADENA AVE, GLENDALE, AZ 85304</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
@@ -4005,9 +5811,17 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain</t>
+        </is>
+      </c>
       <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
@@ -4023,20 +5837,24 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>20260201897</t>
+          <t>20260184004</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., an Arizona Limited Liability Company</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
+          <t>Street address or identifiable 4037 S 12th St, Unit 106 &amp; 206, location: Phoenix, AZ 85040</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -4049,9 +5867,17 @@
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that</t>
+        </is>
+      </c>
       <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
@@ -4067,20 +5893,24 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>20260201906</t>
+          <t>20260184020</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., a Arizona Limited Liability Company</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
-          <t>7204 South 48th Drive, Laveen, AZ 85339</t>
+          <t>Street address or identifiable 4037 S 12th St Unit 112 &amp; 212, location: Phoenix, AZ 85040</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -4093,9 +5923,17 @@
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that</t>
+        </is>
+      </c>
       <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
@@ -4111,20 +5949,24 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>20260201933</t>
+          <t>20260184280</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1310 Muscovy Drive, Gillette, WY 82718</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
-          <t>9317 West Marshall Avenue, Glendale, AZ 85305-2711</t>
+          <t>3508 E Megan St, Gilbert, AZ 85295</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -4137,9 +5979,17 @@
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>File ID. #26-05036-JP-AZ Anderson</t>
+        </is>
+      </c>
       <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
@@ -4155,20 +6005,24 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20260201940</t>
+          <t>20260184293</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>28220 N 90th Ln, Peoria, AZ 85383</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
-          <t>10532 W Crown King Rd, Tolleson, AZ 85353</t>
+          <t>28220 N 90th Ln, Peoria, AZ 85383</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -4181,9 +6035,17 @@
       <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>File ID. #26-05273-MS-AZ Cliburn</t>
+        </is>
+      </c>
       <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
@@ -4199,20 +6061,24 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>20260202046</t>
+          <t>20260184413</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>17624 W Lilac St, Goodyear, Arizona 85338</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Purported street address: 18251 W MEADOWBROOK AVE, GOODYEAR, AZ 85395</t>
+          <t>17624 W Lilac St, Goodyear, AZ 85338</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -4225,9 +6091,17 @@
       <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>File ID. #26-05362-VC-AZ Davis</t>
+        </is>
+      </c>
       <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
@@ -4243,20 +6117,24 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>20260202182</t>
+          <t>20260184636</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>20260184636</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
-          <t>17100 Gillette Ave, Irvine, CA 92614</t>
+          <t>3637 Sentara Way, Virginia Beach, VA 23452</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -4269,9 +6147,17 @@
       <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain Deed of</t>
+        </is>
+      </c>
       <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
@@ -4287,20 +6173,24 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>20260202185</t>
+          <t>20260184908</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>DANIEL PITNER AND ALYSSA PITNER</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
+          <t>3707 East Southern Avenue, Mesa, AZ 85206</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -4313,9 +6203,17 @@
       <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain Deed of</t>
+        </is>
+      </c>
       <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
@@ -4331,22 +6229,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>20260202502</t>
+          <t>20260184912</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1148 N, ESTRADA, MESA, AZ 85207</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>5420 W. Onyx Ave., Glendale, AZ 85302</t>
-        </is>
-      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
@@ -4357,9 +6255,17 @@
       <c r="R87" t="inlineStr"/>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>The following legally described trust property will be sold, pursuant to the power of Sale under that certain Deed of</t>
+        </is>
+      </c>
       <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr"/>
@@ -4375,20 +6281,24 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>20260203024</t>
+          <t>20260184938</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>WANDA P. YEAGER, AN UNMARRIED WOMAN</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Street address or identifiable 4529 W Berridge Ln, location: Glendale, AZ 85301</t>
+          <t>3900 Capital City Blvd, Lansing, MI 48906</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -4401,7 +6311,11 @@
       <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>17100 Gillette Ave</t>
+        </is>
+      </c>
       <c r="V88" t="inlineStr"/>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
@@ -4416,794 +6330,6 @@
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>20260203655</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>2150 E. Brown Road, Ste 2 60, Mesa, AZ 85213 Ga</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-      <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr"/>
-      <c r="AC89" t="inlineStr"/>
-      <c r="AD89" t="inlineStr"/>
-      <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr"/>
-      <c r="AG89" t="inlineStr"/>
-      <c r="AH89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>20260203683</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>2150 E. Brown Road, Ste 2 60, Mesa, AZ 85213 Ho:</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
-      <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr"/>
-      <c r="AC90" t="inlineStr"/>
-      <c r="AD90" t="inlineStr"/>
-      <c r="AE90" t="inlineStr"/>
-      <c r="AF90" t="inlineStr"/>
-      <c r="AG90" t="inlineStr"/>
-      <c r="AH90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>20260203883</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>2999 N. 44" Street, Ste. 625, Phoenix, AZ 85018</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
-      <c r="Y91" t="inlineStr"/>
-      <c r="Z91" t="inlineStr"/>
-      <c r="AA91" t="inlineStr"/>
-      <c r="AB91" t="inlineStr"/>
-      <c r="AC91" t="inlineStr"/>
-      <c r="AD91" t="inlineStr"/>
-      <c r="AE91" t="inlineStr"/>
-      <c r="AF91" t="inlineStr"/>
-      <c r="AG91" t="inlineStr"/>
-      <c r="AH91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>20260203946</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
-      <c r="X92" t="inlineStr"/>
-      <c r="Y92" t="inlineStr"/>
-      <c r="Z92" t="inlineStr"/>
-      <c r="AA92" t="inlineStr"/>
-      <c r="AB92" t="inlineStr"/>
-      <c r="AC92" t="inlineStr"/>
-      <c r="AD92" t="inlineStr"/>
-      <c r="AE92" t="inlineStr"/>
-      <c r="AF92" t="inlineStr"/>
-      <c r="AG92" t="inlineStr"/>
-      <c r="AH92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>20260203989</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
-      <c r="X93" t="inlineStr"/>
-      <c r="Y93" t="inlineStr"/>
-      <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr"/>
-      <c r="AB93" t="inlineStr"/>
-      <c r="AC93" t="inlineStr"/>
-      <c r="AD93" t="inlineStr"/>
-      <c r="AE93" t="inlineStr"/>
-      <c r="AF93" t="inlineStr"/>
-      <c r="AG93" t="inlineStr"/>
-      <c r="AH93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>20260204001</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
-      <c r="X94" t="inlineStr"/>
-      <c r="Y94" t="inlineStr"/>
-      <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr"/>
-      <c r="AB94" t="inlineStr"/>
-      <c r="AC94" t="inlineStr"/>
-      <c r="AD94" t="inlineStr"/>
-      <c r="AE94" t="inlineStr"/>
-      <c r="AF94" t="inlineStr"/>
-      <c r="AG94" t="inlineStr"/>
-      <c r="AH94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>20260204029</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
-      <c r="X95" t="inlineStr"/>
-      <c r="Y95" t="inlineStr"/>
-      <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
-      <c r="AB95" t="inlineStr"/>
-      <c r="AC95" t="inlineStr"/>
-      <c r="AD95" t="inlineStr"/>
-      <c r="AE95" t="inlineStr"/>
-      <c r="AF95" t="inlineStr"/>
-      <c r="AG95" t="inlineStr"/>
-      <c r="AH95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>20260204357</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>2763 Camino Del Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
-      <c r="Y96" t="inlineStr"/>
-      <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
-      <c r="AB96" t="inlineStr"/>
-      <c r="AC96" t="inlineStr"/>
-      <c r="AD96" t="inlineStr"/>
-      <c r="AE96" t="inlineStr"/>
-      <c r="AF96" t="inlineStr"/>
-      <c r="AG96" t="inlineStr"/>
-      <c r="AH96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>20260204443</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>9726 Old Bailes Rd Ste 200, Fort Mill, SC 29707</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr"/>
-      <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
-      <c r="AB97" t="inlineStr"/>
-      <c r="AC97" t="inlineStr"/>
-      <c r="AD97" t="inlineStr"/>
-      <c r="AE97" t="inlineStr"/>
-      <c r="AF97" t="inlineStr"/>
-      <c r="AG97" t="inlineStr"/>
-      <c r="AH97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>20260204779</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>323 Fifth Street, Eureka, CA 95501</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
-      <c r="X98" t="inlineStr"/>
-      <c r="Y98" t="inlineStr"/>
-      <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
-      <c r="AB98" t="inlineStr"/>
-      <c r="AC98" t="inlineStr"/>
-      <c r="AD98" t="inlineStr"/>
-      <c r="AE98" t="inlineStr"/>
-      <c r="AF98" t="inlineStr"/>
-      <c r="AG98" t="inlineStr"/>
-      <c r="AH98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>20260204838</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 23, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
-      <c r="X99" t="inlineStr"/>
-      <c r="Y99" t="inlineStr"/>
-      <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
-      <c r="AC99" t="inlineStr"/>
-      <c r="AD99" t="inlineStr"/>
-      <c r="AE99" t="inlineStr"/>
-      <c r="AF99" t="inlineStr"/>
-      <c r="AG99" t="inlineStr"/>
-      <c r="AH99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>20260204845</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>WILL OCCUR at public auction on July 30, 2026 at 10:00 AM at the Main Entrance to the Superior Courts, Building at the Maricopa County Courthouse, 201 W. Jefferson, Phoenix, AZ 85003 and the property will be</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
-      <c r="X100" t="inlineStr"/>
-      <c r="Y100" t="inlineStr"/>
-      <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr"/>
-      <c r="AC100" t="inlineStr"/>
-      <c r="AD100" t="inlineStr"/>
-      <c r="AE100" t="inlineStr"/>
-      <c r="AF100" t="inlineStr"/>
-      <c r="AG100" t="inlineStr"/>
-      <c r="AH100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>20260204967</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
-      <c r="X101" t="inlineStr"/>
-      <c r="Y101" t="inlineStr"/>
-      <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="inlineStr"/>
-      <c r="AB101" t="inlineStr"/>
-      <c r="AC101" t="inlineStr"/>
-      <c r="AD101" t="inlineStr"/>
-      <c r="AE101" t="inlineStr"/>
-      <c r="AF101" t="inlineStr"/>
-      <c r="AG101" t="inlineStr"/>
-      <c r="AH101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>20260205429</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>2999 N, 44" Street, Ste. 625, Phoenix, AZ 85018</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
-      <c r="X102" t="inlineStr"/>
-      <c r="Y102" t="inlineStr"/>
-      <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr"/>
-      <c r="AB102" t="inlineStr"/>
-      <c r="AC102" t="inlineStr"/>
-      <c r="AD102" t="inlineStr"/>
-      <c r="AE102" t="inlineStr"/>
-      <c r="AF102" t="inlineStr"/>
-      <c r="AG102" t="inlineStr"/>
-      <c r="AH102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>20260205432</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave, Irvine, CA 92614</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
-      <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
-      <c r="X103" t="inlineStr"/>
-      <c r="Y103" t="inlineStr"/>
-      <c r="Z103" t="inlineStr"/>
-      <c r="AA103" t="inlineStr"/>
-      <c r="AB103" t="inlineStr"/>
-      <c r="AC103" t="inlineStr"/>
-      <c r="AD103" t="inlineStr"/>
-      <c r="AE103" t="inlineStr"/>
-      <c r="AF103" t="inlineStr"/>
-      <c r="AG103" t="inlineStr"/>
-      <c r="AH103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>20260205473</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>2763 Camino Dei Rio South, San Diego, CA 92108</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
-      <c r="X104" t="inlineStr"/>
-      <c r="Y104" t="inlineStr"/>
-      <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
-      <c r="AB104" t="inlineStr"/>
-      <c r="AC104" t="inlineStr"/>
-      <c r="AD104" t="inlineStr"/>
-      <c r="AE104" t="inlineStr"/>
-      <c r="AF104" t="inlineStr"/>
-      <c r="AG104" t="inlineStr"/>
-      <c r="AH104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>20260205520</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>Street address or identifiable location: 2350 W BRANHAM LN, PHOENIX, AZ 85041</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
-      <c r="X105" t="inlineStr"/>
-      <c r="Y105" t="inlineStr"/>
-      <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr"/>
-      <c r="AB105" t="inlineStr"/>
-      <c r="AC105" t="inlineStr"/>
-      <c r="AD105" t="inlineStr"/>
-      <c r="AE105" t="inlineStr"/>
-      <c r="AF105" t="inlineStr"/>
-      <c r="AG105" t="inlineStr"/>
-      <c r="AH105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>20260205551</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>17100 Gillette Ave, Irvine, CA 92614</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
-      <c r="X106" t="inlineStr"/>
-      <c r="Y106" t="inlineStr"/>
-      <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
-      <c r="AB106" t="inlineStr"/>
-      <c r="AC106" t="inlineStr"/>
-      <c r="AD106" t="inlineStr"/>
-      <c r="AE106" t="inlineStr"/>
-      <c r="AF106" t="inlineStr"/>
-      <c r="AG106" t="inlineStr"/>
-      <c r="AH106" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/nts_data.xlsx
+++ b/nts_data.xlsx
@@ -413,20 +413,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AH64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="56" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
@@ -436,20 +436,20 @@
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="15" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="54" customWidth="1" min="25" max="25"/>
     <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
-    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="60" customWidth="1" min="30" max="30"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="49" customWidth="1" min="32" max="32"/>
     <col width="12" customWidth="1" min="33" max="33"/>
-    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,6 +621,7524 @@
       <c r="AH1" t="inlineStr">
         <is>
           <t>raw_text_path</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260211720</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(s): William Gunty And Jennifer Gunty</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>548,250.00</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10537 E LUMIERE AVE</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>85212</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>304-50-409</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>(202) 101-0388</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>(s): William Gunty And Jennifer</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Gunty</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260211720.pdf</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260211720.pdf</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260211720.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260211848</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>276,822.00</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>or identifiable location: 12164 WEST RIO VISTA LANE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Avondale</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>500-32-628</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee Sale</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>(858) 882-1314</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2017-12-21</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260211848.pdf</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260211848.pdf</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260211848.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260211893</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>874,250.00</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>219-31-796</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(949) 427-2010</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260211893.pdf</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260211893.pdf</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_address</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260211893.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260211934</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>525,000.00</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>510 E BELMONT AVE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>85020</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>160-38-025</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mtc Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(202) 200-5938</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260211934.pdf</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260211934.pdf</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260211934.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260211955</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>285,729.00</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16521 N 171ST DR</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>85388</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>502-01-404</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mtg Finangialtoc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(201) 908-8913</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260211955.pdf</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260211955.pdf</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260211955.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260213276</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(s): Paul M Power, a married man as his sole and</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>264,000.00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>4034 W VOLTAIRE AVE</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>85029</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>149-26-146</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Name and Address of Trustee/Agent: Quality Loan Service Corporation</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>(202) 103-2054</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>(s): Paul M Power, a married man as his sole</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>and</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260213276.pdf</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260213276.pdf</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260213276.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260213302</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>396,000.00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2594 E BOSTON ST</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Gilbert</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>85295</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sale Or If You Have An Objection To The Trustee</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(202) 300-8998</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260213302.pdf</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260213302.pdf</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_apn</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260213302.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260213451</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lucy Akpan</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>43,780.00</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>or IDENTIFIABLE LOCATION: 4932 W SAINT ANNE AVENUE</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Laveen</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>85339</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>104-78-254</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>(866) 931-0036</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Lucy</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Akpan</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260213451.pdf</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260213451.pdf</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260213451.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260213720</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>516,000.00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7239 S 65TH DR</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Laveen</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>85339</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>104-85-149</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>inanciai-lnc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>(202) 208-7023</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260213720.pdf</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260213720.pdf</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260213720.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260213853</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>in favor of Financial Freedom Senior Funding</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>318,773.40</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>23-23-0708</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>before a trustee’s deed upon sale will be issued</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>(201) 900-3127</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2018-11-28</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>in favor of Financial Freedom Senior</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Funding</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260213853.pdf</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260213853.pdf</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260213853.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260213898</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>340,500.00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>140-42-178</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Prestige Default Services, Llc</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>(949) 427-2010</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>2006-05-01</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260213898.pdf</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260213898.pdf</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_owner, missing_address</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>45</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260213898.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260214110</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Francisco Javier Guzman Orozco, a married man as his sole and separate</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>300,000.00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>148-26-414</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pioneer Title Agency, Inc., an Arizona corporation</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>(202) 602-1411</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Francisco Javier Guzman Orozco, a married man as his</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>sole</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>separate</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260214110.pdf</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260214110.pdf</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>ocr_used, missing_address</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260214110.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260214859</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An Arizona</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>480,000.00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4037 S. 12th Street</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>113-25-057</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arizona Dept. of Real Estate.</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>(202) 405-4360</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260214859.pdf</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260214859.pdf</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260214859.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260214860</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An Arizona</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>480,000.00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4037 S. 12th Street</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>113-25-053</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arizona Dept. of Real Estate.</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>(202) 404-5323</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260214860.pdf</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260214860.pdf</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260214860.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260214861</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An Arizona</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>480,000.00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4037 S. 12th Street</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>13-2504</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arizona Dept. of Real Estate.</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>(202) 404-5062</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260214861.pdf</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260214861.pdf</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260214861.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260214862</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An Arizona</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>480,000.00</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4037 S. 12th Street</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>113-25-051</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arizona Dept. of Real Estate.</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>(202) 404-5059</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260214862.pdf</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260214862.pdf</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260214862.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260215914</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An Arizona</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>480,000.00</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>4037 S. 12th Street</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Maricopa</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>113-25-057</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arizona Dept. of Real Estate.</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>(202) 405-4360</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>https://legacy.recorder.maricopa.gov/UnOfficialDocs/pdf/20260215914.pdf</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/grouped_output/pdfs/20260215914.pdf</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>ocr_used</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/Chat-Scraper/Chat-Scraper/parsed_output/20260215914.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260215915</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>N/TR SALE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rymax Development, L.L.C., An Arizona</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>480,000.00</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>403